--- a/Taxa de Crescimento.xlsx
+++ b/Taxa de Crescimento.xlsx
@@ -607,7 +607,7 @@
         <v>99.90000000000001</v>
       </c>
       <c r="S2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         <v>33.71</v>
       </c>
       <c r="S3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -765,7 +765,7 @@
         <v>100.79</v>
       </c>
       <c r="S4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>63.62</v>
       </c>
       <c r="S5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>63.62</v>
       </c>
       <c r="S6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1072,7 +1072,7 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>93.45999999999999</v>
       </c>
       <c r="S10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1213,16 +1213,16 @@
         <v>5814</v>
       </c>
       <c r="P11" t="n">
-        <v>6093</v>
+        <v>6171</v>
       </c>
       <c r="Q11" t="n">
-        <v>6093</v>
+        <v>6171</v>
       </c>
       <c r="R11" t="n">
-        <v>97.48999999999999</v>
+        <v>98.73999999999999</v>
       </c>
       <c r="S11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1233,10 +1233,10 @@
         <v>5672.46</v>
       </c>
       <c r="V11" t="n">
-        <v>7.41</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="W11" t="n">
-        <v>1.181639093142961</v>
+        <v>1.198576448060394</v>
       </c>
     </row>
     <row r="12">
@@ -1292,16 +1292,16 @@
         <v>20912</v>
       </c>
       <c r="P12" t="n">
-        <v>20848</v>
+        <v>20934</v>
       </c>
       <c r="Q12" t="n">
-        <v>20912</v>
+        <v>20934</v>
       </c>
       <c r="R12" t="n">
-        <v>83.65000000000001</v>
+        <v>83.73999999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>25366.3</v>
       </c>
       <c r="V12" t="n">
-        <v>-17.56</v>
+        <v>-17.47</v>
       </c>
       <c r="W12" t="inlineStr"/>
     </row>
@@ -1378,7 +1378,7 @@
         <v>35.9</v>
       </c>
       <c r="S13" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>44.6</v>
       </c>
       <c r="S14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>105.95</v>
       </c>
       <c r="S15" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>57.98</v>
       </c>
       <c r="S16" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         <v>39.4</v>
       </c>
       <c r="S17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -1769,7 +1769,7 @@
         <v>113.48</v>
       </c>
       <c r="S18" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
         <v>62.62</v>
       </c>
       <c r="S21" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>6.12</v>
       </c>
       <c r="S22" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2121,16 +2121,16 @@
         <v>701</v>
       </c>
       <c r="P23" t="n">
-        <v>718</v>
+        <v>740</v>
       </c>
       <c r="Q23" t="n">
-        <v>718</v>
+        <v>740</v>
       </c>
       <c r="R23" t="n">
-        <v>23.93</v>
+        <v>24.67</v>
       </c>
       <c r="S23" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2141,10 +2141,10 @@
         <v>700.38</v>
       </c>
       <c r="V23" t="n">
-        <v>2.52</v>
+        <v>5.66</v>
       </c>
       <c r="W23" t="n">
-        <v>1.080065378688878</v>
+        <v>1.155406223755519</v>
       </c>
     </row>
     <row r="24">
@@ -2185,7 +2185,7 @@
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2251,16 +2251,16 @@
         <v>1472</v>
       </c>
       <c r="P25" t="n">
-        <v>1519</v>
+        <v>1594</v>
       </c>
       <c r="Q25" t="n">
-        <v>1519</v>
+        <v>1594</v>
       </c>
       <c r="R25" t="n">
-        <v>75.95</v>
+        <v>79.7</v>
       </c>
       <c r="S25" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -2271,10 +2271,10 @@
         <v>1400.36</v>
       </c>
       <c r="V25" t="n">
-        <v>8.470000000000001</v>
+        <v>13.83</v>
       </c>
       <c r="W25" t="n">
-        <v>1.194878144501162</v>
+        <v>1.244710963923838</v>
       </c>
     </row>
     <row r="26">
@@ -2330,7 +2330,7 @@
         <v>9466</v>
       </c>
       <c r="P26" t="n">
-        <v>9039</v>
+        <v>9373</v>
       </c>
       <c r="Q26" t="n">
         <v>9466</v>
@@ -2339,7 +2339,7 @@
         <v>75.73</v>
       </c>
       <c r="S26" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>42.73</v>
       </c>
       <c r="S28" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -2544,7 +2544,7 @@
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
       <c r="S29" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         <v>12217</v>
       </c>
       <c r="P30" t="n">
-        <v>11414</v>
+        <v>12017</v>
       </c>
       <c r="Q30" t="n">
         <v>12217</v>
@@ -2617,7 +2617,7 @@
         <v>40.72</v>
       </c>
       <c r="S30" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
         <v>58.49</v>
       </c>
       <c r="S31" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -2749,7 +2749,7 @@
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         <v>25.73</v>
       </c>
       <c r="S34" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
         <v>66.23</v>
       </c>
       <c r="S36" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         <v>75.03</v>
       </c>
       <c r="S37" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         <v>38.22</v>
       </c>
       <c r="S38" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
         <v>38.99</v>
       </c>
       <c r="S39" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>93</v>
       </c>
       <c r="S40" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -3362,7 +3362,7 @@
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
         <v>14.4</v>
       </c>
       <c r="S42" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>94.44</v>
       </c>
       <c r="S43" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>62.36</v>
       </c>
       <c r="S44" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -3664,7 +3664,7 @@
         <v>91.20999999999999</v>
       </c>
       <c r="S45" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         <v>18</v>
       </c>
       <c r="S46" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -3811,16 +3811,16 @@
         <v>3477</v>
       </c>
       <c r="P47" t="n">
-        <v>4079</v>
+        <v>4333</v>
       </c>
       <c r="Q47" t="n">
-        <v>4079</v>
+        <v>4333</v>
       </c>
       <c r="R47" t="n">
-        <v>27.19</v>
+        <v>28.89</v>
       </c>
       <c r="S47" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         <v>4438.47</v>
       </c>
       <c r="V47" t="n">
-        <v>-8.1</v>
+        <v>-2.38</v>
       </c>
       <c r="W47" t="inlineStr"/>
     </row>
@@ -3888,16 +3888,16 @@
         <v>967</v>
       </c>
       <c r="P48" t="n">
-        <v>967</v>
+        <v>1200</v>
       </c>
       <c r="Q48" t="n">
-        <v>967</v>
+        <v>1200</v>
       </c>
       <c r="R48" t="n">
-        <v>15.47</v>
+        <v>19.2</v>
       </c>
       <c r="S48" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -3908,7 +3908,7 @@
         <v>3939.79</v>
       </c>
       <c r="V48" t="n">
-        <v>-75.45999999999999</v>
+        <v>-69.54000000000001</v>
       </c>
       <c r="W48" t="inlineStr"/>
     </row>
@@ -3974,7 +3974,7 @@
         <v>54.97</v>
       </c>
       <c r="S49" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
         <v>67.7</v>
       </c>
       <c r="S50" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>2639</v>
       </c>
       <c r="P52" t="n">
-        <v>2564</v>
+        <v>2701</v>
       </c>
       <c r="Q52" t="n">
         <v>2726</v>
@@ -4177,7 +4177,7 @@
         <v>10.9</v>
       </c>
       <c r="S52" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -4230,7 +4230,7 @@
       <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr"/>
       <c r="S53" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -4305,7 +4305,7 @@
         <v>81.59999999999999</v>
       </c>
       <c r="S54" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>524.27</v>
       </c>
       <c r="S55" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -4463,7 +4463,7 @@
         <v>57.11</v>
       </c>
       <c r="S56" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -4542,7 +4542,7 @@
         <v>70.65000000000001</v>
       </c>
       <c r="S57" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
         <v>69.83</v>
       </c>
       <c r="S58" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -4691,16 +4691,16 @@
         <v>707</v>
       </c>
       <c r="P59" t="n">
-        <v>717</v>
+        <v>723</v>
       </c>
       <c r="Q59" t="n">
-        <v>717</v>
+        <v>723</v>
       </c>
       <c r="R59" t="n">
-        <v>71.7</v>
+        <v>72.3</v>
       </c>
       <c r="S59" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -4711,10 +4711,10 @@
         <v>651.84</v>
       </c>
       <c r="V59" t="n">
-        <v>10</v>
+        <v>10.92</v>
       </c>
       <c r="W59" t="n">
-        <v>1.211527658628588</v>
+        <v>1.220445957467314</v>
       </c>
     </row>
     <row r="60">
@@ -4779,7 +4779,7 @@
         <v>36</v>
       </c>
       <c r="S60" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -4834,7 +4834,7 @@
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr"/>
       <c r="S61" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -4909,7 +4909,7 @@
         <v>105.62</v>
       </c>
       <c r="S62" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>81.59999999999999</v>
       </c>
       <c r="S63" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         <v>98.48</v>
       </c>
       <c r="S64" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -5146,7 +5146,7 @@
         <v>96.95</v>
       </c>
       <c r="S65" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -5225,7 +5225,7 @@
         <v>52.97</v>
       </c>
       <c r="S66" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -5298,7 +5298,7 @@
         <v>77.69</v>
       </c>
       <c r="S67" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
       <c r="S68" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -5417,7 +5417,7 @@
         <v>11393</v>
       </c>
       <c r="P69" t="n">
-        <v>11012</v>
+        <v>11429</v>
       </c>
       <c r="Q69" t="n">
         <v>12404</v>
@@ -5426,7 +5426,7 @@
         <v>99.23</v>
       </c>
       <c r="S69" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -5481,7 +5481,7 @@
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
       <c r="S70" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -5545,7 +5545,7 @@
         <v>12752</v>
       </c>
       <c r="P71" t="n">
-        <v>11980</v>
+        <v>11592</v>
       </c>
       <c r="Q71" t="n">
         <v>12752</v>
@@ -5554,7 +5554,7 @@
         <v>51.01</v>
       </c>
       <c r="S71" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
         <v>93.93000000000001</v>
       </c>
       <c r="S72" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -5710,7 +5710,7 @@
         <v>110.42</v>
       </c>
       <c r="S73" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -5780,16 +5780,16 @@
         <v>25454</v>
       </c>
       <c r="P74" t="n">
-        <v>26363</v>
+        <v>27366</v>
       </c>
       <c r="Q74" t="n">
-        <v>26363</v>
+        <v>27366</v>
       </c>
       <c r="R74" t="n">
-        <v>58.58</v>
+        <v>60.81</v>
       </c>
       <c r="S74" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -5800,10 +5800,10 @@
         <v>21655.98</v>
       </c>
       <c r="V74" t="n">
-        <v>21.74</v>
+        <v>26.37</v>
       </c>
       <c r="W74" t="n">
-        <v>1.292523044714382</v>
+        <v>1.313487197667266</v>
       </c>
     </row>
     <row r="75">
@@ -5844,7 +5844,7 @@
       <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr"/>
       <c r="S75" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         <v>59.94</v>
       </c>
       <c r="S76" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -5996,7 +5996,7 @@
         <v>104</v>
       </c>
       <c r="S77" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -6073,7 +6073,7 @@
         <v>108.21</v>
       </c>
       <c r="S78" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -6143,16 +6143,16 @@
         <v>19559</v>
       </c>
       <c r="P79" t="n">
-        <v>17616</v>
+        <v>20590</v>
       </c>
       <c r="Q79" t="n">
-        <v>19559</v>
+        <v>20590</v>
       </c>
       <c r="R79" t="n">
-        <v>43.46</v>
+        <v>45.76</v>
       </c>
       <c r="S79" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -6163,10 +6163,10 @@
         <v>19321.81</v>
       </c>
       <c r="V79" t="n">
-        <v>1.23</v>
+        <v>6.56</v>
       </c>
       <c r="W79" t="n">
-        <v>1.017400841772182</v>
+        <v>1.169702235577781</v>
       </c>
     </row>
     <row r="80">
@@ -6231,7 +6231,7 @@
         <v>80.14</v>
       </c>
       <c r="S80" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -6308,7 +6308,7 @@
         <v>43.25</v>
       </c>
       <c r="S81" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -6376,16 +6376,16 @@
         <v>36867</v>
       </c>
       <c r="P82" t="n">
-        <v>38300</v>
+        <v>38477</v>
       </c>
       <c r="Q82" t="n">
-        <v>38300</v>
+        <v>38477</v>
       </c>
       <c r="R82" t="n">
-        <v>85.11</v>
+        <v>85.5</v>
       </c>
       <c r="S82" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -6396,10 +6396,10 @@
         <v>35969.29</v>
       </c>
       <c r="V82" t="n">
-        <v>6.48</v>
+        <v>6.97</v>
       </c>
       <c r="W82" t="n">
-        <v>1.168506817282867</v>
+        <v>1.175626584341361</v>
       </c>
     </row>
     <row r="83">
@@ -6464,7 +6464,7 @@
         <v>66.56999999999999</v>
       </c>
       <c r="S83" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -6541,7 +6541,7 @@
         <v>93.84</v>
       </c>
       <c r="S84" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -6620,7 +6620,7 @@
         <v>59.84</v>
       </c>
       <c r="S85" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -6697,7 +6697,7 @@
         <v>48.39</v>
       </c>
       <c r="S86" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -6774,7 +6774,7 @@
         <v>106.75</v>
       </c>
       <c r="S87" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -6853,7 +6853,7 @@
         <v>58.65</v>
       </c>
       <c r="S88" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -6930,7 +6930,7 @@
         <v>54.6</v>
       </c>
       <c r="S89" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -7000,7 +7000,7 @@
         <v>23857</v>
       </c>
       <c r="P90" t="n">
-        <v>18933</v>
+        <v>19317</v>
       </c>
       <c r="Q90" t="n">
         <v>23857</v>
@@ -7009,7 +7009,7 @@
         <v>95.43000000000001</v>
       </c>
       <c r="S90" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -7088,7 +7088,7 @@
         <v>56.23</v>
       </c>
       <c r="S91" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -7165,7 +7165,7 @@
         <v>79.76000000000001</v>
       </c>
       <c r="S92" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -7244,7 +7244,7 @@
         <v>73.36</v>
       </c>
       <c r="S93" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -7323,7 +7323,7 @@
         <v>90.04000000000001</v>
       </c>
       <c r="S94" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -7376,7 +7376,7 @@
       <c r="Q95" t="inlineStr"/>
       <c r="R95" t="inlineStr"/>
       <c r="S95" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -7449,7 +7449,7 @@
         <v>92</v>
       </c>
       <c r="S96" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -7519,16 +7519,16 @@
         <v>22630</v>
       </c>
       <c r="P97" t="n">
-        <v>23434</v>
+        <v>23706</v>
       </c>
       <c r="Q97" t="n">
-        <v>23434</v>
+        <v>23706</v>
       </c>
       <c r="R97" t="n">
-        <v>93.73999999999999</v>
+        <v>94.81999999999999</v>
       </c>
       <c r="S97" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>23875.94</v>
       </c>
       <c r="V97" t="n">
-        <v>-1.85</v>
+        <v>-0.71</v>
       </c>
       <c r="W97" t="inlineStr"/>
     </row>
@@ -7605,7 +7605,7 @@
         <v>80.17</v>
       </c>
       <c r="S98" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -7684,7 +7684,7 @@
         <v>108.33</v>
       </c>
       <c r="S99" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -7739,7 +7739,7 @@
       <c r="Q100" t="inlineStr"/>
       <c r="R100" t="inlineStr"/>
       <c r="S100" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -7812,7 +7812,7 @@
         <v>71.52</v>
       </c>
       <c r="S101" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -7861,7 +7861,7 @@
       <c r="Q102" t="inlineStr"/>
       <c r="R102" t="inlineStr"/>
       <c r="S102" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -7934,7 +7934,7 @@
         <v>89.53</v>
       </c>
       <c r="S103" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -8011,7 +8011,7 @@
         <v>65.48</v>
       </c>
       <c r="S104" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -8088,7 +8088,7 @@
         <v>70.98</v>
       </c>
       <c r="S105" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -8167,7 +8167,7 @@
         <v>40.29</v>
       </c>
       <c r="S106" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -8231,7 +8231,7 @@
         <v>27513</v>
       </c>
       <c r="P107" t="n">
-        <v>15393</v>
+        <v>14564</v>
       </c>
       <c r="Q107" t="n">
         <v>27513</v>
@@ -8240,7 +8240,7 @@
         <v>110.05</v>
       </c>
       <c r="S107" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
         <v>9607</v>
       </c>
       <c r="P108" t="n">
-        <v>3973</v>
+        <v>3680</v>
       </c>
       <c r="Q108" t="n">
         <v>9607</v>
@@ -8319,7 +8319,7 @@
         <v>102.47</v>
       </c>
       <c r="S108" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -8396,7 +8396,7 @@
         <v>85.12</v>
       </c>
       <c r="S109" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -8449,7 +8449,7 @@
       <c r="Q110" t="inlineStr"/>
       <c r="R110" t="inlineStr"/>
       <c r="S110" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -8522,7 +8522,7 @@
         <v>58.03</v>
       </c>
       <c r="S111" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -8575,7 +8575,7 @@
       <c r="Q112" t="inlineStr"/>
       <c r="R112" t="inlineStr"/>
       <c r="S112" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -8624,7 +8624,7 @@
       <c r="Q113" t="inlineStr"/>
       <c r="R113" t="inlineStr"/>
       <c r="S113" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -8697,7 +8697,7 @@
         <v>91.88</v>
       </c>
       <c r="S114" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -8774,7 +8774,7 @@
         <v>19.62</v>
       </c>
       <c r="S115" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
       <c r="Q116" t="inlineStr"/>
       <c r="R116" t="inlineStr"/>
       <c r="S116" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -8876,7 +8876,7 @@
       <c r="Q117" t="inlineStr"/>
       <c r="R117" t="inlineStr"/>
       <c r="S117" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -8940,7 +8940,7 @@
         <v>20122</v>
       </c>
       <c r="P118" t="n">
-        <v>19866</v>
+        <v>19937</v>
       </c>
       <c r="Q118" t="n">
         <v>20122</v>
@@ -8949,7 +8949,7 @@
         <v>80.48999999999999</v>
       </c>
       <c r="S118" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -9028,7 +9028,7 @@
         <v>95.56999999999999</v>
       </c>
       <c r="S119" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -9107,7 +9107,7 @@
         <v>58.46</v>
       </c>
       <c r="S120" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -9186,7 +9186,7 @@
         <v>56.58</v>
       </c>
       <c r="S121" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -9265,7 +9265,7 @@
         <v>3.93</v>
       </c>
       <c r="S122" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -9314,7 +9314,7 @@
       <c r="Q123" t="inlineStr"/>
       <c r="R123" t="inlineStr"/>
       <c r="S123" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -9378,16 +9378,16 @@
         <v>16024</v>
       </c>
       <c r="P124" t="n">
-        <v>17836</v>
+        <v>17861</v>
       </c>
       <c r="Q124" t="n">
-        <v>17836</v>
+        <v>17861</v>
       </c>
       <c r="R124" t="n">
-        <v>59.45</v>
+        <v>59.54</v>
       </c>
       <c r="S124" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -9398,7 +9398,7 @@
         <v>19742.71</v>
       </c>
       <c r="V124" t="n">
-        <v>-9.66</v>
+        <v>-9.529999999999999</v>
       </c>
       <c r="W124" t="inlineStr"/>
     </row>
@@ -9455,16 +9455,16 @@
         <v>10859</v>
       </c>
       <c r="P125" t="n">
-        <v>10764</v>
+        <v>12850</v>
       </c>
       <c r="Q125" t="n">
-        <v>10859</v>
+        <v>12850</v>
       </c>
       <c r="R125" t="n">
-        <v>86.87</v>
+        <v>102.8</v>
       </c>
       <c r="S125" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -9475,10 +9475,10 @@
         <v>5742.82</v>
       </c>
       <c r="V125" t="n">
-        <v>89.09</v>
+        <v>123.76</v>
       </c>
       <c r="W125" t="n">
-        <v>1.453736673598276</v>
+        <v>1.494106969963621</v>
       </c>
     </row>
     <row r="126">
@@ -9543,7 +9543,7 @@
         <v>102.76</v>
       </c>
       <c r="S126" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -9622,7 +9622,7 @@
         <v>109.5</v>
       </c>
       <c r="S127" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -9701,7 +9701,7 @@
         <v>80.19</v>
       </c>
       <c r="S128" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -9780,7 +9780,7 @@
         <v>99.58</v>
       </c>
       <c r="S129" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -9853,7 +9853,7 @@
         <v>63.05</v>
       </c>
       <c r="S130" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -9932,7 +9932,7 @@
         <v>84.26000000000001</v>
       </c>
       <c r="S131" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -10011,7 +10011,7 @@
         <v>110.26</v>
       </c>
       <c r="S132" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -10081,16 +10081,16 @@
         <v>26362</v>
       </c>
       <c r="P133" t="n">
-        <v>27220</v>
+        <v>28323</v>
       </c>
       <c r="Q133" t="n">
-        <v>27220</v>
+        <v>28323</v>
       </c>
       <c r="R133" t="n">
-        <v>90.73</v>
+        <v>94.41</v>
       </c>
       <c r="S133" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -10101,7 +10101,7 @@
         <v>32518.02</v>
       </c>
       <c r="V133" t="n">
-        <v>-16.29</v>
+        <v>-12.9</v>
       </c>
       <c r="W133" t="inlineStr"/>
     </row>
@@ -10167,7 +10167,7 @@
         <v>92.59999999999999</v>
       </c>
       <c r="S134" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -10246,7 +10246,7 @@
         <v>32.86</v>
       </c>
       <c r="S135" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -10295,7 +10295,7 @@
       <c r="Q136" t="inlineStr"/>
       <c r="R136" t="inlineStr"/>
       <c r="S136" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -10370,7 +10370,7 @@
         <v>38.1</v>
       </c>
       <c r="S137" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -10423,7 +10423,7 @@
       <c r="Q138" t="inlineStr"/>
       <c r="R138" t="inlineStr"/>
       <c r="S138" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -10496,7 +10496,7 @@
         <v>16.19</v>
       </c>
       <c r="S139" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -10549,7 +10549,7 @@
       <c r="Q140" t="inlineStr"/>
       <c r="R140" t="inlineStr"/>
       <c r="S140" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -10624,7 +10624,7 @@
         <v>93.81</v>
       </c>
       <c r="S141" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -10703,7 +10703,7 @@
         <v>44.1</v>
       </c>
       <c r="S142" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -10782,7 +10782,7 @@
         <v>56.92</v>
       </c>
       <c r="S143" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -10861,7 +10861,7 @@
         <v>99.83</v>
       </c>
       <c r="S144" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -10931,7 +10931,7 @@
         <v>17803</v>
       </c>
       <c r="P145" t="n">
-        <v>14201</v>
+        <v>16445</v>
       </c>
       <c r="Q145" t="n">
         <v>19796</v>
@@ -10940,7 +10940,7 @@
         <v>79.18000000000001</v>
       </c>
       <c r="S145" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -10995,7 +10995,7 @@
       <c r="Q146" t="inlineStr"/>
       <c r="R146" t="inlineStr"/>
       <c r="S146" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -11068,7 +11068,7 @@
         <v>39.2</v>
       </c>
       <c r="S147" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -11145,7 +11145,7 @@
         <v>42.99</v>
       </c>
       <c r="S148" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -11222,7 +11222,7 @@
         <v>85.90000000000001</v>
       </c>
       <c r="S149" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -11301,7 +11301,7 @@
         <v>59.9</v>
       </c>
       <c r="S150" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
         <v>0</v>
       </c>
       <c r="S151" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -11451,7 +11451,7 @@
         <v>53.49</v>
       </c>
       <c r="S152" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -11528,7 +11528,7 @@
         <v>70.64</v>
       </c>
       <c r="S153" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -11581,7 +11581,7 @@
       <c r="Q154" t="inlineStr"/>
       <c r="R154" t="inlineStr"/>
       <c r="S154" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -11630,7 +11630,7 @@
       <c r="Q155" t="inlineStr"/>
       <c r="R155" t="inlineStr"/>
       <c r="S155" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -11703,7 +11703,7 @@
         <v>106.18</v>
       </c>
       <c r="S156" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -11782,7 +11782,7 @@
         <v>84.48</v>
       </c>
       <c r="S157" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -11859,7 +11859,7 @@
         <v>98.66</v>
       </c>
       <c r="S158" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -11938,7 +11938,7 @@
         <v>65.83</v>
       </c>
       <c r="S159" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -12017,7 +12017,7 @@
         <v>3.87</v>
       </c>
       <c r="S160" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -12066,7 +12066,7 @@
       <c r="Q161" t="inlineStr"/>
       <c r="R161" t="inlineStr"/>
       <c r="S161" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         <v>108.88</v>
       </c>
       <c r="S162" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T162" t="inlineStr">
         <is>
@@ -12209,16 +12209,16 @@
         <v>18776</v>
       </c>
       <c r="P163" t="n">
-        <v>19040</v>
+        <v>19135</v>
       </c>
       <c r="Q163" t="n">
-        <v>19040</v>
+        <v>19135</v>
       </c>
       <c r="R163" t="n">
-        <v>76.16</v>
+        <v>76.54000000000001</v>
       </c>
       <c r="S163" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T163" t="inlineStr">
         <is>
@@ -12229,10 +12229,10 @@
         <v>16858.56</v>
       </c>
       <c r="V163" t="n">
-        <v>12.94</v>
+        <v>13.5</v>
       </c>
       <c r="W163" t="n">
-        <v>1.237830529186372</v>
+        <v>1.242208454413772</v>
       </c>
     </row>
     <row r="164">
@@ -12297,7 +12297,7 @@
         <v>104.22</v>
       </c>
       <c r="S164" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T164" t="inlineStr">
         <is>
@@ -12365,7 +12365,7 @@
         <v>12269</v>
       </c>
       <c r="P165" t="n">
-        <v>10035</v>
+        <v>11682</v>
       </c>
       <c r="Q165" t="n">
         <v>12557</v>
@@ -12374,7 +12374,7 @@
         <v>62.78</v>
       </c>
       <c r="S165" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -12427,7 +12427,7 @@
       <c r="Q166" t="inlineStr"/>
       <c r="R166" t="inlineStr"/>
       <c r="S166" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -12491,7 +12491,7 @@
         <v>8322</v>
       </c>
       <c r="P167" t="n">
-        <v>8254</v>
+        <v>11042</v>
       </c>
       <c r="Q167" t="n">
         <v>11890</v>
@@ -12500,7 +12500,7 @@
         <v>59.45</v>
       </c>
       <c r="S167" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T167" t="inlineStr">
         <is>
@@ -12568,7 +12568,7 @@
         <v>23412</v>
       </c>
       <c r="P168" t="n">
-        <v>20190</v>
+        <v>20680</v>
       </c>
       <c r="Q168" t="n">
         <v>23412</v>
@@ -12577,7 +12577,7 @@
         <v>78.04000000000001</v>
       </c>
       <c r="S168" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -12656,7 +12656,7 @@
         <v>82.58</v>
       </c>
       <c r="S169" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -12733,7 +12733,7 @@
         <v>47.57</v>
       </c>
       <c r="S170" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -12812,7 +12812,7 @@
         <v>29.74</v>
       </c>
       <c r="S171" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -12865,7 +12865,7 @@
       <c r="Q172" t="inlineStr"/>
       <c r="R172" t="inlineStr"/>
       <c r="S172" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -12938,7 +12938,7 @@
         <v>43.76</v>
       </c>
       <c r="S173" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -13017,7 +13017,7 @@
         <v>66.22</v>
       </c>
       <c r="S174" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T174" t="inlineStr">
         <is>
@@ -13072,7 +13072,7 @@
       <c r="Q175" t="inlineStr"/>
       <c r="R175" t="inlineStr"/>
       <c r="S175" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T175" t="inlineStr">
         <is>
@@ -13145,7 +13145,7 @@
         <v>0</v>
       </c>
       <c r="S176" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T176" t="inlineStr">
         <is>
@@ -13198,7 +13198,7 @@
       <c r="Q177" t="inlineStr"/>
       <c r="R177" t="inlineStr"/>
       <c r="S177" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T177" t="inlineStr">
         <is>
@@ -13273,7 +13273,7 @@
         <v>48.54</v>
       </c>
       <c r="S178" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T178" t="inlineStr">
         <is>
@@ -13350,7 +13350,7 @@
         <v>90.65000000000001</v>
       </c>
       <c r="S179" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T179" t="inlineStr">
         <is>
@@ -13420,7 +13420,7 @@
         <v>19578</v>
       </c>
       <c r="P180" t="n">
-        <v>13531</v>
+        <v>15584</v>
       </c>
       <c r="Q180" t="n">
         <v>19578</v>
@@ -13429,7 +13429,7 @@
         <v>130.52</v>
       </c>
       <c r="S180" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T180" t="inlineStr">
         <is>
@@ -13508,7 +13508,7 @@
         <v>88.01000000000001</v>
       </c>
       <c r="S181" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T181" t="inlineStr">
         <is>
@@ -13587,7 +13587,7 @@
         <v>95.17</v>
       </c>
       <c r="S182" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -13666,7 +13666,7 @@
         <v>-10.65</v>
       </c>
       <c r="S183" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T183" t="inlineStr">
         <is>
@@ -13743,7 +13743,7 @@
         <v>79</v>
       </c>
       <c r="S184" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -13822,7 +13822,7 @@
         <v>97.13</v>
       </c>
       <c r="S185" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -13899,7 +13899,7 @@
         <v>105.32</v>
       </c>
       <c r="S186" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -13978,7 +13978,7 @@
         <v>0</v>
       </c>
       <c r="S187" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -14016,7 +14016,7 @@
         <v>13.8</v>
       </c>
       <c r="F188" t="n">
-        <v>25000</v>
+        <v>15000</v>
       </c>
       <c r="G188" t="n">
         <v>119</v>
@@ -14052,10 +14052,10 @@
         <v>11432</v>
       </c>
       <c r="R188" t="n">
-        <v>45.73</v>
+        <v>76.20999999999999</v>
       </c>
       <c r="S188" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T188" t="inlineStr">
         <is>
@@ -14125,7 +14125,7 @@
         <v>19286</v>
       </c>
       <c r="P189" t="n">
-        <v>15069</v>
+        <v>16782</v>
       </c>
       <c r="Q189" t="n">
         <v>23208</v>
@@ -14134,7 +14134,7 @@
         <v>92.83</v>
       </c>
       <c r="S189" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T189" t="inlineStr">
         <is>
@@ -14211,7 +14211,7 @@
         <v>56.31</v>
       </c>
       <c r="S190" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T190" t="inlineStr">
         <is>
@@ -14281,7 +14281,7 @@
         <v>26734</v>
       </c>
       <c r="P191" t="n">
-        <v>20523</v>
+        <v>24093</v>
       </c>
       <c r="Q191" t="n">
         <v>27359</v>
@@ -14290,7 +14290,7 @@
         <v>91.2</v>
       </c>
       <c r="S191" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T191" t="inlineStr">
         <is>
@@ -14369,7 +14369,7 @@
         <v>44.89</v>
       </c>
       <c r="S192" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T192" t="inlineStr">
         <is>
@@ -14446,7 +14446,7 @@
         <v>89.28</v>
       </c>
       <c r="S193" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T193" t="inlineStr">
         <is>
@@ -14525,7 +14525,7 @@
         <v>90.27</v>
       </c>
       <c r="S194" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -14604,7 +14604,7 @@
         <v>52.47</v>
       </c>
       <c r="S195" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T195" t="inlineStr">
         <is>
@@ -14668,16 +14668,16 @@
         <v>11271</v>
       </c>
       <c r="P196" t="n">
-        <v>10447</v>
+        <v>11823</v>
       </c>
       <c r="Q196" t="n">
-        <v>11271</v>
+        <v>11823</v>
       </c>
       <c r="R196" t="n">
-        <v>90.17</v>
+        <v>94.58</v>
       </c>
       <c r="S196" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T196" t="inlineStr">
         <is>
@@ -14688,10 +14688,10 @@
         <v>10941.96</v>
       </c>
       <c r="V196" t="n">
-        <v>3.01</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="W196" t="n">
-        <v>1.096176636134711</v>
+        <v>1.189824726499131</v>
       </c>
     </row>
     <row r="197">
@@ -14732,7 +14732,7 @@
       <c r="Q197" t="inlineStr"/>
       <c r="R197" t="inlineStr"/>
       <c r="S197" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T197" t="inlineStr">
         <is>
@@ -14805,7 +14805,7 @@
         <v>51.91</v>
       </c>
       <c r="S198" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T198" t="inlineStr">
         <is>
@@ -14882,7 +14882,7 @@
         <v>61.17</v>
       </c>
       <c r="S199" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T199" t="inlineStr">
         <is>
@@ -14959,7 +14959,7 @@
         <v>64.98</v>
       </c>
       <c r="S200" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T200" t="inlineStr">
         <is>
@@ -15038,7 +15038,7 @@
         <v>50.06</v>
       </c>
       <c r="S201" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T201" t="inlineStr">
         <is>
@@ -15115,7 +15115,7 @@
         <v>10.98</v>
       </c>
       <c r="S202" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T202" t="inlineStr">
         <is>
@@ -15168,7 +15168,7 @@
       <c r="Q203" t="inlineStr"/>
       <c r="R203" t="inlineStr"/>
       <c r="S203" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T203" t="inlineStr">
         <is>
@@ -15232,7 +15232,7 @@
         <v>25463</v>
       </c>
       <c r="P204" t="n">
-        <v>22986</v>
+        <v>23020</v>
       </c>
       <c r="Q204" t="n">
         <v>25463</v>
@@ -15241,7 +15241,7 @@
         <v>101.85</v>
       </c>
       <c r="S204" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T204" t="inlineStr">
         <is>
@@ -15318,7 +15318,7 @@
         <v>18.95</v>
       </c>
       <c r="S205" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T205" t="inlineStr">
         <is>
@@ -15395,7 +15395,7 @@
         <v>58.47</v>
       </c>
       <c r="S206" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T206" t="inlineStr">
         <is>
@@ -15444,7 +15444,7 @@
       <c r="Q207" t="inlineStr"/>
       <c r="R207" t="inlineStr"/>
       <c r="S207" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T207" t="inlineStr">
         <is>
@@ -15517,7 +15517,7 @@
         <v>36.68</v>
       </c>
       <c r="S208" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T208" t="inlineStr">
         <is>
@@ -15596,7 +15596,7 @@
         <v>9.74</v>
       </c>
       <c r="S209" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T209" t="inlineStr">
         <is>
@@ -15673,7 +15673,7 @@
         <v>41.86</v>
       </c>
       <c r="S210" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T210" t="inlineStr">
         <is>
@@ -15726,7 +15726,7 @@
       <c r="Q211" t="inlineStr"/>
       <c r="R211" t="inlineStr"/>
       <c r="S211" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T211" t="inlineStr">
         <is>
@@ -15801,7 +15801,7 @@
         <v>91.16</v>
       </c>
       <c r="S212" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T212" t="inlineStr">
         <is>
@@ -15856,7 +15856,7 @@
       <c r="Q213" t="inlineStr"/>
       <c r="R213" t="inlineStr"/>
       <c r="S213" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T213" t="inlineStr">
         <is>
@@ -15907,7 +15907,7 @@
       <c r="Q214" t="inlineStr"/>
       <c r="R214" t="inlineStr"/>
       <c r="S214" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T214" t="inlineStr">
         <is>
@@ -15973,16 +15973,16 @@
         <v>2584</v>
       </c>
       <c r="P215" t="n">
-        <v>2638</v>
+        <v>2639</v>
       </c>
       <c r="Q215" t="n">
-        <v>2638</v>
+        <v>2639</v>
       </c>
       <c r="R215" t="n">
-        <v>87.93000000000001</v>
+        <v>87.97</v>
       </c>
       <c r="S215" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T215" t="inlineStr">
         <is>
@@ -15993,10 +15993,10 @@
         <v>2510.67</v>
       </c>
       <c r="V215" t="n">
-        <v>5.07</v>
+        <v>5.11</v>
       </c>
       <c r="W215" t="n">
-        <v>1.144855469430165</v>
+        <v>1.145605460470037</v>
       </c>
     </row>
     <row r="216">
@@ -16061,7 +16061,7 @@
         <v>48.51</v>
       </c>
       <c r="S216" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T216" t="inlineStr">
         <is>
@@ -16138,7 +16138,7 @@
         <v>86.75</v>
       </c>
       <c r="S217" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T217" t="inlineStr">
         <is>
@@ -16217,7 +16217,7 @@
         <v>79.45999999999999</v>
       </c>
       <c r="S218" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T218" t="inlineStr">
         <is>
@@ -16296,7 +16296,7 @@
         <v>53.94</v>
       </c>
       <c r="S219" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T219" t="inlineStr">
         <is>
@@ -16375,7 +16375,7 @@
         <v>29.52</v>
       </c>
       <c r="S220" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T220" t="inlineStr">
         <is>
@@ -16452,7 +16452,7 @@
         <v>52.03</v>
       </c>
       <c r="S221" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T221" t="inlineStr">
         <is>
@@ -16505,7 +16505,7 @@
       <c r="Q222" t="inlineStr"/>
       <c r="R222" t="inlineStr"/>
       <c r="S222" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T222" t="inlineStr">
         <is>
@@ -16578,7 +16578,7 @@
         <v>46.12</v>
       </c>
       <c r="S223" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T223" t="inlineStr">
         <is>
@@ -16651,7 +16651,7 @@
         <v>21.77</v>
       </c>
       <c r="S224" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T224" t="inlineStr">
         <is>
@@ -16728,7 +16728,7 @@
         <v>96.52</v>
       </c>
       <c r="S225" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T225" t="inlineStr">
         <is>
@@ -16781,7 +16781,7 @@
       <c r="Q226" t="inlineStr"/>
       <c r="R226" t="inlineStr"/>
       <c r="S226" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T226" t="inlineStr">
         <is>
@@ -16856,7 +16856,7 @@
         <v>103.83</v>
       </c>
       <c r="S227" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T227" t="inlineStr">
         <is>
@@ -16935,7 +16935,7 @@
         <v>72.12</v>
       </c>
       <c r="S228" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T228" t="inlineStr">
         <is>
@@ -17012,7 +17012,7 @@
         <v>90.18000000000001</v>
       </c>
       <c r="S229" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T229" t="inlineStr">
         <is>
@@ -17089,7 +17089,7 @@
         <v>42.12</v>
       </c>
       <c r="S230" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T230" t="inlineStr">
         <is>
@@ -17166,7 +17166,7 @@
         <v>90.2</v>
       </c>
       <c r="S231" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T231" t="inlineStr">
         <is>
@@ -17236,16 +17236,16 @@
         <v>29585</v>
       </c>
       <c r="P232" t="n">
-        <v>29329</v>
+        <v>29745</v>
       </c>
       <c r="Q232" t="n">
-        <v>29585</v>
+        <v>29745</v>
       </c>
       <c r="R232" t="n">
-        <v>98.62</v>
+        <v>99.15000000000001</v>
       </c>
       <c r="S232" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T232" t="inlineStr">
         <is>
@@ -17256,10 +17256,10 @@
         <v>28960.51</v>
       </c>
       <c r="V232" t="n">
-        <v>2.16</v>
+        <v>2.71</v>
       </c>
       <c r="W232" t="n">
-        <v>1.066279711808841</v>
+        <v>1.086627706232656</v>
       </c>
     </row>
     <row r="233">
@@ -17324,7 +17324,7 @@
         <v>7.17</v>
       </c>
       <c r="S233" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T233" t="inlineStr">
         <is>
@@ -17373,7 +17373,7 @@
       <c r="Q234" t="inlineStr"/>
       <c r="R234" t="inlineStr"/>
       <c r="S234" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T234" t="inlineStr">
         <is>
@@ -17446,7 +17446,7 @@
         <v>67.78</v>
       </c>
       <c r="S235" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T235" t="inlineStr">
         <is>
@@ -17514,7 +17514,7 @@
         <v>6622</v>
       </c>
       <c r="P236" t="n">
-        <v>5916</v>
+        <v>5941</v>
       </c>
       <c r="Q236" t="n">
         <v>6622</v>
@@ -17523,7 +17523,7 @@
         <v>65.95999999999999</v>
       </c>
       <c r="S236" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T236" t="inlineStr">
         <is>
@@ -17600,7 +17600,7 @@
         <v>75.01000000000001</v>
       </c>
       <c r="S237" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T237" t="inlineStr">
         <is>
@@ -17679,7 +17679,7 @@
         <v>42.74</v>
       </c>
       <c r="S238" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T238" t="inlineStr">
         <is>
@@ -17758,7 +17758,7 @@
         <v>15.48</v>
       </c>
       <c r="S239" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T239" t="inlineStr">
         <is>
@@ -17835,7 +17835,7 @@
         <v>46.39</v>
       </c>
       <c r="S240" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T240" t="inlineStr">
         <is>
@@ -17914,7 +17914,7 @@
         <v>69.8</v>
       </c>
       <c r="S241" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T241" t="inlineStr">
         <is>
@@ -17993,7 +17993,7 @@
         <v>1.26</v>
       </c>
       <c r="S242" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T242" t="inlineStr">
         <is>
@@ -18061,7 +18061,7 @@
         <v>1485</v>
       </c>
       <c r="P243" t="n">
-        <v>1317</v>
+        <v>1347</v>
       </c>
       <c r="Q243" t="n">
         <v>2389</v>
@@ -18070,7 +18070,7 @@
         <v>39.82</v>
       </c>
       <c r="S243" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T243" t="inlineStr">
         <is>
@@ -18147,7 +18147,7 @@
         <v>55.63</v>
       </c>
       <c r="S244" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T244" t="inlineStr">
         <is>
@@ -18226,7 +18226,7 @@
         <v>49.5</v>
       </c>
       <c r="S245" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T245" t="inlineStr">
         <is>
@@ -18296,7 +18296,7 @@
         <v>7330</v>
       </c>
       <c r="P246" t="n">
-        <v>6578</v>
+        <v>6332</v>
       </c>
       <c r="Q246" t="n">
         <v>7330</v>
@@ -18305,7 +18305,7 @@
         <v>73.3</v>
       </c>
       <c r="S246" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T246" t="inlineStr">
         <is>
@@ -18382,7 +18382,7 @@
         <v>43.38</v>
       </c>
       <c r="S247" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T247" t="inlineStr">
         <is>
@@ -18459,7 +18459,7 @@
         <v>43.32</v>
       </c>
       <c r="S248" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T248" t="inlineStr">
         <is>
@@ -18538,7 +18538,7 @@
         <v>61.67</v>
       </c>
       <c r="S249" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T249" t="inlineStr">
         <is>
@@ -18615,7 +18615,7 @@
         <v>50.13</v>
       </c>
       <c r="S250" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T250" t="inlineStr">
         <is>
@@ -18694,7 +18694,7 @@
         <v>50</v>
       </c>
       <c r="S251" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T251" t="inlineStr">
         <is>
@@ -18764,7 +18764,7 @@
         <v>6287</v>
       </c>
       <c r="P252" t="n">
-        <v>6082</v>
+        <v>6193</v>
       </c>
       <c r="Q252" t="n">
         <v>6287</v>
@@ -18773,7 +18773,7 @@
         <v>62.87</v>
       </c>
       <c r="S252" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T252" t="inlineStr">
         <is>
@@ -18841,16 +18841,16 @@
         <v>1432</v>
       </c>
       <c r="P253" t="n">
-        <v>1400</v>
+        <v>1695</v>
       </c>
       <c r="Q253" t="n">
-        <v>1432</v>
+        <v>1695</v>
       </c>
       <c r="R253" t="n">
-        <v>23.96</v>
+        <v>28.37</v>
       </c>
       <c r="S253" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T253" t="inlineStr">
         <is>
@@ -18861,7 +18861,7 @@
         <v>1954.52</v>
       </c>
       <c r="V253" t="n">
-        <v>-26.73</v>
+        <v>-13.28</v>
       </c>
       <c r="W253" t="inlineStr"/>
     </row>
@@ -18927,7 +18927,7 @@
         <v>43.63</v>
       </c>
       <c r="S254" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T254" t="inlineStr">
         <is>
@@ -19004,7 +19004,7 @@
         <v>51.15</v>
       </c>
       <c r="S255" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T255" t="inlineStr">
         <is>
@@ -19083,7 +19083,7 @@
         <v>82.90000000000001</v>
       </c>
       <c r="S256" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T256" t="inlineStr">
         <is>
@@ -19153,7 +19153,7 @@
         <v>1797</v>
       </c>
       <c r="P257" t="n">
-        <v>1321</v>
+        <v>1220</v>
       </c>
       <c r="Q257" t="n">
         <v>1930</v>
@@ -19162,7 +19162,7 @@
         <v>48.25</v>
       </c>
       <c r="S257" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T257" t="inlineStr">
         <is>
@@ -19239,7 +19239,7 @@
         <v>101.59</v>
       </c>
       <c r="S258" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T258" t="inlineStr">
         <is>
@@ -19318,7 +19318,7 @@
         <v>62.55</v>
       </c>
       <c r="S259" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T259" t="inlineStr">
         <is>
@@ -19397,7 +19397,7 @@
         <v>45.85</v>
       </c>
       <c r="S260" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T260" t="inlineStr">
         <is>
@@ -19476,7 +19476,7 @@
         <v>78.44</v>
       </c>
       <c r="S261" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T261" t="inlineStr">
         <is>
@@ -19546,7 +19546,7 @@
         <v>5793</v>
       </c>
       <c r="P262" t="n">
-        <v>5365</v>
+        <v>5481</v>
       </c>
       <c r="Q262" t="n">
         <v>5793</v>
@@ -19555,7 +19555,7 @@
         <v>80.45999999999999</v>
       </c>
       <c r="S262" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T262" t="inlineStr">
         <is>
@@ -19634,7 +19634,7 @@
         <v>32.78</v>
       </c>
       <c r="S263" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T263" t="inlineStr">
         <is>
@@ -19702,7 +19702,7 @@
         <v>2164</v>
       </c>
       <c r="P264" t="n">
-        <v>1821</v>
+        <v>1838</v>
       </c>
       <c r="Q264" t="n">
         <v>3044</v>
@@ -19711,7 +19711,7 @@
         <v>50.73</v>
       </c>
       <c r="S264" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T264" t="inlineStr">
         <is>
@@ -19790,7 +19790,7 @@
         <v>89.41</v>
       </c>
       <c r="S265" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T265" t="inlineStr">
         <is>
@@ -19869,7 +19869,7 @@
         <v>69.42</v>
       </c>
       <c r="S266" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T266" t="inlineStr">
         <is>
@@ -19948,7 +19948,7 @@
         <v>67.26000000000001</v>
       </c>
       <c r="S267" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T267" t="inlineStr">
         <is>
@@ -20027,7 +20027,7 @@
         <v>78.86</v>
       </c>
       <c r="S268" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T268" t="inlineStr">
         <is>
@@ -20106,7 +20106,7 @@
         <v>74.29000000000001</v>
       </c>
       <c r="S269" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T269" t="inlineStr">
         <is>
@@ -20174,16 +20174,16 @@
         <v>2312</v>
       </c>
       <c r="P270" t="n">
-        <v>2389</v>
+        <v>2398</v>
       </c>
       <c r="Q270" t="n">
-        <v>2389</v>
+        <v>2398</v>
       </c>
       <c r="R270" t="n">
-        <v>59.72</v>
+        <v>59.95</v>
       </c>
       <c r="S270" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T270" t="inlineStr">
         <is>
@@ -20194,10 +20194,10 @@
         <v>1570.9</v>
       </c>
       <c r="V270" t="n">
-        <v>52.08</v>
+        <v>52.65</v>
       </c>
       <c r="W270" t="n">
-        <v>1.390131596624224</v>
+        <v>1.391393161806551</v>
       </c>
     </row>
     <row r="271">
@@ -20262,7 +20262,7 @@
         <v>20.2</v>
       </c>
       <c r="S271" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T271" t="inlineStr">
         <is>
@@ -20341,7 +20341,7 @@
         <v>73.09999999999999</v>
       </c>
       <c r="S272" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T272" t="inlineStr">
         <is>
@@ -20420,7 +20420,7 @@
         <v>18.32</v>
       </c>
       <c r="S273" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T273" t="inlineStr">
         <is>
@@ -20490,16 +20490,16 @@
         <v>703</v>
       </c>
       <c r="P274" t="n">
-        <v>718</v>
+        <v>743</v>
       </c>
       <c r="Q274" t="n">
-        <v>718</v>
+        <v>743</v>
       </c>
       <c r="R274" t="n">
-        <v>14.36</v>
+        <v>14.86</v>
       </c>
       <c r="S274" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T274" t="inlineStr">
         <is>
@@ -20510,10 +20510,10 @@
         <v>687.48</v>
       </c>
       <c r="V274" t="n">
-        <v>4.44</v>
+        <v>8.08</v>
       </c>
       <c r="W274" t="n">
-        <v>1.132266298383708</v>
+        <v>1.190193607630468</v>
       </c>
     </row>
     <row r="275">
@@ -20569,7 +20569,7 @@
         <v>4999</v>
       </c>
       <c r="P275" t="n">
-        <v>4904</v>
+        <v>5018</v>
       </c>
       <c r="Q275" t="n">
         <v>5324</v>
@@ -20578,7 +20578,7 @@
         <v>76.06</v>
       </c>
       <c r="S275" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T275" t="inlineStr">
         <is>
@@ -20648,7 +20648,7 @@
         <v>4413</v>
       </c>
       <c r="P276" t="n">
-        <v>4130</v>
+        <v>4307</v>
       </c>
       <c r="Q276" t="n">
         <v>4413</v>
@@ -20657,7 +20657,7 @@
         <v>63.04</v>
       </c>
       <c r="S276" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T276" t="inlineStr">
         <is>
@@ -20725,7 +20725,7 @@
         <v>4586</v>
       </c>
       <c r="P277" t="n">
-        <v>4804</v>
+        <v>5097</v>
       </c>
       <c r="Q277" t="n">
         <v>8427</v>
@@ -20734,7 +20734,7 @@
         <v>70.23</v>
       </c>
       <c r="S277" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T277" t="inlineStr">
         <is>
@@ -20811,7 +20811,7 @@
         <v>38.24</v>
       </c>
       <c r="S278" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T278" t="inlineStr">
         <is>
@@ -20888,7 +20888,7 @@
         <v>22.37</v>
       </c>
       <c r="S279" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T279" t="inlineStr">
         <is>
@@ -20958,16 +20958,16 @@
         <v>4863</v>
       </c>
       <c r="P280" t="n">
-        <v>4551</v>
+        <v>5083</v>
       </c>
       <c r="Q280" t="n">
-        <v>4974</v>
+        <v>5083</v>
       </c>
       <c r="R280" t="n">
-        <v>41.45</v>
+        <v>42.36</v>
       </c>
       <c r="S280" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T280" t="inlineStr">
         <is>
@@ -20978,7 +20978,7 @@
         <v>5157.95</v>
       </c>
       <c r="V280" t="n">
-        <v>-3.57</v>
+        <v>-1.45</v>
       </c>
       <c r="W280" t="inlineStr"/>
     </row>
@@ -21020,7 +21020,7 @@
       <c r="Q281" t="inlineStr"/>
       <c r="R281" t="inlineStr"/>
       <c r="S281" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T281" t="inlineStr">
         <is>
@@ -21093,7 +21093,7 @@
         <v>75.59999999999999</v>
       </c>
       <c r="S282" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T282" t="inlineStr">
         <is>
@@ -21172,7 +21172,7 @@
         <v>42.2</v>
       </c>
       <c r="S283" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T283" t="inlineStr">
         <is>
@@ -21249,7 +21249,7 @@
         <v>81.67</v>
       </c>
       <c r="S284" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T284" t="inlineStr">
         <is>
@@ -21326,7 +21326,7 @@
         <v>79.63</v>
       </c>
       <c r="S285" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T285" t="inlineStr">
         <is>
@@ -21396,7 +21396,7 @@
         <v>4412</v>
       </c>
       <c r="P286" t="n">
-        <v>4135</v>
+        <v>4256</v>
       </c>
       <c r="Q286" t="n">
         <v>4502</v>
@@ -21405,7 +21405,7 @@
         <v>78.48</v>
       </c>
       <c r="S286" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T286" t="inlineStr">
         <is>
@@ -21473,7 +21473,7 @@
         <v>3273</v>
       </c>
       <c r="P287" t="n">
-        <v>2450</v>
+        <v>2569</v>
       </c>
       <c r="Q287" t="n">
         <v>4359</v>
@@ -21482,7 +21482,7 @@
         <v>75.98999999999999</v>
       </c>
       <c r="S287" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T287" t="inlineStr">
         <is>
@@ -21559,7 +21559,7 @@
         <v>83</v>
       </c>
       <c r="S288" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T288" t="inlineStr">
         <is>
@@ -21629,7 +21629,7 @@
         <v>8309</v>
       </c>
       <c r="P289" t="n">
-        <v>6389</v>
+        <v>6683</v>
       </c>
       <c r="Q289" t="n">
         <v>9318</v>
@@ -21638,7 +21638,7 @@
         <v>97.45999999999999</v>
       </c>
       <c r="S289" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T289" t="inlineStr">
         <is>
@@ -21717,7 +21717,7 @@
         <v>64.3</v>
       </c>
       <c r="S290" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T290" t="inlineStr">
         <is>
@@ -21772,7 +21772,7 @@
       <c r="Q291" t="inlineStr"/>
       <c r="R291" t="inlineStr"/>
       <c r="S291" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T291" t="inlineStr">
         <is>
@@ -21821,7 +21821,7 @@
       <c r="Q292" t="inlineStr"/>
       <c r="R292" t="inlineStr"/>
       <c r="S292" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T292" t="inlineStr">
         <is>
@@ -21894,7 +21894,7 @@
         <v>241.2</v>
       </c>
       <c r="S293" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T293" t="inlineStr">
         <is>
@@ -21967,7 +21967,7 @@
         <v>28.62</v>
       </c>
       <c r="S294" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T294" t="inlineStr">
         <is>
@@ -22040,7 +22040,7 @@
         <v>62.1</v>
       </c>
       <c r="S295" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T295" t="inlineStr">
         <is>
@@ -22113,7 +22113,7 @@
         <v>74.97</v>
       </c>
       <c r="S296" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T296" t="inlineStr">
         <is>
@@ -22192,7 +22192,7 @@
         <v>43.7</v>
       </c>
       <c r="S297" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T297" t="inlineStr">
         <is>
@@ -22265,7 +22265,7 @@
         <v>34.7</v>
       </c>
       <c r="S298" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T298" t="inlineStr">
         <is>
@@ -22344,7 +22344,7 @@
         <v>24.77</v>
       </c>
       <c r="S299" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T299" t="inlineStr">
         <is>
@@ -22421,7 +22421,7 @@
         <v>64.65000000000001</v>
       </c>
       <c r="S300" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T300" t="inlineStr">
         <is>
@@ -22498,7 +22498,7 @@
         <v>58.54</v>
       </c>
       <c r="S301" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T301" t="inlineStr">
         <is>
@@ -22568,7 +22568,7 @@
         <v>4617</v>
       </c>
       <c r="P302" t="n">
-        <v>4514</v>
+        <v>4602</v>
       </c>
       <c r="Q302" t="n">
         <v>4617</v>
@@ -22577,7 +22577,7 @@
         <v>65.95999999999999</v>
       </c>
       <c r="S302" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T302" t="inlineStr">
         <is>
@@ -22656,7 +22656,7 @@
         <v>47.6</v>
       </c>
       <c r="S303" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T303" t="inlineStr">
         <is>
@@ -22735,7 +22735,7 @@
         <v>51.04</v>
       </c>
       <c r="S304" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T304" t="inlineStr">
         <is>
@@ -22814,7 +22814,7 @@
         <v>50.87</v>
       </c>
       <c r="S305" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T305" t="inlineStr">
         <is>
@@ -22891,7 +22891,7 @@
         <v>96.43000000000001</v>
       </c>
       <c r="S306" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T306" t="inlineStr">
         <is>
@@ -22970,7 +22970,7 @@
         <v>6.48</v>
       </c>
       <c r="S307" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T307" t="inlineStr">
         <is>
@@ -23047,7 +23047,7 @@
         <v>53.94</v>
       </c>
       <c r="S308" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T308" t="inlineStr">
         <is>
@@ -23124,7 +23124,7 @@
         <v>19.48</v>
       </c>
       <c r="S309" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T309" t="inlineStr">
         <is>
@@ -23201,7 +23201,7 @@
         <v>57.54</v>
       </c>
       <c r="S310" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T310" t="inlineStr">
         <is>
@@ -23280,7 +23280,7 @@
         <v>61.4</v>
       </c>
       <c r="S311" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T311" t="inlineStr">
         <is>
@@ -23359,7 +23359,7 @@
         <v>63.72</v>
       </c>
       <c r="S312" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T312" t="inlineStr">
         <is>
@@ -23436,7 +23436,7 @@
         <v>38.43</v>
       </c>
       <c r="S313" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T313" t="inlineStr">
         <is>
@@ -23513,7 +23513,7 @@
         <v>51.45</v>
       </c>
       <c r="S314" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T314" t="inlineStr">
         <is>
@@ -23590,7 +23590,7 @@
         <v>43.55</v>
       </c>
       <c r="S315" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T315" t="inlineStr">
         <is>
@@ -23669,7 +23669,7 @@
         <v>55.61</v>
       </c>
       <c r="S316" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T316" t="inlineStr">
         <is>
@@ -23748,7 +23748,7 @@
         <v>64.56</v>
       </c>
       <c r="S317" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T317" t="inlineStr">
         <is>
@@ -23827,7 +23827,7 @@
         <v>70.09</v>
       </c>
       <c r="S318" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T318" t="inlineStr">
         <is>
@@ -23906,7 +23906,7 @@
         <v>60.19</v>
       </c>
       <c r="S319" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T319" t="inlineStr">
         <is>
@@ -23961,7 +23961,7 @@
       <c r="Q320" t="inlineStr"/>
       <c r="R320" t="inlineStr"/>
       <c r="S320" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T320" t="inlineStr">
         <is>
@@ -24012,7 +24012,7 @@
       <c r="Q321" t="inlineStr"/>
       <c r="R321" t="inlineStr"/>
       <c r="S321" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T321" t="inlineStr">
         <is>
@@ -24087,7 +24087,7 @@
         <v>9</v>
       </c>
       <c r="S322" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T322" t="inlineStr">
         <is>
@@ -24140,7 +24140,7 @@
       <c r="Q323" t="inlineStr"/>
       <c r="R323" t="inlineStr"/>
       <c r="S323" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T323" t="inlineStr">
         <is>
@@ -24191,7 +24191,7 @@
       <c r="Q324" t="inlineStr"/>
       <c r="R324" t="inlineStr"/>
       <c r="S324" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T324" t="inlineStr">
         <is>
@@ -24264,7 +24264,7 @@
         <v>66.5</v>
       </c>
       <c r="S325" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T325" t="inlineStr">
         <is>
@@ -24319,7 +24319,7 @@
       <c r="Q326" t="inlineStr"/>
       <c r="R326" t="inlineStr"/>
       <c r="S326" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T326" t="inlineStr">
         <is>
@@ -24368,7 +24368,7 @@
       <c r="Q327" t="inlineStr"/>
       <c r="R327" t="inlineStr"/>
       <c r="S327" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T327" t="inlineStr">
         <is>
@@ -24443,7 +24443,7 @@
         <v>11.69</v>
       </c>
       <c r="S328" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T328" t="inlineStr">
         <is>
@@ -24520,7 +24520,7 @@
         <v>96.7</v>
       </c>
       <c r="S329" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T329" t="inlineStr">
         <is>
@@ -24599,7 +24599,7 @@
         <v>68.95999999999999</v>
       </c>
       <c r="S330" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T330" t="inlineStr">
         <is>
@@ -24678,7 +24678,7 @@
         <v>6.4</v>
       </c>
       <c r="S331" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T331" t="inlineStr">
         <is>
@@ -24731,7 +24731,7 @@
       <c r="Q332" t="inlineStr"/>
       <c r="R332" t="inlineStr"/>
       <c r="S332" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T332" t="inlineStr">
         <is>
@@ -24804,7 +24804,7 @@
         <v>109.58</v>
       </c>
       <c r="S333" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T333" t="inlineStr">
         <is>
@@ -24883,7 +24883,7 @@
         <v>89.25</v>
       </c>
       <c r="S334" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T334" t="inlineStr">
         <is>
@@ -24962,7 +24962,7 @@
         <v>119.64</v>
       </c>
       <c r="S335" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T335" t="inlineStr">
         <is>
@@ -25041,7 +25041,7 @@
         <v>48.79</v>
       </c>
       <c r="S336" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T336" t="inlineStr">
         <is>
@@ -25118,7 +25118,7 @@
         <v>44.26</v>
       </c>
       <c r="S337" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T337" t="inlineStr">
         <is>
@@ -25188,16 +25188,16 @@
         <v>2975</v>
       </c>
       <c r="P338" t="n">
-        <v>3078</v>
+        <v>3127</v>
       </c>
       <c r="Q338" t="n">
-        <v>3078</v>
+        <v>3127</v>
       </c>
       <c r="R338" t="n">
-        <v>43.97</v>
+        <v>44.67</v>
       </c>
       <c r="S338" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T338" t="inlineStr">
         <is>
@@ -25208,7 +25208,7 @@
         <v>3225.87</v>
       </c>
       <c r="V338" t="n">
-        <v>-4.58</v>
+        <v>-3.06</v>
       </c>
       <c r="W338" t="inlineStr"/>
     </row>
@@ -25274,7 +25274,7 @@
         <v>85.95999999999999</v>
       </c>
       <c r="S339" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T339" t="inlineStr">
         <is>
@@ -25353,7 +25353,7 @@
         <v>72.18000000000001</v>
       </c>
       <c r="S340" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T340" t="inlineStr">
         <is>
@@ -25432,7 +25432,7 @@
         <v>25.52</v>
       </c>
       <c r="S341" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T341" t="inlineStr">
         <is>
@@ -25509,7 +25509,7 @@
         <v>41.14</v>
       </c>
       <c r="S342" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T342" t="inlineStr">
         <is>
@@ -25586,7 +25586,7 @@
         <v>51.45</v>
       </c>
       <c r="S343" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T343" t="inlineStr">
         <is>
@@ -25665,7 +25665,7 @@
         <v>6.83</v>
       </c>
       <c r="S344" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T344" t="inlineStr">
         <is>
@@ -25742,7 +25742,7 @@
         <v>44.19</v>
       </c>
       <c r="S345" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T345" t="inlineStr">
         <is>
@@ -25821,7 +25821,7 @@
         <v>37.22</v>
       </c>
       <c r="S346" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T346" t="inlineStr">
         <is>
@@ -25874,7 +25874,7 @@
       <c r="Q347" t="inlineStr"/>
       <c r="R347" t="inlineStr"/>
       <c r="S347" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T347" t="inlineStr">
         <is>
@@ -25947,7 +25947,7 @@
         <v>47.5</v>
       </c>
       <c r="S348" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T348" t="inlineStr">
         <is>
@@ -26000,7 +26000,7 @@
       <c r="Q349" t="inlineStr"/>
       <c r="R349" t="inlineStr"/>
       <c r="S349" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T349" t="inlineStr">
         <is>
@@ -26073,7 +26073,7 @@
         <v>32.79</v>
       </c>
       <c r="S350" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T350" t="inlineStr">
         <is>
@@ -26128,7 +26128,7 @@
       <c r="Q351" t="inlineStr"/>
       <c r="R351" t="inlineStr"/>
       <c r="S351" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T351" t="inlineStr">
         <is>
@@ -26201,7 +26201,7 @@
         <v>90.66</v>
       </c>
       <c r="S352" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T352" t="inlineStr">
         <is>
@@ -26280,7 +26280,7 @@
         <v>52.53</v>
       </c>
       <c r="S353" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T353" t="inlineStr">
         <is>
@@ -26357,7 +26357,7 @@
         <v>67.11</v>
       </c>
       <c r="S354" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T354" t="inlineStr">
         <is>
@@ -26434,7 +26434,7 @@
         <v>27.66</v>
       </c>
       <c r="S355" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T355" t="inlineStr">
         <is>
@@ -26513,7 +26513,7 @@
         <v>40.23</v>
       </c>
       <c r="S356" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T356" t="inlineStr">
         <is>
@@ -26592,7 +26592,7 @@
         <v>57.23</v>
       </c>
       <c r="S357" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T357" t="inlineStr">
         <is>
@@ -26671,7 +26671,7 @@
         <v>20.96</v>
       </c>
       <c r="S358" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T358" t="inlineStr">
         <is>
@@ -26748,7 +26748,7 @@
         <v>54.84</v>
       </c>
       <c r="S359" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T359" t="inlineStr">
         <is>
@@ -26825,7 +26825,7 @@
         <v>29.78</v>
       </c>
       <c r="S360" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T360" t="inlineStr">
         <is>
@@ -26902,7 +26902,7 @@
         <v>59.5</v>
       </c>
       <c r="S361" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T361" t="inlineStr">
         <is>
@@ -26970,16 +26970,16 @@
         <v>4348</v>
       </c>
       <c r="P362" t="n">
-        <v>4496</v>
+        <v>4644</v>
       </c>
       <c r="Q362" t="n">
-        <v>4496</v>
+        <v>4644</v>
       </c>
       <c r="R362" t="n">
-        <v>44.96</v>
+        <v>46.44</v>
       </c>
       <c r="S362" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T362" t="inlineStr">
         <is>
@@ -26990,7 +26990,7 @@
         <v>5715.61</v>
       </c>
       <c r="V362" t="n">
-        <v>-21.34</v>
+        <v>-18.75</v>
       </c>
       <c r="W362" t="inlineStr"/>
     </row>
@@ -27047,16 +27047,16 @@
         <v>5726</v>
       </c>
       <c r="P363" t="n">
-        <v>6590</v>
+        <v>6043</v>
       </c>
       <c r="Q363" t="n">
-        <v>6590</v>
+        <v>6043</v>
       </c>
       <c r="R363" t="n">
-        <v>65.90000000000001</v>
+        <v>60.43</v>
       </c>
       <c r="S363" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T363" t="inlineStr">
         <is>
@@ -27067,7 +27067,7 @@
         <v>6881.72</v>
       </c>
       <c r="V363" t="n">
-        <v>-4.24</v>
+        <v>-12.19</v>
       </c>
       <c r="W363" t="inlineStr"/>
     </row>
@@ -27133,7 +27133,7 @@
         <v>22.23</v>
       </c>
       <c r="S364" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T364" t="inlineStr">
         <is>
@@ -27210,7 +27210,7 @@
         <v>80.91</v>
       </c>
       <c r="S365" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T365" t="inlineStr">
         <is>
@@ -27289,7 +27289,7 @@
         <v>93.45</v>
       </c>
       <c r="S366" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T366" t="inlineStr">
         <is>
@@ -27368,7 +27368,7 @@
         <v>26.44</v>
       </c>
       <c r="S367" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T367" t="inlineStr">
         <is>
@@ -27445,7 +27445,7 @@
         <v>78.02</v>
       </c>
       <c r="S368" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T368" t="inlineStr">
         <is>
@@ -27524,7 +27524,7 @@
         <v>64.93000000000001</v>
       </c>
       <c r="S369" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T369" t="inlineStr">
         <is>
@@ -27603,7 +27603,7 @@
         <v>71.02</v>
       </c>
       <c r="S370" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T370" t="inlineStr">
         <is>
@@ -27682,7 +27682,7 @@
         <v>60.37</v>
       </c>
       <c r="S371" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T371" t="inlineStr">
         <is>
@@ -27759,7 +27759,7 @@
         <v>58.84</v>
       </c>
       <c r="S372" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T372" t="inlineStr">
         <is>
@@ -27838,7 +27838,7 @@
         <v>79.70999999999999</v>
       </c>
       <c r="S373" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T373" t="inlineStr">
         <is>
@@ -27917,7 +27917,7 @@
         <v>72.97</v>
       </c>
       <c r="S374" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T374" t="inlineStr">
         <is>
@@ -27994,7 +27994,7 @@
         <v>67.77</v>
       </c>
       <c r="S375" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T375" t="inlineStr">
         <is>
@@ -28073,7 +28073,7 @@
         <v>53.1</v>
       </c>
       <c r="S376" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T376" t="inlineStr">
         <is>
@@ -28143,16 +28143,16 @@
         <v>3531</v>
       </c>
       <c r="P377" t="n">
-        <v>5489</v>
+        <v>5346</v>
       </c>
       <c r="Q377" t="n">
-        <v>5489</v>
+        <v>5346</v>
       </c>
       <c r="R377" t="n">
-        <v>54.89</v>
+        <v>53.46</v>
       </c>
       <c r="S377" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T377" t="inlineStr">
         <is>
@@ -28163,10 +28163,10 @@
         <v>4606.28</v>
       </c>
       <c r="V377" t="n">
-        <v>19.16</v>
+        <v>16.06</v>
       </c>
       <c r="W377" t="n">
-        <v>1.278987476666969</v>
+        <v>1.260314100124435</v>
       </c>
     </row>
     <row r="378">
@@ -28231,7 +28231,7 @@
         <v>40.25</v>
       </c>
       <c r="S378" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T378" t="inlineStr">
         <is>
@@ -28310,7 +28310,7 @@
         <v>43.67</v>
       </c>
       <c r="S379" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T379" t="inlineStr">
         <is>
@@ -28387,7 +28387,7 @@
         <v>53.52</v>
       </c>
       <c r="S380" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T380" t="inlineStr">
         <is>
@@ -28466,7 +28466,7 @@
         <v>58.98</v>
       </c>
       <c r="S381" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T381" t="inlineStr">
         <is>
@@ -28543,7 +28543,7 @@
         <v>49.25</v>
       </c>
       <c r="S382" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T382" t="inlineStr">
         <is>
@@ -28620,7 +28620,7 @@
         <v>35.43</v>
       </c>
       <c r="S383" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T383" t="inlineStr">
         <is>
@@ -28699,7 +28699,7 @@
         <v>30.64</v>
       </c>
       <c r="S384" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T384" t="inlineStr">
         <is>
@@ -28776,7 +28776,7 @@
         <v>39.4</v>
       </c>
       <c r="S385" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T385" t="inlineStr">
         <is>
@@ -28855,7 +28855,7 @@
         <v>78.03</v>
       </c>
       <c r="S386" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T386" t="inlineStr">
         <is>
@@ -28932,7 +28932,7 @@
         <v>45.83</v>
       </c>
       <c r="S387" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T387" t="inlineStr">
         <is>
@@ -29011,7 +29011,7 @@
         <v>49.09</v>
       </c>
       <c r="S388" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T388" t="inlineStr">
         <is>
@@ -29079,7 +29079,7 @@
         <v>4569</v>
       </c>
       <c r="P389" t="n">
-        <v>4075</v>
+        <v>4132</v>
       </c>
       <c r="Q389" t="n">
         <v>4569</v>
@@ -29088,7 +29088,7 @@
         <v>63.72</v>
       </c>
       <c r="S389" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T389" t="inlineStr">
         <is>
@@ -29165,7 +29165,7 @@
         <v>37.9</v>
       </c>
       <c r="S390" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T390" t="inlineStr">
         <is>
@@ -29229,7 +29229,7 @@
         <v>2537</v>
       </c>
       <c r="P391" t="n">
-        <v>1643</v>
+        <v>2442</v>
       </c>
       <c r="Q391" t="n">
         <v>2537</v>
@@ -29238,7 +29238,7 @@
         <v>42.46</v>
       </c>
       <c r="S391" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T391" t="inlineStr">
         <is>
@@ -29315,7 +29315,7 @@
         <v>74.03</v>
       </c>
       <c r="S392" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T392" t="inlineStr">
         <is>
@@ -29392,7 +29392,7 @@
         <v>28.86</v>
       </c>
       <c r="S393" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T393" t="inlineStr">
         <is>
@@ -29469,7 +29469,7 @@
         <v>11.33</v>
       </c>
       <c r="S394" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T394" t="inlineStr">
         <is>
@@ -29539,16 +29539,16 @@
         <v>2904</v>
       </c>
       <c r="P395" t="n">
-        <v>3536</v>
+        <v>3214</v>
       </c>
       <c r="Q395" t="n">
-        <v>3536</v>
+        <v>3214</v>
       </c>
       <c r="R395" t="n">
-        <v>35.36</v>
+        <v>32.14</v>
       </c>
       <c r="S395" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T395" t="inlineStr">
         <is>
@@ -29559,7 +29559,7 @@
         <v>3806.98</v>
       </c>
       <c r="V395" t="n">
-        <v>-7.12</v>
+        <v>-15.58</v>
       </c>
       <c r="W395" t="inlineStr"/>
     </row>
@@ -29625,7 +29625,7 @@
         <v>59.81</v>
       </c>
       <c r="S396" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T396" t="inlineStr">
         <is>
@@ -29704,7 +29704,7 @@
         <v>14.86</v>
       </c>
       <c r="S397" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T397" t="inlineStr">
         <is>
@@ -29783,7 +29783,7 @@
         <v>98.11</v>
       </c>
       <c r="S398" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T398" t="inlineStr">
         <is>
@@ -29862,7 +29862,7 @@
         <v>39.61</v>
       </c>
       <c r="S399" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T399" t="inlineStr">
         <is>
@@ -29941,7 +29941,7 @@
         <v>52.12</v>
       </c>
       <c r="S400" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T400" t="inlineStr">
         <is>
@@ -30018,7 +30018,7 @@
         <v>73.36</v>
       </c>
       <c r="S401" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T401" t="inlineStr">
         <is>
@@ -30095,7 +30095,7 @@
         <v>85.94</v>
       </c>
       <c r="S402" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T402" t="inlineStr">
         <is>
@@ -30174,7 +30174,7 @@
         <v>80.94</v>
       </c>
       <c r="S403" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T403" t="inlineStr">
         <is>
@@ -30251,7 +30251,7 @@
         <v>52.75</v>
       </c>
       <c r="S404" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T404" t="inlineStr">
         <is>
@@ -30304,7 +30304,7 @@
       <c r="Q405" t="inlineStr"/>
       <c r="R405" t="inlineStr"/>
       <c r="S405" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T405" t="inlineStr">
         <is>
@@ -30377,7 +30377,7 @@
         <v>36.11</v>
       </c>
       <c r="S406" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T406" t="inlineStr">
         <is>
@@ -30454,7 +30454,7 @@
         <v>90.12</v>
       </c>
       <c r="S407" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T407" t="inlineStr">
         <is>
@@ -30533,7 +30533,7 @@
         <v>44.68</v>
       </c>
       <c r="S408" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T408" t="inlineStr">
         <is>
@@ -30601,16 +30601,16 @@
         <v>875</v>
       </c>
       <c r="P409" t="n">
-        <v>1516</v>
+        <v>1504</v>
       </c>
       <c r="Q409" t="n">
-        <v>1516</v>
+        <v>1504</v>
       </c>
       <c r="R409" t="n">
-        <v>8.92</v>
+        <v>8.85</v>
       </c>
       <c r="S409" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T409" t="inlineStr">
         <is>
@@ -30621,11 +30621,9 @@
         <v>1512.99</v>
       </c>
       <c r="V409" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="W409" t="n">
-        <v>0.8744852722211679</v>
-      </c>
+        <v>-0.59</v>
+      </c>
+      <c r="W409" t="inlineStr"/>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -30689,7 +30687,7 @@
         <v>73.14</v>
       </c>
       <c r="S410" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T410" t="inlineStr">
         <is>
@@ -30766,7 +30764,7 @@
         <v>45.9</v>
       </c>
       <c r="S411" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T411" t="inlineStr">
         <is>
@@ -30843,7 +30841,7 @@
         <v>32.99</v>
       </c>
       <c r="S412" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T412" t="inlineStr">
         <is>
@@ -30920,7 +30918,7 @@
         <v>42.95</v>
       </c>
       <c r="S413" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T413" t="inlineStr">
         <is>
@@ -30999,7 +30997,7 @@
         <v>37.11</v>
       </c>
       <c r="S414" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T414" t="inlineStr">
         <is>
@@ -31076,7 +31074,7 @@
         <v>93.17</v>
       </c>
       <c r="S415" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T415" t="inlineStr">
         <is>
@@ -31155,7 +31153,7 @@
         <v>0</v>
       </c>
       <c r="S416" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T416" t="inlineStr">
         <is>
@@ -31232,7 +31230,7 @@
         <v>75.01000000000001</v>
       </c>
       <c r="S417" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T417" t="inlineStr">
         <is>
@@ -31309,7 +31307,7 @@
         <v>38.54</v>
       </c>
       <c r="S418" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T418" t="inlineStr">
         <is>
@@ -31386,7 +31384,7 @@
         <v>45.48</v>
       </c>
       <c r="S419" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T419" t="inlineStr">
         <is>
@@ -31463,7 +31461,7 @@
         <v>62.27</v>
       </c>
       <c r="S420" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T420" t="inlineStr">
         <is>
@@ -31542,7 +31540,7 @@
         <v>35.45</v>
       </c>
       <c r="S421" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T421" t="inlineStr">
         <is>
@@ -31619,7 +31617,7 @@
         <v>64.45999999999999</v>
       </c>
       <c r="S422" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T422" t="inlineStr">
         <is>
@@ -31696,7 +31694,7 @@
         <v>69.11</v>
       </c>
       <c r="S423" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T423" t="inlineStr">
         <is>
@@ -31775,7 +31773,7 @@
         <v>84.81999999999999</v>
       </c>
       <c r="S424" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T424" t="inlineStr">
         <is>
@@ -31854,7 +31852,7 @@
         <v>82.53</v>
       </c>
       <c r="S425" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T425" t="inlineStr">
         <is>
@@ -31933,7 +31931,7 @@
         <v>62.79</v>
       </c>
       <c r="S426" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T426" t="inlineStr">
         <is>
@@ -32010,7 +32008,7 @@
         <v>91.27</v>
       </c>
       <c r="S427" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T427" t="inlineStr">
         <is>
@@ -32089,7 +32087,7 @@
         <v>35.81</v>
       </c>
       <c r="S428" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T428" t="inlineStr">
         <is>
@@ -32168,7 +32166,7 @@
         <v>47.26</v>
       </c>
       <c r="S429" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T429" t="inlineStr">
         <is>
@@ -32247,7 +32245,7 @@
         <v>46.39</v>
       </c>
       <c r="S430" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T430" t="inlineStr">
         <is>
@@ -32324,7 +32322,7 @@
         <v>58.69</v>
       </c>
       <c r="S431" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T431" t="inlineStr">
         <is>
@@ -32401,7 +32399,7 @@
         <v>54.2</v>
       </c>
       <c r="S432" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T432" t="inlineStr">
         <is>
@@ -32478,7 +32476,7 @@
         <v>56.19</v>
       </c>
       <c r="S433" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T433" t="inlineStr">
         <is>
@@ -32557,7 +32555,7 @@
         <v>49.2</v>
       </c>
       <c r="S434" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T434" t="inlineStr">
         <is>
@@ -32636,7 +32634,7 @@
         <v>48.76</v>
       </c>
       <c r="S435" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T435" t="inlineStr">
         <is>
@@ -32713,7 +32711,7 @@
         <v>48.45</v>
       </c>
       <c r="S436" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T436" t="inlineStr">
         <is>
@@ -32790,7 +32788,7 @@
         <v>43.96</v>
       </c>
       <c r="S437" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T437" t="inlineStr">
         <is>
@@ -32869,7 +32867,7 @@
         <v>80.65000000000001</v>
       </c>
       <c r="S438" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T438" t="inlineStr">
         <is>
@@ -32948,7 +32946,7 @@
         <v>26.62</v>
       </c>
       <c r="S439" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T439" t="inlineStr">
         <is>
@@ -33025,7 +33023,7 @@
         <v>70.72</v>
       </c>
       <c r="S440" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T440" t="inlineStr">
         <is>
@@ -33102,7 +33100,7 @@
         <v>63.3</v>
       </c>
       <c r="S441" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T441" t="inlineStr">
         <is>
@@ -33181,7 +33179,7 @@
         <v>27.75</v>
       </c>
       <c r="S442" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T442" t="inlineStr">
         <is>
@@ -33260,7 +33258,7 @@
         <v>20.53</v>
       </c>
       <c r="S443" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T443" t="inlineStr">
         <is>
@@ -33337,7 +33335,7 @@
         <v>31.63</v>
       </c>
       <c r="S444" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T444" t="inlineStr">
         <is>
@@ -33414,7 +33412,7 @@
         <v>1.96</v>
       </c>
       <c r="S445" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T445" t="inlineStr">
         <is>
@@ -33491,7 +33489,7 @@
         <v>71.98999999999999</v>
       </c>
       <c r="S446" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T446" t="inlineStr">
         <is>
@@ -33568,7 +33566,7 @@
         <v>64.19</v>
       </c>
       <c r="S447" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T447" t="inlineStr">
         <is>
@@ -33645,7 +33643,7 @@
         <v>31.08</v>
       </c>
       <c r="S448" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T448" t="inlineStr">
         <is>
@@ -33724,7 +33722,7 @@
         <v>30.87</v>
       </c>
       <c r="S449" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T449" t="inlineStr">
         <is>
@@ -33794,16 +33792,16 @@
         <v>4704</v>
       </c>
       <c r="P450" t="n">
-        <v>4876</v>
+        <v>5077</v>
       </c>
       <c r="Q450" t="n">
-        <v>4876</v>
+        <v>5077</v>
       </c>
       <c r="R450" t="n">
-        <v>48.57</v>
+        <v>50.57</v>
       </c>
       <c r="S450" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T450" t="inlineStr">
         <is>
@@ -33814,7 +33812,7 @@
         <v>5969.77</v>
       </c>
       <c r="V450" t="n">
-        <v>-18.32</v>
+        <v>-14.95</v>
       </c>
       <c r="W450" t="inlineStr"/>
     </row>
@@ -33880,7 +33878,7 @@
         <v>92.89</v>
       </c>
       <c r="S451" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T451" t="inlineStr">
         <is>
@@ -33950,16 +33948,16 @@
         <v>4114</v>
       </c>
       <c r="P452" t="n">
-        <v>4027</v>
+        <v>5106</v>
       </c>
       <c r="Q452" t="n">
-        <v>4486</v>
+        <v>5106</v>
       </c>
       <c r="R452" t="n">
-        <v>44.86</v>
+        <v>51.06</v>
       </c>
       <c r="S452" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T452" t="inlineStr">
         <is>
@@ -33970,10 +33968,10 @@
         <v>4416.41</v>
       </c>
       <c r="V452" t="n">
-        <v>1.58</v>
+        <v>15.61</v>
       </c>
       <c r="W452" t="n">
-        <v>1.038854576294528</v>
+        <v>1.257332790719738</v>
       </c>
     </row>
     <row r="453">
@@ -34038,7 +34036,7 @@
         <v>77.15000000000001</v>
       </c>
       <c r="S453" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T453" t="inlineStr">
         <is>
@@ -34117,7 +34115,7 @@
         <v>87.08</v>
       </c>
       <c r="S454" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T454" t="inlineStr">
         <is>
@@ -34194,7 +34192,7 @@
         <v>43.67</v>
       </c>
       <c r="S455" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T455" t="inlineStr">
         <is>
@@ -34271,7 +34269,7 @@
         <v>77.44</v>
       </c>
       <c r="S456" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T456" t="inlineStr">
         <is>
@@ -34339,16 +34337,16 @@
         <v>6391</v>
       </c>
       <c r="P457" t="n">
-        <v>6249</v>
+        <v>7740</v>
       </c>
       <c r="Q457" t="n">
-        <v>6391</v>
+        <v>7740</v>
       </c>
       <c r="R457" t="n">
-        <v>63.91</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="S457" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T457" t="inlineStr">
         <is>
@@ -34359,7 +34357,7 @@
         <v>9919.860000000001</v>
       </c>
       <c r="V457" t="n">
-        <v>-35.57</v>
+        <v>-21.97</v>
       </c>
       <c r="W457" t="inlineStr"/>
     </row>
@@ -34425,7 +34423,7 @@
         <v>37.98</v>
       </c>
       <c r="S458" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T458" t="inlineStr">
         <is>
@@ -34502,7 +34500,7 @@
         <v>32.75</v>
       </c>
       <c r="S459" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T459" t="inlineStr">
         <is>
@@ -34579,7 +34577,7 @@
         <v>53.34</v>
       </c>
       <c r="S460" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T460" t="inlineStr">
         <is>
@@ -34658,7 +34656,7 @@
         <v>0</v>
       </c>
       <c r="S461" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T461" t="inlineStr">
         <is>
@@ -34735,7 +34733,7 @@
         <v>76.09</v>
       </c>
       <c r="S462" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T462" t="inlineStr">
         <is>
@@ -34805,16 +34803,16 @@
         <v>5133</v>
       </c>
       <c r="P463" t="n">
-        <v>5197</v>
+        <v>5293</v>
       </c>
       <c r="Q463" t="n">
-        <v>5197</v>
+        <v>5293</v>
       </c>
       <c r="R463" t="n">
-        <v>51.97</v>
+        <v>52.93</v>
       </c>
       <c r="S463" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T463" t="inlineStr">
         <is>
@@ -34825,7 +34823,7 @@
         <v>5369.08</v>
       </c>
       <c r="V463" t="n">
-        <v>-3.21</v>
+        <v>-1.42</v>
       </c>
       <c r="W463" t="inlineStr"/>
     </row>
@@ -34891,7 +34889,7 @@
         <v>29.98</v>
       </c>
       <c r="S464" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T464" t="inlineStr">
         <is>
@@ -34959,16 +34957,16 @@
         <v>525</v>
       </c>
       <c r="P465" t="n">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="Q465" t="n">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="R465" t="n">
-        <v>28.8</v>
+        <v>28.9</v>
       </c>
       <c r="S465" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T465" t="inlineStr">
         <is>
@@ -34979,7 +34977,7 @@
         <v>620.76</v>
       </c>
       <c r="V465" t="n">
-        <v>-7.21</v>
+        <v>-6.89</v>
       </c>
       <c r="W465" t="inlineStr"/>
     </row>
@@ -35045,7 +35043,7 @@
         <v>61.26</v>
       </c>
       <c r="S466" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T466" t="inlineStr">
         <is>
@@ -35113,16 +35111,16 @@
         <v>4868</v>
       </c>
       <c r="P467" t="n">
-        <v>4848</v>
+        <v>4894</v>
       </c>
       <c r="Q467" t="n">
-        <v>4868</v>
+        <v>4894</v>
       </c>
       <c r="R467" t="n">
-        <v>67.89</v>
+        <v>68.25</v>
       </c>
       <c r="S467" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T467" t="inlineStr">
         <is>
@@ -35133,7 +35131,7 @@
         <v>6223.23</v>
       </c>
       <c r="V467" t="n">
-        <v>-21.78</v>
+        <v>-21.36</v>
       </c>
       <c r="W467" t="inlineStr"/>
     </row>
@@ -35199,7 +35197,7 @@
         <v>69.64</v>
       </c>
       <c r="S468" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T468" t="inlineStr">
         <is>
@@ -35278,7 +35276,7 @@
         <v>78.83</v>
       </c>
       <c r="S469" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T469" t="inlineStr">
         <is>
@@ -35355,7 +35353,7 @@
         <v>86.27</v>
       </c>
       <c r="S470" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T470" t="inlineStr">
         <is>
@@ -35432,7 +35430,7 @@
         <v>74.13</v>
       </c>
       <c r="S471" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T471" t="inlineStr">
         <is>
@@ -35509,7 +35507,7 @@
         <v>42.79</v>
       </c>
       <c r="S472" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T472" t="inlineStr">
         <is>
@@ -35586,7 +35584,7 @@
         <v>73.84999999999999</v>
       </c>
       <c r="S473" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T473" t="inlineStr">
         <is>
@@ -35665,7 +35663,7 @@
         <v>70.69</v>
       </c>
       <c r="S474" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T474" t="inlineStr">
         <is>
@@ -35742,7 +35740,7 @@
         <v>61.32</v>
       </c>
       <c r="S475" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T475" t="inlineStr">
         <is>
@@ -35819,7 +35817,7 @@
         <v>76.45999999999999</v>
       </c>
       <c r="S476" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T476" t="inlineStr">
         <is>
@@ -35896,7 +35894,7 @@
         <v>44.52</v>
       </c>
       <c r="S477" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T477" t="inlineStr">
         <is>
@@ -35975,7 +35973,7 @@
         <v>30.08</v>
       </c>
       <c r="S478" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T478" t="inlineStr">
         <is>
@@ -36052,7 +36050,7 @@
         <v>89.40000000000001</v>
       </c>
       <c r="S479" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T479" t="inlineStr">
         <is>
@@ -36131,7 +36129,7 @@
         <v>71.79000000000001</v>
       </c>
       <c r="S480" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T480" t="inlineStr">
         <is>
@@ -36210,7 +36208,7 @@
         <v>10.82</v>
       </c>
       <c r="S481" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T481" t="inlineStr">
         <is>
@@ -36287,7 +36285,7 @@
         <v>87.76000000000001</v>
       </c>
       <c r="S482" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T482" t="inlineStr">
         <is>
@@ -36366,7 +36364,7 @@
         <v>89.75</v>
       </c>
       <c r="S483" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T483" t="inlineStr">
         <is>
@@ -36445,7 +36443,7 @@
         <v>50.52</v>
       </c>
       <c r="S484" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T484" t="inlineStr">
         <is>
@@ -36522,7 +36520,7 @@
         <v>38.41</v>
       </c>
       <c r="S485" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T485" t="inlineStr">
         <is>
@@ -36599,7 +36597,7 @@
         <v>78.08</v>
       </c>
       <c r="S486" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T486" t="inlineStr">
         <is>
@@ -36678,7 +36676,7 @@
         <v>22.72</v>
       </c>
       <c r="S487" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T487" t="inlineStr">
         <is>
@@ -36755,7 +36753,7 @@
         <v>29.41</v>
       </c>
       <c r="S488" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T488" t="inlineStr">
         <is>
@@ -36832,7 +36830,7 @@
         <v>51.04</v>
       </c>
       <c r="S489" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T489" t="inlineStr">
         <is>
@@ -36915,7 +36913,7 @@
         <v>40.37</v>
       </c>
       <c r="S490" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T490" t="inlineStr">
         <is>
@@ -36992,7 +36990,7 @@
         <v>40.08</v>
       </c>
       <c r="S491" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T491" t="inlineStr">
         <is>
@@ -37069,7 +37067,7 @@
         <v>52.69</v>
       </c>
       <c r="S492" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T492" t="inlineStr">
         <is>
@@ -37139,16 +37137,16 @@
         <v>9169</v>
       </c>
       <c r="P493" t="n">
-        <v>9210</v>
+        <v>9270</v>
       </c>
       <c r="Q493" t="n">
-        <v>9210</v>
+        <v>9270</v>
       </c>
       <c r="R493" t="n">
-        <v>70.84999999999999</v>
+        <v>71.31</v>
       </c>
       <c r="S493" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T493" t="inlineStr">
         <is>
@@ -37159,10 +37157,10 @@
         <v>8950.9</v>
       </c>
       <c r="V493" t="n">
-        <v>2.89</v>
+        <v>3.57</v>
       </c>
       <c r="W493" t="n">
-        <v>1.092466563299462</v>
+        <v>1.111874281222708</v>
       </c>
     </row>
     <row r="494">
@@ -37227,7 +37225,7 @@
         <v>44.36</v>
       </c>
       <c r="S494" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T494" t="inlineStr">
         <is>
@@ -37304,7 +37302,7 @@
         <v>51.76</v>
       </c>
       <c r="S495" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T495" t="inlineStr">
         <is>
@@ -37381,7 +37379,7 @@
         <v>47.09</v>
       </c>
       <c r="S496" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T496" t="inlineStr">
         <is>
@@ -37460,7 +37458,7 @@
         <v>41.12</v>
       </c>
       <c r="S497" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T497" t="inlineStr">
         <is>
@@ -37537,7 +37535,7 @@
         <v>57.66</v>
       </c>
       <c r="S498" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T498" t="inlineStr">
         <is>
@@ -37616,7 +37614,7 @@
         <v>52.9</v>
       </c>
       <c r="S499" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T499" t="inlineStr">
         <is>
@@ -37693,7 +37691,7 @@
         <v>44.09</v>
       </c>
       <c r="S500" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T500" t="inlineStr">
         <is>
@@ -37770,7 +37768,7 @@
         <v>41.87</v>
       </c>
       <c r="S501" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T501" t="inlineStr">
         <is>
@@ -37847,7 +37845,7 @@
         <v>81.84</v>
       </c>
       <c r="S502" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T502" t="inlineStr">
         <is>
@@ -37926,7 +37924,7 @@
         <v>39.72</v>
       </c>
       <c r="S503" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T503" t="inlineStr">
         <is>
@@ -38005,7 +38003,7 @@
         <v>52.29</v>
       </c>
       <c r="S504" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T504" t="inlineStr">
         <is>
@@ -38084,7 +38082,7 @@
         <v>75.37</v>
       </c>
       <c r="S505" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T505" t="inlineStr">
         <is>
@@ -38161,7 +38159,7 @@
         <v>56.7</v>
       </c>
       <c r="S506" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T506" t="inlineStr">
         <is>
@@ -38238,7 +38236,7 @@
         <v>72.55</v>
       </c>
       <c r="S507" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T507" t="inlineStr">
         <is>
@@ -38317,7 +38315,7 @@
         <v>39.38</v>
       </c>
       <c r="S508" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T508" t="inlineStr">
         <is>
@@ -38394,7 +38392,7 @@
         <v>26.75</v>
       </c>
       <c r="S509" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T509" t="inlineStr">
         <is>
@@ -38471,7 +38469,7 @@
         <v>33.36</v>
       </c>
       <c r="S510" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T510" t="inlineStr">
         <is>
@@ -38539,7 +38537,7 @@
         <v>7115</v>
       </c>
       <c r="P511" t="n">
-        <v>7306</v>
+        <v>7358</v>
       </c>
       <c r="Q511" t="n">
         <v>8169</v>
@@ -38548,7 +38546,7 @@
         <v>81.69</v>
       </c>
       <c r="S511" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T511" t="inlineStr">
         <is>
@@ -38625,7 +38623,7 @@
         <v>44.63</v>
       </c>
       <c r="S512" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T512" t="inlineStr">
         <is>
@@ -38702,7 +38700,7 @@
         <v>58.63</v>
       </c>
       <c r="S513" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T513" t="inlineStr">
         <is>
@@ -38779,7 +38777,7 @@
         <v>39.58</v>
       </c>
       <c r="S514" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T514" t="inlineStr">
         <is>
@@ -38856,7 +38854,7 @@
         <v>76.65000000000001</v>
       </c>
       <c r="S515" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T515" t="inlineStr">
         <is>
@@ -38933,7 +38931,7 @@
         <v>63.35</v>
       </c>
       <c r="S516" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T516" t="inlineStr">
         <is>
@@ -39012,7 +39010,7 @@
         <v>0</v>
       </c>
       <c r="S517" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T517" t="inlineStr">
         <is>
@@ -39089,7 +39087,7 @@
         <v>91.55</v>
       </c>
       <c r="S518" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T518" t="inlineStr">
         <is>
@@ -39159,7 +39157,7 @@
         <v>5093</v>
       </c>
       <c r="P519" t="n">
-        <v>4820</v>
+        <v>4880</v>
       </c>
       <c r="Q519" t="n">
         <v>5093</v>
@@ -39168,7 +39166,7 @@
         <v>50.93</v>
       </c>
       <c r="S519" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T519" t="inlineStr">
         <is>
@@ -39245,7 +39243,7 @@
         <v>40.99</v>
       </c>
       <c r="S520" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T520" t="inlineStr">
         <is>
@@ -39322,7 +39320,7 @@
         <v>47.12</v>
       </c>
       <c r="S521" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T521" t="inlineStr">
         <is>
@@ -39401,7 +39399,7 @@
         <v>1.09</v>
       </c>
       <c r="S522" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T522" t="inlineStr">
         <is>
@@ -39480,7 +39478,7 @@
         <v>74.87</v>
       </c>
       <c r="S523" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T523" t="inlineStr">
         <is>
@@ -39557,7 +39555,7 @@
         <v>43.3</v>
       </c>
       <c r="S524" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T524" t="inlineStr">
         <is>
@@ -39625,7 +39623,7 @@
         <v>6020</v>
       </c>
       <c r="P525" t="n">
-        <v>5877</v>
+        <v>5940</v>
       </c>
       <c r="Q525" t="n">
         <v>6020</v>
@@ -39634,7 +39632,7 @@
         <v>60.2</v>
       </c>
       <c r="S525" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T525" t="inlineStr">
         <is>
@@ -39711,7 +39709,7 @@
         <v>35.96</v>
       </c>
       <c r="S526" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T526" t="inlineStr">
         <is>
@@ -39788,7 +39786,7 @@
         <v>18.88</v>
       </c>
       <c r="S527" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T527" t="inlineStr">
         <is>
@@ -39865,7 +39863,7 @@
         <v>26.81</v>
       </c>
       <c r="S528" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T528" t="inlineStr">
         <is>
@@ -39944,7 +39942,7 @@
         <v>62.27</v>
       </c>
       <c r="S529" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T529" t="inlineStr">
         <is>
@@ -40021,7 +40019,7 @@
         <v>48.05</v>
       </c>
       <c r="S530" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T530" t="inlineStr">
         <is>
@@ -40098,7 +40096,7 @@
         <v>0</v>
       </c>
       <c r="S531" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T531" t="inlineStr">
         <is>
@@ -40162,7 +40160,7 @@
         <v>550</v>
       </c>
       <c r="P532" t="n">
-        <v>524</v>
+        <v>565</v>
       </c>
       <c r="Q532" t="n">
         <v>1035</v>
@@ -40171,7 +40169,7 @@
         <v>25.87</v>
       </c>
       <c r="S532" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T532" t="inlineStr">
         <is>
@@ -40248,7 +40246,7 @@
         <v>127.22</v>
       </c>
       <c r="S533" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T533" t="inlineStr">
         <is>
@@ -40325,7 +40323,7 @@
         <v>87.43000000000001</v>
       </c>
       <c r="S534" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T534" t="inlineStr">
         <is>
@@ -40402,7 +40400,7 @@
         <v>71.90000000000001</v>
       </c>
       <c r="S535" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T535" t="inlineStr">
         <is>
@@ -40470,7 +40468,7 @@
         <v>665</v>
       </c>
       <c r="P536" t="n">
-        <v>631</v>
+        <v>657</v>
       </c>
       <c r="Q536" t="n">
         <v>707</v>
@@ -40479,7 +40477,7 @@
         <v>35.35</v>
       </c>
       <c r="S536" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T536" t="inlineStr">
         <is>
@@ -40532,7 +40530,7 @@
       <c r="Q537" t="inlineStr"/>
       <c r="R537" t="inlineStr"/>
       <c r="S537" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T537" t="inlineStr">
         <is>
@@ -40605,7 +40603,7 @@
         <v>42.07</v>
       </c>
       <c r="S538" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T538" t="inlineStr">
         <is>
@@ -40682,7 +40680,7 @@
         <v>39.14</v>
       </c>
       <c r="S539" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T539" t="inlineStr">
         <is>
@@ -40761,7 +40759,7 @@
         <v>39.71</v>
       </c>
       <c r="S540" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T540" t="inlineStr">
         <is>
@@ -40829,16 +40827,16 @@
         <v>7893</v>
       </c>
       <c r="P541" t="n">
-        <v>7914</v>
+        <v>8199</v>
       </c>
       <c r="Q541" t="n">
-        <v>7914</v>
+        <v>8199</v>
       </c>
       <c r="R541" t="n">
-        <v>55.34</v>
+        <v>57.34</v>
       </c>
       <c r="S541" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T541" t="inlineStr">
         <is>
@@ -40849,10 +40847,10 @@
         <v>7519.46</v>
       </c>
       <c r="V541" t="n">
-        <v>5.25</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="W541" t="n">
-        <v>1.148188718185417</v>
+        <v>1.20138084314864</v>
       </c>
     </row>
     <row r="542">
@@ -40893,7 +40891,7 @@
       <c r="Q542" t="inlineStr"/>
       <c r="R542" t="inlineStr"/>
       <c r="S542" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T542" t="inlineStr">
         <is>
@@ -40968,7 +40966,7 @@
         <v>39.61</v>
       </c>
       <c r="S543" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T543" t="inlineStr">
         <is>
@@ -41021,7 +41019,7 @@
       <c r="Q544" t="inlineStr"/>
       <c r="R544" t="inlineStr"/>
       <c r="S544" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T544" t="inlineStr">
         <is>
@@ -41085,7 +41083,7 @@
         <v>435</v>
       </c>
       <c r="P545" t="n">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="Q545" t="n">
         <v>3755</v>
@@ -41094,7 +41092,7 @@
         <v>37.55</v>
       </c>
       <c r="S545" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T545" t="inlineStr">
         <is>
@@ -41171,7 +41169,7 @@
         <v>50.12</v>
       </c>
       <c r="S546" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T546" t="inlineStr">
         <is>
@@ -41239,7 +41237,7 @@
         <v>5417</v>
       </c>
       <c r="P547" t="n">
-        <v>2881</v>
+        <v>2691</v>
       </c>
       <c r="Q547" t="n">
         <v>6510</v>
@@ -41248,7 +41246,7 @@
         <v>65.09999999999999</v>
       </c>
       <c r="S547" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T547" t="inlineStr">
         <is>
@@ -41316,7 +41314,7 @@
         <v>6861</v>
       </c>
       <c r="P548" t="n">
-        <v>2560</v>
+        <v>2531</v>
       </c>
       <c r="Q548" t="n">
         <v>6861</v>
@@ -41325,7 +41323,7 @@
         <v>62.37</v>
       </c>
       <c r="S548" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T548" t="inlineStr">
         <is>
@@ -41404,7 +41402,7 @@
         <v>90.11</v>
       </c>
       <c r="S549" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T549" t="inlineStr">
         <is>
@@ -41483,7 +41481,7 @@
         <v>77.02</v>
       </c>
       <c r="S550" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T550" t="inlineStr">
         <is>
@@ -41562,7 +41560,7 @@
         <v>34.11</v>
       </c>
       <c r="S551" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T551" t="inlineStr">
         <is>
@@ -41632,7 +41630,7 @@
         <v>3810</v>
       </c>
       <c r="P552" t="n">
-        <v>925</v>
+        <v>791</v>
       </c>
       <c r="Q552" t="n">
         <v>3847</v>
@@ -41641,7 +41639,7 @@
         <v>34.97</v>
       </c>
       <c r="S552" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T552" t="inlineStr">
         <is>
@@ -41718,7 +41716,7 @@
         <v>36.74</v>
       </c>
       <c r="S553" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T553" t="inlineStr">
         <is>
@@ -41795,7 +41793,7 @@
         <v>1.04</v>
       </c>
       <c r="S554" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T554" t="inlineStr">
         <is>
@@ -41844,7 +41842,7 @@
       <c r="Q555" t="inlineStr"/>
       <c r="R555" t="inlineStr"/>
       <c r="S555" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T555" t="inlineStr">
         <is>
@@ -41917,7 +41915,7 @@
         <v>57.14</v>
       </c>
       <c r="S556" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T556" t="inlineStr">
         <is>
@@ -41981,7 +41979,7 @@
         <v>529</v>
       </c>
       <c r="P557" t="n">
-        <v>459</v>
+        <v>435</v>
       </c>
       <c r="Q557" t="n">
         <v>603</v>
@@ -41990,7 +41988,7 @@
         <v>6.03</v>
       </c>
       <c r="S557" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T557" t="inlineStr">
         <is>
@@ -42043,7 +42041,7 @@
       <c r="Q558" t="inlineStr"/>
       <c r="R558" t="inlineStr"/>
       <c r="S558" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T558" t="inlineStr">
         <is>
@@ -42094,7 +42092,7 @@
       <c r="Q559" t="inlineStr"/>
       <c r="R559" t="inlineStr"/>
       <c r="S559" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T559" t="inlineStr">
         <is>
@@ -42158,16 +42156,16 @@
         <v>1904</v>
       </c>
       <c r="P560" t="n">
-        <v>2157</v>
+        <v>2338</v>
       </c>
       <c r="Q560" t="n">
-        <v>2157</v>
+        <v>2338</v>
       </c>
       <c r="R560" t="n">
-        <v>10.78</v>
+        <v>11.69</v>
       </c>
       <c r="S560" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T560" t="inlineStr">
         <is>
@@ -42178,7 +42176,7 @@
         <v>4921.4</v>
       </c>
       <c r="V560" t="n">
-        <v>-56.17</v>
+        <v>-52.49</v>
       </c>
       <c r="W560" t="inlineStr"/>
     </row>
@@ -42244,7 +42242,7 @@
         <v>16.72</v>
       </c>
       <c r="S561" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T561" t="inlineStr">
         <is>
@@ -42312,7 +42310,7 @@
         <v>5382</v>
       </c>
       <c r="P562" t="n">
-        <v>4279</v>
+        <v>4754</v>
       </c>
       <c r="Q562" t="n">
         <v>5382</v>
@@ -42321,7 +42319,7 @@
         <v>21.53</v>
       </c>
       <c r="S562" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T562" t="inlineStr">
         <is>
@@ -42376,7 +42374,7 @@
       <c r="Q563" t="inlineStr"/>
       <c r="R563" t="inlineStr"/>
       <c r="S563" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T563" t="inlineStr">
         <is>
@@ -42449,7 +42447,7 @@
         <v>74.3</v>
       </c>
       <c r="S564" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T564" t="inlineStr">
         <is>
@@ -42519,7 +42517,7 @@
         <v>4348</v>
       </c>
       <c r="P565" t="n">
-        <v>3824</v>
+        <v>3938</v>
       </c>
       <c r="Q565" t="n">
         <v>4348</v>
@@ -42528,7 +42526,7 @@
         <v>76.28</v>
       </c>
       <c r="S565" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T565" t="inlineStr">
         <is>
@@ -42607,7 +42605,7 @@
         <v>64.39</v>
       </c>
       <c r="S566" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T566" t="inlineStr">
         <is>
@@ -42684,7 +42682,7 @@
         <v>57.77</v>
       </c>
       <c r="S567" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T567" t="inlineStr">
         <is>
@@ -42737,7 +42735,7 @@
       <c r="Q568" t="inlineStr"/>
       <c r="R568" t="inlineStr"/>
       <c r="S568" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T568" t="inlineStr">
         <is>
@@ -42810,7 +42808,7 @@
         <v>99.09999999999999</v>
       </c>
       <c r="S569" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T569" t="inlineStr">
         <is>
@@ -42889,7 +42887,7 @@
         <v>58.07</v>
       </c>
       <c r="S570" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T570" t="inlineStr">
         <is>
@@ -42968,7 +42966,7 @@
         <v>43.67</v>
       </c>
       <c r="S571" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T571" t="inlineStr">
         <is>
@@ -43047,7 +43045,7 @@
         <v>40.04</v>
       </c>
       <c r="S572" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T572" t="inlineStr">
         <is>
@@ -43126,7 +43124,7 @@
         <v>40.12</v>
       </c>
       <c r="S573" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T573" t="inlineStr">
         <is>
@@ -43203,7 +43201,7 @@
         <v>84.84</v>
       </c>
       <c r="S574" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T574" t="inlineStr">
         <is>
@@ -43282,7 +43280,7 @@
         <v>25.93</v>
       </c>
       <c r="S575" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T575" t="inlineStr">
         <is>
@@ -43361,7 +43359,7 @@
         <v>67.55</v>
       </c>
       <c r="S576" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T576" t="inlineStr">
         <is>
@@ -43438,7 +43436,7 @@
         <v>71.06</v>
       </c>
       <c r="S577" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T577" t="inlineStr">
         <is>
@@ -43508,7 +43506,7 @@
         <v>4100</v>
       </c>
       <c r="P578" t="n">
-        <v>4193</v>
+        <v>4423</v>
       </c>
       <c r="Q578" t="n">
         <v>5088</v>
@@ -43517,7 +43515,7 @@
         <v>42.4</v>
       </c>
       <c r="S578" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T578" t="inlineStr">
         <is>
@@ -43596,7 +43594,7 @@
         <v>53.36</v>
       </c>
       <c r="S579" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T579" t="inlineStr">
         <is>
@@ -43673,7 +43671,7 @@
         <v>49.62</v>
       </c>
       <c r="S580" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T580" t="inlineStr">
         <is>
@@ -43726,7 +43724,7 @@
       <c r="Q581" t="inlineStr"/>
       <c r="R581" t="inlineStr"/>
       <c r="S581" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T581" t="inlineStr">
         <is>
@@ -43799,7 +43797,7 @@
         <v>46.67</v>
       </c>
       <c r="S582" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T582" t="inlineStr">
         <is>
@@ -43876,7 +43874,7 @@
         <v>97.56</v>
       </c>
       <c r="S583" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T583" t="inlineStr">
         <is>
@@ -43955,7 +43953,7 @@
         <v>72.59</v>
       </c>
       <c r="S584" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T584" t="inlineStr">
         <is>
@@ -44032,7 +44030,7 @@
         <v>87.81999999999999</v>
       </c>
       <c r="S585" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T585" t="inlineStr">
         <is>
@@ -44111,7 +44109,7 @@
         <v>59.79</v>
       </c>
       <c r="S586" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T586" t="inlineStr">
         <is>
@@ -44188,7 +44186,7 @@
         <v>59.72</v>
       </c>
       <c r="S587" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T587" t="inlineStr">
         <is>
@@ -44265,7 +44263,7 @@
         <v>39.59</v>
       </c>
       <c r="S588" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T588" t="inlineStr">
         <is>
@@ -44333,16 +44331,16 @@
         <v>2992</v>
       </c>
       <c r="P589" t="n">
-        <v>3005</v>
+        <v>3230</v>
       </c>
       <c r="Q589" t="n">
-        <v>3204</v>
+        <v>3230</v>
       </c>
       <c r="R589" t="n">
-        <v>29.79</v>
+        <v>30.03</v>
       </c>
       <c r="S589" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T589" t="inlineStr">
         <is>
@@ -44353,7 +44351,7 @@
         <v>8109.57</v>
       </c>
       <c r="V589" t="n">
-        <v>-60.49</v>
+        <v>-60.17</v>
       </c>
       <c r="W589" t="inlineStr"/>
     </row>
@@ -44410,7 +44408,7 @@
         <v>2423</v>
       </c>
       <c r="P590" t="n">
-        <v>21</v>
+        <v>1213</v>
       </c>
       <c r="Q590" t="n">
         <v>3670</v>
@@ -44419,7 +44417,7 @@
         <v>36.7</v>
       </c>
       <c r="S590" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T590" t="inlineStr">
         <is>
@@ -44496,7 +44494,7 @@
         <v>93.7</v>
       </c>
       <c r="S591" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T591" t="inlineStr">
         <is>
@@ -44573,7 +44571,7 @@
         <v>15.24</v>
       </c>
       <c r="S592" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T592" t="inlineStr">
         <is>
@@ -44650,7 +44648,7 @@
         <v>34.74</v>
       </c>
       <c r="S593" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T593" t="inlineStr">
         <is>
@@ -44727,7 +44725,7 @@
         <v>62.45</v>
       </c>
       <c r="S594" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T594" t="inlineStr">
         <is>
@@ -44804,7 +44802,7 @@
         <v>3.98</v>
       </c>
       <c r="S595" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T595" t="inlineStr">
         <is>
@@ -44881,7 +44879,7 @@
         <v>67.06</v>
       </c>
       <c r="S596" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T596" t="inlineStr">
         <is>
@@ -44960,7 +44958,7 @@
         <v>67.54000000000001</v>
       </c>
       <c r="S597" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T597" t="inlineStr">
         <is>
@@ -45039,7 +45037,7 @@
         <v>29.57</v>
       </c>
       <c r="S598" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T598" t="inlineStr">
         <is>
@@ -45116,7 +45114,7 @@
         <v>64</v>
       </c>
       <c r="S599" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T599" t="inlineStr">
         <is>
@@ -45195,7 +45193,7 @@
         <v>83.68000000000001</v>
       </c>
       <c r="S600" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T600" t="inlineStr">
         <is>
@@ -45274,7 +45272,7 @@
         <v>64.51000000000001</v>
       </c>
       <c r="S601" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T601" t="inlineStr">
         <is>
@@ -45353,7 +45351,7 @@
         <v>68.38</v>
       </c>
       <c r="S602" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T602" t="inlineStr">
         <is>
@@ -45421,16 +45419,16 @@
         <v>5124</v>
       </c>
       <c r="P603" t="n">
-        <v>7860</v>
+        <v>7646</v>
       </c>
       <c r="Q603" t="n">
-        <v>7860</v>
+        <v>7646</v>
       </c>
       <c r="R603" t="n">
-        <v>78.59999999999999</v>
+        <v>76.45999999999999</v>
       </c>
       <c r="S603" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T603" t="inlineStr">
         <is>
@@ -45441,7 +45439,7 @@
         <v>8054.65</v>
       </c>
       <c r="V603" t="n">
-        <v>-2.42</v>
+        <v>-5.07</v>
       </c>
       <c r="W603" t="inlineStr"/>
     </row>
@@ -45507,7 +45505,7 @@
         <v>92.23999999999999</v>
       </c>
       <c r="S604" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T604" t="inlineStr">
         <is>
@@ -45586,7 +45584,7 @@
         <v>151.18</v>
       </c>
       <c r="S605" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T605" t="inlineStr">
         <is>
@@ -45665,7 +45663,7 @@
         <v>47.21</v>
       </c>
       <c r="S606" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T606" t="inlineStr">
         <is>
@@ -45742,7 +45740,7 @@
         <v>66.15000000000001</v>
       </c>
       <c r="S607" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T607" t="inlineStr">
         <is>
@@ -45821,7 +45819,7 @@
         <v>47.24</v>
       </c>
       <c r="S608" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T608" t="inlineStr">
         <is>
@@ -45900,7 +45898,7 @@
         <v>32.25</v>
       </c>
       <c r="S609" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T609" t="inlineStr">
         <is>
@@ -45970,16 +45968,16 @@
         <v>7934</v>
       </c>
       <c r="P610" t="n">
-        <v>7971</v>
+        <v>8200</v>
       </c>
       <c r="Q610" t="n">
-        <v>7971</v>
+        <v>8200</v>
       </c>
       <c r="R610" t="n">
-        <v>79.70999999999999</v>
+        <v>82</v>
       </c>
       <c r="S610" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T610" t="inlineStr">
         <is>
@@ -45990,9 +45988,11 @@
         <v>8181.73</v>
       </c>
       <c r="V610" t="n">
-        <v>-2.58</v>
-      </c>
-      <c r="W610" t="inlineStr"/>
+        <v>0.22</v>
+      </c>
+      <c r="W610" t="n">
+        <v>0.8814585405848675</v>
+      </c>
     </row>
     <row r="611">
       <c r="A611" t="inlineStr">
@@ -46056,7 +46056,7 @@
         <v>53.07</v>
       </c>
       <c r="S611" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T611" t="inlineStr">
         <is>
@@ -46124,16 +46124,16 @@
         <v>7250</v>
       </c>
       <c r="P612" t="n">
-        <v>7892</v>
+        <v>8964</v>
       </c>
       <c r="Q612" t="n">
-        <v>7892</v>
+        <v>8964</v>
       </c>
       <c r="R612" t="n">
-        <v>78.92</v>
+        <v>89.64</v>
       </c>
       <c r="S612" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T612" t="inlineStr">
         <is>
@@ -46144,9 +46144,11 @@
         <v>8735.27</v>
       </c>
       <c r="V612" t="n">
-        <v>-9.65</v>
-      </c>
-      <c r="W612" t="inlineStr"/>
+        <v>2.62</v>
+      </c>
+      <c r="W612" t="n">
+        <v>1.083573663695421</v>
+      </c>
     </row>
     <row r="613">
       <c r="A613" t="inlineStr">
@@ -46201,7 +46203,7 @@
         <v>3274</v>
       </c>
       <c r="P613" t="n">
-        <v>2480</v>
+        <v>2933</v>
       </c>
       <c r="Q613" t="n">
         <v>3274</v>
@@ -46210,7 +46212,7 @@
         <v>36.53</v>
       </c>
       <c r="S613" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T613" t="inlineStr">
         <is>
@@ -46287,7 +46289,7 @@
         <v>67.58</v>
       </c>
       <c r="S614" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T614" t="inlineStr">
         <is>
@@ -46364,7 +46366,7 @@
         <v>61.6</v>
       </c>
       <c r="S615" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T615" t="inlineStr">
         <is>
@@ -46441,7 +46443,7 @@
         <v>61.17</v>
       </c>
       <c r="S616" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T616" t="inlineStr">
         <is>
@@ -46518,7 +46520,7 @@
         <v>22.98</v>
       </c>
       <c r="S617" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T617" t="inlineStr">
         <is>
@@ -46595,7 +46597,7 @@
         <v>76.70999999999999</v>
       </c>
       <c r="S618" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T618" t="inlineStr">
         <is>
@@ -46674,7 +46676,7 @@
         <v>70.31</v>
       </c>
       <c r="S619" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T619" t="inlineStr">
         <is>
@@ -46753,7 +46755,7 @@
         <v>62.5</v>
       </c>
       <c r="S620" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T620" t="inlineStr">
         <is>
@@ -46830,7 +46832,7 @@
         <v>45.82</v>
       </c>
       <c r="S621" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T621" t="inlineStr">
         <is>
@@ -46883,7 +46885,7 @@
       <c r="Q622" t="inlineStr"/>
       <c r="R622" t="inlineStr"/>
       <c r="S622" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T622" t="inlineStr">
         <is>
@@ -46958,7 +46960,7 @@
         <v>56.39</v>
       </c>
       <c r="S623" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T623" t="inlineStr">
         <is>
@@ -47037,7 +47039,7 @@
         <v>24.2</v>
       </c>
       <c r="S624" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T624" t="inlineStr">
         <is>
@@ -47092,7 +47094,7 @@
       <c r="Q625" t="inlineStr"/>
       <c r="R625" t="inlineStr"/>
       <c r="S625" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T625" t="inlineStr">
         <is>
@@ -47167,7 +47169,7 @@
         <v>41.02</v>
       </c>
       <c r="S626" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T626" t="inlineStr">
         <is>
@@ -47231,7 +47233,7 @@
         <v>4097</v>
       </c>
       <c r="P627" t="n">
-        <v>3527</v>
+        <v>3993</v>
       </c>
       <c r="Q627" t="n">
         <v>5528</v>
@@ -47240,7 +47242,7 @@
         <v>92.51000000000001</v>
       </c>
       <c r="S627" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T627" t="inlineStr">
         <is>
@@ -47313,7 +47315,7 @@
         <v>41.16</v>
       </c>
       <c r="S628" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T628" t="inlineStr">
         <is>
@@ -47386,7 +47388,7 @@
         <v>55.8</v>
       </c>
       <c r="S629" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T629" t="inlineStr">
         <is>
@@ -47463,7 +47465,7 @@
         <v>55.53</v>
       </c>
       <c r="S630" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T630" t="inlineStr">
         <is>
@@ -47542,7 +47544,7 @@
         <v>66.77</v>
       </c>
       <c r="S631" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T631" t="inlineStr">
         <is>
@@ -47619,7 +47621,7 @@
         <v>49.87</v>
       </c>
       <c r="S632" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T632" t="inlineStr">
         <is>
@@ -47687,7 +47689,7 @@
         <v>1450</v>
       </c>
       <c r="P633" t="n">
-        <v>1353</v>
+        <v>1500</v>
       </c>
       <c r="Q633" t="n">
         <v>1722</v>
@@ -47696,7 +47698,7 @@
         <v>19.13</v>
       </c>
       <c r="S633" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T633" t="inlineStr">
         <is>
@@ -47775,7 +47777,7 @@
         <v>36.8</v>
       </c>
       <c r="S634" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T634" t="inlineStr">
         <is>
@@ -47852,7 +47854,7 @@
         <v>58.96</v>
       </c>
       <c r="S635" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T635" t="inlineStr">
         <is>
@@ -47929,7 +47931,7 @@
         <v>28.69</v>
       </c>
       <c r="S636" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T636" t="inlineStr">
         <is>
@@ -48008,7 +48010,7 @@
         <v>10.68</v>
       </c>
       <c r="S637" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T637" t="inlineStr">
         <is>
@@ -48085,7 +48087,7 @@
         <v>85.58</v>
       </c>
       <c r="S638" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T638" t="inlineStr">
         <is>
@@ -48164,7 +48166,7 @@
         <v>76.2</v>
       </c>
       <c r="S639" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T639" t="inlineStr">
         <is>
@@ -48243,7 +48245,7 @@
         <v>29.45</v>
       </c>
       <c r="S640" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T640" t="inlineStr">
         <is>
@@ -48313,7 +48315,7 @@
         <v>7248</v>
       </c>
       <c r="P641" t="n">
-        <v>4412</v>
+        <v>4823</v>
       </c>
       <c r="Q641" t="n">
         <v>9088</v>
@@ -48322,7 +48324,7 @@
         <v>95.05</v>
       </c>
       <c r="S641" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T641" t="inlineStr">
         <is>
@@ -48401,7 +48403,7 @@
         <v>85.69</v>
       </c>
       <c r="S642" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T642" t="inlineStr">
         <is>
@@ -48480,7 +48482,7 @@
         <v>44.15</v>
       </c>
       <c r="S643" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T643" t="inlineStr">
         <is>
@@ -48559,7 +48561,7 @@
         <v>49.8</v>
       </c>
       <c r="S644" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T644" t="inlineStr">
         <is>
@@ -48636,7 +48638,7 @@
         <v>48.85</v>
       </c>
       <c r="S645" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T645" t="inlineStr">
         <is>
@@ -48713,7 +48715,7 @@
         <v>34.93</v>
       </c>
       <c r="S646" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T646" t="inlineStr">
         <is>
@@ -48790,7 +48792,7 @@
         <v>46.87</v>
       </c>
       <c r="S647" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T647" t="inlineStr">
         <is>
@@ -48869,7 +48871,7 @@
         <v>19.09</v>
       </c>
       <c r="S648" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T648" t="inlineStr">
         <is>
@@ -48946,7 +48948,7 @@
         <v>54.33</v>
       </c>
       <c r="S649" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T649" t="inlineStr">
         <is>
@@ -49025,7 +49027,7 @@
         <v>65.40000000000001</v>
       </c>
       <c r="S650" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T650" t="inlineStr">
         <is>
@@ -49104,7 +49106,7 @@
         <v>34.89</v>
       </c>
       <c r="S651" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T651" t="inlineStr">
         <is>
@@ -49177,7 +49179,7 @@
         <v>56.83</v>
       </c>
       <c r="S652" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T652" t="inlineStr">
         <is>
@@ -49254,7 +49256,7 @@
         <v>29.74</v>
       </c>
       <c r="S653" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T653" t="inlineStr">
         <is>
@@ -49331,7 +49333,7 @@
         <v>61.72</v>
       </c>
       <c r="S654" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T654" t="inlineStr">
         <is>
@@ -49410,7 +49412,7 @@
         <v>48.83</v>
       </c>
       <c r="S655" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T655" t="inlineStr">
         <is>
@@ -49487,7 +49489,7 @@
         <v>36.73</v>
       </c>
       <c r="S656" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T656" t="inlineStr">
         <is>
@@ -49555,7 +49557,7 @@
         <v>2005</v>
       </c>
       <c r="P657" t="n">
-        <v>2003</v>
+        <v>2146</v>
       </c>
       <c r="Q657" t="n">
         <v>2377</v>
@@ -49564,7 +49566,7 @@
         <v>33.96</v>
       </c>
       <c r="S657" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T657" t="inlineStr">
         <is>
@@ -49641,7 +49643,7 @@
         <v>74.06</v>
       </c>
       <c r="S658" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T658" t="inlineStr">
         <is>
@@ -49690,7 +49692,7 @@
       <c r="Q659" t="inlineStr"/>
       <c r="R659" t="inlineStr"/>
       <c r="S659" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T659" t="inlineStr">
         <is>
@@ -49765,7 +49767,7 @@
         <v>79.13</v>
       </c>
       <c r="S660" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T660" t="inlineStr">
         <is>
@@ -49844,7 +49846,7 @@
         <v>92.45</v>
       </c>
       <c r="S661" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T661" t="inlineStr">
         <is>
@@ -49914,7 +49916,7 @@
         <v>5275</v>
       </c>
       <c r="P662" t="n">
-        <v>3434</v>
+        <v>3212</v>
       </c>
       <c r="Q662" t="n">
         <v>9224</v>
@@ -49923,7 +49925,7 @@
         <v>92.23999999999999</v>
       </c>
       <c r="S662" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T662" t="inlineStr">
         <is>
@@ -49987,7 +49989,7 @@
         <v>10585</v>
       </c>
       <c r="P663" t="n">
-        <v>6649</v>
+        <v>6978</v>
       </c>
       <c r="Q663" t="n">
         <v>10585</v>
@@ -49996,7 +49998,7 @@
         <v>105.85</v>
       </c>
       <c r="S663" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T663" t="inlineStr">
         <is>
@@ -50075,7 +50077,7 @@
         <v>111.93</v>
       </c>
       <c r="S664" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T664" t="inlineStr">
         <is>
@@ -50154,7 +50156,7 @@
         <v>8.59</v>
       </c>
       <c r="S665" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T665" t="inlineStr">
         <is>
@@ -50231,7 +50233,7 @@
         <v>85.81</v>
       </c>
       <c r="S666" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T666" t="inlineStr">
         <is>
@@ -50310,7 +50312,7 @@
         <v>92.91</v>
       </c>
       <c r="S667" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T667" t="inlineStr">
         <is>
@@ -50389,7 +50391,7 @@
         <v>94.81999999999999</v>
       </c>
       <c r="S668" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T668" t="inlineStr">
         <is>
@@ -50468,7 +50470,7 @@
         <v>69.70999999999999</v>
       </c>
       <c r="S669" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T669" t="inlineStr">
         <is>
@@ -50547,7 +50549,7 @@
         <v>10.57</v>
       </c>
       <c r="S670" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T670" t="inlineStr">
         <is>
@@ -50624,7 +50626,7 @@
         <v>92.61</v>
       </c>
       <c r="S671" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T671" t="inlineStr">
         <is>
@@ -50703,7 +50705,7 @@
         <v>79.34</v>
       </c>
       <c r="S672" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T672" t="inlineStr">
         <is>
@@ -50773,7 +50775,7 @@
         <v>8128</v>
       </c>
       <c r="P673" t="n">
-        <v>7073</v>
+        <v>7688</v>
       </c>
       <c r="Q673" t="n">
         <v>8128</v>
@@ -50782,7 +50784,7 @@
         <v>90.68000000000001</v>
       </c>
       <c r="S673" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T673" t="inlineStr">
         <is>
@@ -50861,7 +50863,7 @@
         <v>44.11</v>
       </c>
       <c r="S674" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T674" t="inlineStr">
         <is>
@@ -50931,7 +50933,7 @@
         <v>4216</v>
       </c>
       <c r="P675" t="n">
-        <v>2513</v>
+        <v>2632</v>
       </c>
       <c r="Q675" t="n">
         <v>5639</v>
@@ -50940,7 +50942,7 @@
         <v>78.64</v>
       </c>
       <c r="S675" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T675" t="inlineStr">
         <is>
@@ -51017,7 +51019,7 @@
         <v>25.82</v>
       </c>
       <c r="S676" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T676" t="inlineStr">
         <is>
@@ -51085,7 +51087,7 @@
         <v>4967</v>
       </c>
       <c r="P677" t="n">
-        <v>4421</v>
+        <v>4477</v>
       </c>
       <c r="Q677" t="n">
         <v>5957</v>
@@ -51094,7 +51096,7 @@
         <v>49.64</v>
       </c>
       <c r="S677" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T677" t="inlineStr">
         <is>
@@ -51167,7 +51169,7 @@
         <v>77.86</v>
       </c>
       <c r="S678" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T678" t="inlineStr">
         <is>
@@ -51246,7 +51248,7 @@
         <v>72.38</v>
       </c>
       <c r="S679" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T679" t="inlineStr">
         <is>
@@ -51325,7 +51327,7 @@
         <v>94.14</v>
       </c>
       <c r="S680" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T680" t="inlineStr">
         <is>
@@ -51404,7 +51406,7 @@
         <v>42.84</v>
       </c>
       <c r="S681" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T681" t="inlineStr">
         <is>
@@ -51481,7 +51483,7 @@
         <v>66.8</v>
       </c>
       <c r="S682" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T682" t="inlineStr">
         <is>
@@ -51560,7 +51562,7 @@
         <v>42.53</v>
       </c>
       <c r="S683" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T683" t="inlineStr">
         <is>
@@ -51639,7 +51641,7 @@
         <v>78.41</v>
       </c>
       <c r="S684" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T684" t="inlineStr">
         <is>
@@ -51716,7 +51718,7 @@
         <v>54.68</v>
       </c>
       <c r="S685" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T685" t="inlineStr">
         <is>
@@ -51793,7 +51795,7 @@
         <v>65.20999999999999</v>
       </c>
       <c r="S686" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T686" t="inlineStr">
         <is>
@@ -51863,7 +51865,7 @@
         <v>8124</v>
       </c>
       <c r="P687" t="n">
-        <v>0</v>
+        <v>901</v>
       </c>
       <c r="Q687" t="n">
         <v>13027</v>
@@ -51872,7 +51874,7 @@
         <v>81.42</v>
       </c>
       <c r="S687" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T687" t="inlineStr">
         <is>
@@ -51951,7 +51953,7 @@
         <v>56.07</v>
       </c>
       <c r="S688" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T688" t="inlineStr">
         <is>
@@ -52004,7 +52006,7 @@
       <c r="Q689" t="inlineStr"/>
       <c r="R689" t="inlineStr"/>
       <c r="S689" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T689" t="inlineStr">
         <is>
@@ -52053,7 +52055,7 @@
       <c r="Q690" t="inlineStr"/>
       <c r="R690" t="inlineStr"/>
       <c r="S690" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T690" t="inlineStr">
         <is>
@@ -52126,7 +52128,7 @@
         <v>8.949999999999999</v>
       </c>
       <c r="S691" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T691" t="inlineStr">
         <is>
@@ -52203,7 +52205,7 @@
         <v>51</v>
       </c>
       <c r="S692" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T692" t="inlineStr">
         <is>
@@ -52280,7 +52282,7 @@
         <v>8.65</v>
       </c>
       <c r="S693" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T693" t="inlineStr">
         <is>
@@ -52357,7 +52359,7 @@
         <v>50.79</v>
       </c>
       <c r="S694" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T694" t="inlineStr">
         <is>
@@ -52436,7 +52438,7 @@
         <v>78.69</v>
       </c>
       <c r="S695" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T695" t="inlineStr">
         <is>
@@ -52515,7 +52517,7 @@
         <v>92.51000000000001</v>
       </c>
       <c r="S696" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T696" t="inlineStr">
         <is>
@@ -52592,7 +52594,7 @@
         <v>91.09999999999999</v>
       </c>
       <c r="S697" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T697" t="inlineStr">
         <is>
@@ -52669,7 +52671,7 @@
         <v>79.7</v>
       </c>
       <c r="S698" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T698" t="inlineStr">
         <is>
@@ -52746,7 +52748,7 @@
         <v>85.40000000000001</v>
       </c>
       <c r="S699" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T699" t="inlineStr">
         <is>
@@ -52823,7 +52825,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="S700" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T700" t="inlineStr">
         <is>
@@ -52900,7 +52902,7 @@
         <v>68.45</v>
       </c>
       <c r="S701" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T701" t="inlineStr">
         <is>
@@ -52977,7 +52979,7 @@
         <v>68.13</v>
       </c>
       <c r="S702" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T702" t="inlineStr">
         <is>
@@ -53054,7 +53056,7 @@
         <v>50.14</v>
       </c>
       <c r="S703" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T703" t="inlineStr">
         <is>
@@ -53131,7 +53133,7 @@
         <v>6.9</v>
       </c>
       <c r="S704" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T704" t="inlineStr">
         <is>
@@ -53208,7 +53210,7 @@
         <v>42</v>
       </c>
       <c r="S705" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T705" t="inlineStr">
         <is>
@@ -53287,7 +53289,7 @@
         <v>12.25</v>
       </c>
       <c r="S706" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T706" t="inlineStr">
         <is>
@@ -53364,7 +53366,7 @@
         <v>6.83</v>
       </c>
       <c r="S707" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T707" t="inlineStr">
         <is>
@@ -53441,7 +53443,7 @@
         <v>37.96</v>
       </c>
       <c r="S708" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T708" t="inlineStr">
         <is>
@@ -53520,7 +53522,7 @@
         <v>16.48</v>
       </c>
       <c r="S709" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T709" t="inlineStr">
         <is>
@@ -53597,7 +53599,7 @@
         <v>44.42</v>
       </c>
       <c r="S710" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T710" t="inlineStr">
         <is>
@@ -53676,7 +53678,7 @@
         <v>77.22</v>
       </c>
       <c r="S711" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T711" t="inlineStr">
         <is>
@@ -53755,7 +53757,7 @@
         <v>30.39</v>
       </c>
       <c r="S712" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T712" t="inlineStr">
         <is>
@@ -53832,7 +53834,7 @@
         <v>7.07</v>
       </c>
       <c r="S713" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T713" t="inlineStr">
         <is>
@@ -53909,7 +53911,7 @@
         <v>41.16</v>
       </c>
       <c r="S714" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T714" t="inlineStr">
         <is>
@@ -53988,7 +53990,7 @@
         <v>44.51</v>
       </c>
       <c r="S715" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T715" t="inlineStr">
         <is>
@@ -54065,7 +54067,7 @@
         <v>73.19</v>
       </c>
       <c r="S716" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T716" t="inlineStr">
         <is>
@@ -54133,7 +54135,7 @@
         <v>9341</v>
       </c>
       <c r="P717" t="n">
-        <v>5246</v>
+        <v>7740</v>
       </c>
       <c r="Q717" t="n">
         <v>9341</v>
@@ -54142,7 +54144,7 @@
         <v>87.3</v>
       </c>
       <c r="S717" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T717" t="inlineStr">
         <is>
@@ -54219,7 +54221,7 @@
         <v>55.91</v>
       </c>
       <c r="S718" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T718" t="inlineStr">
         <is>
@@ -54298,7 +54300,7 @@
         <v>51.57</v>
       </c>
       <c r="S719" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T719" t="inlineStr">
         <is>
@@ -54377,7 +54379,7 @@
         <v>14.8</v>
       </c>
       <c r="S720" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T720" t="inlineStr">
         <is>
@@ -54454,7 +54456,7 @@
         <v>55.84</v>
       </c>
       <c r="S721" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T721" t="inlineStr">
         <is>
@@ -54533,7 +54535,7 @@
         <v>73.54000000000001</v>
       </c>
       <c r="S722" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T722" t="inlineStr">
         <is>
@@ -54610,7 +54612,7 @@
         <v>60.96</v>
       </c>
       <c r="S723" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T723" t="inlineStr">
         <is>
@@ -54687,7 +54689,7 @@
         <v>0</v>
       </c>
       <c r="S724" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T724" t="inlineStr">
         <is>
@@ -54764,7 +54766,7 @@
         <v>46.25</v>
       </c>
       <c r="S725" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T725" t="inlineStr">
         <is>
@@ -54841,7 +54843,7 @@
         <v>85.61</v>
       </c>
       <c r="S726" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T726" t="inlineStr">
         <is>
@@ -54918,7 +54920,7 @@
         <v>92.39</v>
       </c>
       <c r="S727" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T727" t="inlineStr">
         <is>
@@ -54997,7 +54999,7 @@
         <v>55.49</v>
       </c>
       <c r="S728" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T728" t="inlineStr">
         <is>
@@ -55074,7 +55076,7 @@
         <v>58.49</v>
       </c>
       <c r="S729" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T729" t="inlineStr">
         <is>
@@ -55151,7 +55153,7 @@
         <v>69.05</v>
       </c>
       <c r="S730" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T730" t="inlineStr">
         <is>
@@ -55230,7 +55232,7 @@
         <v>89.18000000000001</v>
       </c>
       <c r="S731" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T731" t="inlineStr">
         <is>
@@ -55309,7 +55311,7 @@
         <v>0</v>
       </c>
       <c r="S732" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T732" t="inlineStr">
         <is>
@@ -55384,7 +55386,7 @@
         <v>66.40000000000001</v>
       </c>
       <c r="S733" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T733" t="inlineStr">
         <is>
@@ -55461,7 +55463,7 @@
         <v>77.12</v>
       </c>
       <c r="S734" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T734" t="inlineStr">
         <is>
@@ -55529,7 +55531,7 @@
         <v>7052</v>
       </c>
       <c r="P735" t="n">
-        <v>4277</v>
+        <v>5351</v>
       </c>
       <c r="Q735" t="n">
         <v>7052</v>
@@ -55538,7 +55540,7 @@
         <v>70.25</v>
       </c>
       <c r="S735" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T735" t="inlineStr">
         <is>
@@ -55615,7 +55617,7 @@
         <v>73.23999999999999</v>
       </c>
       <c r="S736" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T736" t="inlineStr">
         <is>
@@ -55692,7 +55694,7 @@
         <v>94.12</v>
       </c>
       <c r="S737" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T737" t="inlineStr">
         <is>
@@ -55771,7 +55773,7 @@
         <v>76.28</v>
       </c>
       <c r="S738" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T738" t="inlineStr">
         <is>
@@ -55848,7 +55850,7 @@
         <v>75.48</v>
       </c>
       <c r="S739" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T739" t="inlineStr">
         <is>
@@ -55927,7 +55929,7 @@
         <v>67.38</v>
       </c>
       <c r="S740" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T740" t="inlineStr">
         <is>
@@ -56006,7 +56008,7 @@
         <v>58.21</v>
       </c>
       <c r="S741" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T741" t="inlineStr">
         <is>
@@ -56085,7 +56087,7 @@
         <v>28.85</v>
       </c>
       <c r="S742" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T742" t="inlineStr">
         <is>
@@ -56153,7 +56155,7 @@
         <v>8830</v>
       </c>
       <c r="P743" t="n">
-        <v>4692</v>
+        <v>6506</v>
       </c>
       <c r="Q743" t="n">
         <v>8830</v>
@@ -56162,7 +56164,7 @@
         <v>92.36</v>
       </c>
       <c r="S743" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T743" t="inlineStr">
         <is>
@@ -56232,7 +56234,7 @@
         <v>1267</v>
       </c>
       <c r="P744" t="n">
-        <v>1064</v>
+        <v>1122</v>
       </c>
       <c r="Q744" t="n">
         <v>1610</v>
@@ -56241,7 +56243,7 @@
         <v>13.42</v>
       </c>
       <c r="S744" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T744" t="inlineStr">
         <is>
@@ -56309,7 +56311,7 @@
         <v>6356</v>
       </c>
       <c r="P745" t="n">
-        <v>5058</v>
+        <v>7070</v>
       </c>
       <c r="Q745" t="n">
         <v>11079</v>
@@ -56318,7 +56320,7 @@
         <v>84.25</v>
       </c>
       <c r="S745" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T745" t="inlineStr">
         <is>
@@ -56395,7 +56397,7 @@
         <v>50.08</v>
       </c>
       <c r="S746" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T746" t="inlineStr">
         <is>
@@ -56472,7 +56474,7 @@
         <v>54.57</v>
       </c>
       <c r="S747" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T747" t="inlineStr">
         <is>
@@ -56540,7 +56542,7 @@
         <v>7046</v>
       </c>
       <c r="P748" t="n">
-        <v>5476</v>
+        <v>6620</v>
       </c>
       <c r="Q748" t="n">
         <v>7787</v>
@@ -56549,7 +56551,7 @@
         <v>70.79000000000001</v>
       </c>
       <c r="S748" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T748" t="inlineStr">
         <is>
@@ -56617,7 +56619,7 @@
         <v>2365</v>
       </c>
       <c r="P749" t="n">
-        <v>3116</v>
+        <v>2986</v>
       </c>
       <c r="Q749" t="n">
         <v>4293</v>
@@ -56626,7 +56628,7 @@
         <v>35.92</v>
       </c>
       <c r="S749" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T749" t="inlineStr">
         <is>
@@ -56699,7 +56701,7 @@
         <v>73.98</v>
       </c>
       <c r="S750" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T750" t="inlineStr">
         <is>
@@ -56769,7 +56771,7 @@
         <v>5858</v>
       </c>
       <c r="P751" t="n">
-        <v>3576</v>
+        <v>4085</v>
       </c>
       <c r="Q751" t="n">
         <v>5858</v>
@@ -56778,7 +56780,7 @@
         <v>58.58</v>
       </c>
       <c r="S751" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T751" t="inlineStr">
         <is>
@@ -56846,7 +56848,7 @@
         <v>5114</v>
       </c>
       <c r="P752" t="n">
-        <v>2228</v>
+        <v>2184</v>
       </c>
       <c r="Q752" t="n">
         <v>5114</v>
@@ -56855,7 +56857,7 @@
         <v>71.03</v>
       </c>
       <c r="S752" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T752" t="inlineStr">
         <is>
@@ -56928,7 +56930,7 @@
         <v>20.44</v>
       </c>
       <c r="S753" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T753" t="inlineStr">
         <is>
@@ -57001,7 +57003,7 @@
         <v>30.18</v>
       </c>
       <c r="S754" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T754" t="inlineStr">
         <is>
@@ -57080,7 +57082,7 @@
         <v>78.09999999999999</v>
       </c>
       <c r="S755" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T755" t="inlineStr">
         <is>
@@ -57148,16 +57150,16 @@
         <v>1934</v>
       </c>
       <c r="P756" t="n">
-        <v>3593</v>
+        <v>3412</v>
       </c>
       <c r="Q756" t="n">
-        <v>3593</v>
+        <v>3412</v>
       </c>
       <c r="R756" t="n">
-        <v>44.91</v>
+        <v>42.65</v>
       </c>
       <c r="S756" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T756" t="inlineStr">
         <is>
@@ -57168,10 +57170,10 @@
         <v>2448.7</v>
       </c>
       <c r="V756" t="n">
-        <v>46.73</v>
+        <v>39.34</v>
       </c>
       <c r="W756" t="n">
-        <v>1.377631237481955</v>
+        <v>1.358009671633811</v>
       </c>
     </row>
     <row r="757">
@@ -57236,7 +57238,7 @@
         <v>44.5</v>
       </c>
       <c r="S757" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T757" t="inlineStr">
         <is>
@@ -57289,7 +57291,7 @@
       <c r="Q758" t="inlineStr"/>
       <c r="R758" t="inlineStr"/>
       <c r="S758" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T758" t="inlineStr">
         <is>
@@ -57362,7 +57364,7 @@
         <v>22.36</v>
       </c>
       <c r="S759" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T759" t="inlineStr">
         <is>
@@ -57435,7 +57437,7 @@
         <v>91.66</v>
       </c>
       <c r="S760" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T760" t="inlineStr">
         <is>
@@ -57505,7 +57507,7 @@
         <v>5661</v>
       </c>
       <c r="P761" t="n">
-        <v>4109</v>
+        <v>4835</v>
       </c>
       <c r="Q761" t="n">
         <v>5661</v>
@@ -57514,7 +57516,7 @@
         <v>80.87</v>
       </c>
       <c r="S761" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T761" t="inlineStr">
         <is>
@@ -57593,7 +57595,7 @@
         <v>90.94</v>
       </c>
       <c r="S762" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T762" t="inlineStr">
         <is>
@@ -57672,7 +57674,7 @@
         <v>38.96</v>
       </c>
       <c r="S763" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T763" t="inlineStr">
         <is>
@@ -57751,7 +57753,7 @@
         <v>91.44</v>
       </c>
       <c r="S764" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T764" t="inlineStr">
         <is>
@@ -57821,16 +57823,16 @@
         <v>1268</v>
       </c>
       <c r="P765" t="n">
-        <v>1343</v>
+        <v>1604</v>
       </c>
       <c r="Q765" t="n">
-        <v>1343</v>
+        <v>1604</v>
       </c>
       <c r="R765" t="n">
-        <v>27.98</v>
+        <v>33.42</v>
       </c>
       <c r="S765" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T765" t="inlineStr">
         <is>
@@ -57841,7 +57843,7 @@
         <v>2605.49</v>
       </c>
       <c r="V765" t="n">
-        <v>-48.45</v>
+        <v>-38.44</v>
       </c>
       <c r="W765" t="inlineStr"/>
     </row>
@@ -57907,7 +57909,7 @@
         <v>79.34</v>
       </c>
       <c r="S766" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T766" t="inlineStr">
         <is>
@@ -57986,7 +57988,7 @@
         <v>30.49</v>
       </c>
       <c r="S767" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T767" t="inlineStr">
         <is>
@@ -58063,7 +58065,7 @@
         <v>75.7</v>
       </c>
       <c r="S768" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T768" t="inlineStr">
         <is>
@@ -58142,7 +58144,7 @@
         <v>16.58</v>
       </c>
       <c r="S769" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T769" t="inlineStr">
         <is>
@@ -58219,7 +58221,7 @@
         <v>43.87</v>
       </c>
       <c r="S770" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T770" t="inlineStr">
         <is>
@@ -58296,7 +58298,7 @@
         <v>35.92</v>
       </c>
       <c r="S771" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T771" t="inlineStr">
         <is>
@@ -58373,7 +58375,7 @@
         <v>28.25</v>
       </c>
       <c r="S772" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T772" t="inlineStr">
         <is>
@@ -58452,7 +58454,7 @@
         <v>32.36</v>
       </c>
       <c r="S773" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T773" t="inlineStr">
         <is>
@@ -58522,7 +58524,7 @@
         <v>5878</v>
       </c>
       <c r="P774" t="n">
-        <v>4901</v>
+        <v>4947</v>
       </c>
       <c r="Q774" t="n">
         <v>5878</v>
@@ -58531,7 +58533,7 @@
         <v>49.81</v>
       </c>
       <c r="S774" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T774" t="inlineStr">
         <is>
@@ -58608,7 +58610,7 @@
         <v>129.83</v>
       </c>
       <c r="S775" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T775" t="inlineStr">
         <is>
@@ -58687,7 +58689,7 @@
         <v>45.47</v>
       </c>
       <c r="S776" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T776" t="inlineStr">
         <is>
@@ -58740,7 +58742,7 @@
       <c r="Q777" t="inlineStr"/>
       <c r="R777" t="inlineStr"/>
       <c r="S777" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T777" t="inlineStr">
         <is>
@@ -58813,7 +58815,7 @@
         <v>158824.8</v>
       </c>
       <c r="S778" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T778" t="inlineStr">
         <is>
@@ -58892,7 +58894,7 @@
         <v>52.98</v>
       </c>
       <c r="S779" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T779" t="inlineStr">
         <is>
@@ -58941,7 +58943,7 @@
       <c r="Q780" t="inlineStr"/>
       <c r="R780" t="inlineStr"/>
       <c r="S780" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T780" t="inlineStr">
         <is>
@@ -58992,7 +58994,7 @@
       <c r="Q781" t="inlineStr"/>
       <c r="R781" t="inlineStr"/>
       <c r="S781" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T781" t="inlineStr">
         <is>
@@ -59058,16 +59060,16 @@
         <v>961</v>
       </c>
       <c r="P782" t="n">
-        <v>969</v>
+        <v>1217</v>
       </c>
       <c r="Q782" t="n">
-        <v>969</v>
+        <v>1217</v>
       </c>
       <c r="R782" t="n">
-        <v>13.84</v>
+        <v>17.39</v>
       </c>
       <c r="S782" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T782" t="inlineStr">
         <is>
@@ -59078,7 +59080,7 @@
         <v>3939.79</v>
       </c>
       <c r="V782" t="n">
-        <v>-75.40000000000001</v>
+        <v>-69.11</v>
       </c>
       <c r="W782" t="inlineStr"/>
     </row>
@@ -59144,7 +59146,7 @@
         <v>25.9</v>
       </c>
       <c r="S783" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T783" t="inlineStr">
         <is>
@@ -59223,7 +59225,7 @@
         <v>36.4</v>
       </c>
       <c r="S784" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T784" t="inlineStr">
         <is>
@@ -59302,7 +59304,7 @@
         <v>41.5</v>
       </c>
       <c r="S785" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T785" t="inlineStr">
         <is>
@@ -59381,7 +59383,7 @@
         <v>19.42</v>
       </c>
       <c r="S786" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T786" t="inlineStr">
         <is>
@@ -59449,16 +59451,16 @@
         <v>4422</v>
       </c>
       <c r="P787" t="n">
-        <v>4516</v>
+        <v>5739</v>
       </c>
       <c r="Q787" t="n">
-        <v>5679</v>
+        <v>5739</v>
       </c>
       <c r="R787" t="n">
-        <v>78.88</v>
+        <v>79.70999999999999</v>
       </c>
       <c r="S787" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T787" t="inlineStr">
         <is>
@@ -59469,10 +59471,10 @@
         <v>5571.35</v>
       </c>
       <c r="V787" t="n">
-        <v>1.93</v>
+        <v>3.01</v>
       </c>
       <c r="W787" t="n">
-        <v>1.056322285766675</v>
+        <v>1.096176636134711</v>
       </c>
     </row>
     <row r="788">
@@ -59528,7 +59530,7 @@
         <v>4507</v>
       </c>
       <c r="P788" t="n">
-        <v>4335</v>
+        <v>4506</v>
       </c>
       <c r="Q788" t="n">
         <v>4507</v>
@@ -59537,7 +59539,7 @@
         <v>64.39</v>
       </c>
       <c r="S788" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T788" t="inlineStr">
         <is>
@@ -59614,7 +59616,7 @@
         <v>4.04</v>
       </c>
       <c r="S789" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T789" t="inlineStr">
         <is>
@@ -59691,7 +59693,7 @@
         <v>57.14</v>
       </c>
       <c r="S790" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T790" t="inlineStr">
         <is>
@@ -59744,7 +59746,7 @@
       <c r="Q791" t="inlineStr"/>
       <c r="R791" t="inlineStr"/>
       <c r="S791" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T791" t="inlineStr">
         <is>
@@ -59795,7 +59797,7 @@
       <c r="Q792" t="inlineStr"/>
       <c r="R792" t="inlineStr"/>
       <c r="S792" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T792" t="inlineStr">
         <is>
@@ -59870,7 +59872,7 @@
         <v>52.93</v>
       </c>
       <c r="S793" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T793" t="inlineStr">
         <is>
@@ -59947,7 +59949,7 @@
         <v>71.84</v>
       </c>
       <c r="S794" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T794" t="inlineStr">
         <is>
@@ -60024,7 +60026,7 @@
         <v>15.89</v>
       </c>
       <c r="S795" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T795" t="inlineStr">
         <is>
@@ -60101,7 +60103,7 @@
         <v>28.12</v>
       </c>
       <c r="S796" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T796" t="inlineStr">
         <is>
@@ -60178,7 +60180,7 @@
         <v>35.26</v>
       </c>
       <c r="S797" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T797" t="inlineStr">
         <is>
@@ -60257,7 +60259,7 @@
         <v>54.36</v>
       </c>
       <c r="S798" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T798" t="inlineStr">
         <is>
@@ -60334,7 +60336,7 @@
         <v>40.57</v>
       </c>
       <c r="S799" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T799" t="inlineStr">
         <is>
@@ -60411,7 +60413,7 @@
         <v>6.54</v>
       </c>
       <c r="S800" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T800" t="inlineStr">
         <is>
@@ -60488,7 +60490,7 @@
         <v>71.68000000000001</v>
       </c>
       <c r="S801" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T801" t="inlineStr">
         <is>
@@ -60565,7 +60567,7 @@
         <v>88.14</v>
       </c>
       <c r="S802" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T802" t="inlineStr">
         <is>
@@ -60644,7 +60646,7 @@
         <v>59.54</v>
       </c>
       <c r="S803" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T803" t="inlineStr">
         <is>
@@ -60723,7 +60725,7 @@
         <v>66.66</v>
       </c>
       <c r="S804" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T804" t="inlineStr">
         <is>
@@ -60802,7 +60804,7 @@
         <v>49.63</v>
       </c>
       <c r="S805" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T805" t="inlineStr">
         <is>
@@ -60881,7 +60883,7 @@
         <v>53.29</v>
       </c>
       <c r="S806" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T806" t="inlineStr">
         <is>
@@ -60960,7 +60962,7 @@
         <v>49.28</v>
       </c>
       <c r="S807" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T807" t="inlineStr">
         <is>
@@ -61037,7 +61039,7 @@
         <v>71.5</v>
       </c>
       <c r="S808" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T808" t="inlineStr">
         <is>
@@ -61114,7 +61116,7 @@
         <v>32.5</v>
       </c>
       <c r="S809" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T809" t="inlineStr">
         <is>
@@ -61184,16 +61186,16 @@
         <v>1586</v>
       </c>
       <c r="P810" t="n">
-        <v>1602</v>
+        <v>1660</v>
       </c>
       <c r="Q810" t="n">
-        <v>1602</v>
+        <v>1660</v>
       </c>
       <c r="R810" t="n">
-        <v>80.09999999999999</v>
+        <v>83</v>
       </c>
       <c r="S810" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T810" t="inlineStr">
         <is>
@@ -61204,10 +61206,10 @@
         <v>1598.58</v>
       </c>
       <c r="V810" t="n">
-        <v>0.21</v>
+        <v>3.84</v>
       </c>
       <c r="W810" t="n">
-        <v>0.8780480334671743</v>
+        <v>1.118650107479548</v>
       </c>
     </row>
     <row r="811">
@@ -61272,7 +61274,7 @@
         <v>77.38</v>
       </c>
       <c r="S811" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T811" t="inlineStr">
         <is>
@@ -61349,7 +61351,7 @@
         <v>52.48</v>
       </c>
       <c r="S812" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T812" t="inlineStr">
         <is>
@@ -61402,7 +61404,7 @@
       <c r="Q813" t="inlineStr"/>
       <c r="R813" t="inlineStr"/>
       <c r="S813" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T813" t="inlineStr">
         <is>
@@ -61468,7 +61470,7 @@
         <v>128</v>
       </c>
       <c r="P814" t="n">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="Q814" t="n">
         <v>4173</v>
@@ -61477,7 +61479,7 @@
         <v>59.61</v>
       </c>
       <c r="S814" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T814" t="inlineStr">
         <is>
@@ -61554,7 +61556,7 @@
         <v>45.92</v>
       </c>
       <c r="S815" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T815" t="inlineStr">
         <is>
@@ -61607,7 +61609,7 @@
       <c r="Q816" t="inlineStr"/>
       <c r="R816" t="inlineStr"/>
       <c r="S816" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T816" t="inlineStr">
         <is>
@@ -61680,7 +61682,7 @@
         <v>99.81999999999999</v>
       </c>
       <c r="S817" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T817" t="inlineStr">
         <is>
@@ -61735,7 +61737,7 @@
       <c r="Q818" t="inlineStr"/>
       <c r="R818" t="inlineStr"/>
       <c r="S818" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T818" t="inlineStr">
         <is>
@@ -61786,7 +61788,7 @@
       <c r="Q819" t="inlineStr"/>
       <c r="R819" t="inlineStr"/>
       <c r="S819" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T819" t="inlineStr">
         <is>
@@ -61861,7 +61863,7 @@
         <v>77.84999999999999</v>
       </c>
       <c r="S820" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T820" t="inlineStr">
         <is>
@@ -61914,7 +61916,7 @@
       <c r="Q821" t="inlineStr"/>
       <c r="R821" t="inlineStr"/>
       <c r="S821" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T821" t="inlineStr">
         <is>
@@ -61963,7 +61965,7 @@
       <c r="Q822" t="inlineStr"/>
       <c r="R822" t="inlineStr"/>
       <c r="S822" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T822" t="inlineStr">
         <is>
@@ -62014,7 +62016,7 @@
       <c r="Q823" t="inlineStr"/>
       <c r="R823" t="inlineStr"/>
       <c r="S823" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T823" t="inlineStr">
         <is>
@@ -62063,7 +62065,7 @@
       <c r="Q824" t="inlineStr"/>
       <c r="R824" t="inlineStr"/>
       <c r="S824" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T824" t="inlineStr">
         <is>
@@ -62138,7 +62140,7 @@
         <v>88.38</v>
       </c>
       <c r="S825" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T825" t="inlineStr">
         <is>
@@ -62217,7 +62219,7 @@
         <v>62.57</v>
       </c>
       <c r="S826" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T826" t="inlineStr">
         <is>
@@ -62294,7 +62296,7 @@
         <v>95.19</v>
       </c>
       <c r="S827" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T827" t="inlineStr">
         <is>
@@ -62371,7 +62373,7 @@
         <v>57.71</v>
       </c>
       <c r="S828" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T828" t="inlineStr">
         <is>
@@ -62450,7 +62452,7 @@
         <v>55.45</v>
       </c>
       <c r="S829" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T829" t="inlineStr">
         <is>
@@ -62527,7 +62529,7 @@
         <v>88.20999999999999</v>
       </c>
       <c r="S830" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T830" t="inlineStr">
         <is>
@@ -62604,7 +62606,7 @@
         <v>50.06</v>
       </c>
       <c r="S831" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T831" t="inlineStr">
         <is>
@@ -62681,7 +62683,7 @@
         <v>65.05</v>
       </c>
       <c r="S832" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T832" t="inlineStr">
         <is>
@@ -62760,7 +62762,7 @@
         <v>88.55</v>
       </c>
       <c r="S833" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T833" t="inlineStr">
         <is>
@@ -62839,7 +62841,7 @@
         <v>55.58</v>
       </c>
       <c r="S834" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T834" t="inlineStr">
         <is>
@@ -62916,7 +62918,7 @@
         <v>19.13</v>
       </c>
       <c r="S835" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T835" t="inlineStr">
         <is>
@@ -62984,7 +62986,7 @@
         <v>1111</v>
       </c>
       <c r="P836" t="n">
-        <v>1083</v>
+        <v>1093</v>
       </c>
       <c r="Q836" t="n">
         <v>1510</v>
@@ -62993,7 +62995,7 @@
         <v>12.58</v>
       </c>
       <c r="S836" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T836" t="inlineStr">
         <is>
@@ -63070,7 +63072,7 @@
         <v>23.98</v>
       </c>
       <c r="S837" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T837" t="inlineStr">
         <is>
@@ -63147,7 +63149,7 @@
         <v>69.83</v>
       </c>
       <c r="S838" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T838" t="inlineStr">
         <is>
@@ -63224,7 +63226,7 @@
         <v>36.59</v>
       </c>
       <c r="S839" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T839" t="inlineStr">
         <is>
@@ -63301,7 +63303,7 @@
         <v>70.2</v>
       </c>
       <c r="S840" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T840" t="inlineStr">
         <is>
@@ -63380,7 +63382,7 @@
         <v>86.86</v>
       </c>
       <c r="S841" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T841" t="inlineStr">
         <is>
@@ -63450,7 +63452,7 @@
         <v>75</v>
       </c>
       <c r="P842" t="n">
-        <v>-266</v>
+        <v>0</v>
       </c>
       <c r="Q842" t="n">
         <v>75</v>
@@ -63459,7 +63461,7 @@
         <v>0.75</v>
       </c>
       <c r="S842" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T842" t="inlineStr">
         <is>
@@ -63527,16 +63529,16 @@
         <v>4051</v>
       </c>
       <c r="P843" t="n">
-        <v>4762</v>
+        <v>5805</v>
       </c>
       <c r="Q843" t="n">
-        <v>4762</v>
+        <v>5805</v>
       </c>
       <c r="R843" t="n">
-        <v>47.62</v>
+        <v>58.05</v>
       </c>
       <c r="S843" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T843" t="inlineStr">
         <is>
@@ -63547,7 +63549,7 @@
         <v>8504.700000000001</v>
       </c>
       <c r="V843" t="n">
-        <v>-44.01</v>
+        <v>-31.74</v>
       </c>
       <c r="W843" t="inlineStr"/>
     </row>
@@ -63604,7 +63606,7 @@
         <v>4910</v>
       </c>
       <c r="P844" t="n">
-        <v>4526</v>
+        <v>4590</v>
       </c>
       <c r="Q844" t="n">
         <v>5470</v>
@@ -63613,7 +63615,7 @@
         <v>54.7</v>
       </c>
       <c r="S844" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T844" t="inlineStr">
         <is>
@@ -63681,16 +63683,16 @@
         <v>5954</v>
       </c>
       <c r="P845" t="n">
-        <v>6060</v>
+        <v>7005</v>
       </c>
       <c r="Q845" t="n">
-        <v>6060</v>
+        <v>7005</v>
       </c>
       <c r="R845" t="n">
-        <v>60.6</v>
+        <v>70.05</v>
       </c>
       <c r="S845" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T845" t="inlineStr">
         <is>
@@ -63701,10 +63703,10 @@
         <v>5171.44</v>
       </c>
       <c r="V845" t="n">
-        <v>17.18</v>
+        <v>35.46</v>
       </c>
       <c r="W845" t="n">
-        <v>1.267414281742381</v>
+        <v>1.346309450230008</v>
       </c>
     </row>
     <row r="846">
@@ -63769,7 +63771,7 @@
         <v>61.72</v>
       </c>
       <c r="S846" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T846" t="inlineStr">
         <is>
@@ -63848,7 +63850,7 @@
         <v>16.17</v>
       </c>
       <c r="S847" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T847" t="inlineStr">
         <is>
@@ -63925,7 +63927,7 @@
         <v>80.77</v>
       </c>
       <c r="S848" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T848" t="inlineStr">
         <is>
@@ -63995,7 +63997,7 @@
         <v>1355</v>
       </c>
       <c r="P849" t="n">
-        <v>278</v>
+        <v>293</v>
       </c>
       <c r="Q849" t="n">
         <v>1355</v>
@@ -64004,7 +64006,7 @@
         <v>18.9</v>
       </c>
       <c r="S849" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T849" t="inlineStr">
         <is>
@@ -64072,16 +64074,16 @@
         <v>1486</v>
       </c>
       <c r="P850" t="n">
-        <v>1327</v>
+        <v>1782</v>
       </c>
       <c r="Q850" t="n">
-        <v>1486</v>
+        <v>1782</v>
       </c>
       <c r="R850" t="n">
-        <v>16.58</v>
+        <v>19.88</v>
       </c>
       <c r="S850" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T850" t="inlineStr">
         <is>
@@ -64092,7 +64094,7 @@
         <v>3528.68</v>
       </c>
       <c r="V850" t="n">
-        <v>-57.89</v>
+        <v>-49.5</v>
       </c>
       <c r="W850" t="inlineStr"/>
     </row>
@@ -64149,16 +64151,16 @@
         <v>2169</v>
       </c>
       <c r="P851" t="n">
-        <v>2165</v>
+        <v>2171</v>
       </c>
       <c r="Q851" t="n">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="R851" t="n">
-        <v>25.21</v>
+        <v>25.23</v>
       </c>
       <c r="S851" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T851" t="inlineStr">
         <is>
@@ -64169,7 +64171,7 @@
         <v>3823.79</v>
       </c>
       <c r="V851" t="n">
-        <v>-43.28</v>
+        <v>-43.22</v>
       </c>
       <c r="W851" t="inlineStr"/>
     </row>
@@ -64235,7 +64237,7 @@
         <v>49.72</v>
       </c>
       <c r="S852" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T852" t="inlineStr">
         <is>
@@ -64312,7 +64314,7 @@
         <v>17.91</v>
       </c>
       <c r="S853" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T853" t="inlineStr">
         <is>
@@ -64389,7 +64391,7 @@
         <v>2.86</v>
       </c>
       <c r="S854" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T854" t="inlineStr">
         <is>
@@ -64468,7 +64470,7 @@
         <v>0.87</v>
       </c>
       <c r="S855" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T855" t="inlineStr">
         <is>
@@ -64541,7 +64543,7 @@
         <v>64.98</v>
       </c>
       <c r="S856" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T856" t="inlineStr">
         <is>
@@ -64618,7 +64620,7 @@
         <v>71.93000000000001</v>
       </c>
       <c r="S857" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T857" t="inlineStr">
         <is>
@@ -64697,7 +64699,7 @@
         <v>62.87</v>
       </c>
       <c r="S858" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T858" t="inlineStr">
         <is>
@@ -64776,7 +64778,7 @@
         <v>86.63</v>
       </c>
       <c r="S859" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T859" t="inlineStr">
         <is>
@@ -64855,7 +64857,7 @@
         <v>44.85</v>
       </c>
       <c r="S860" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T860" t="inlineStr">
         <is>
@@ -64932,7 +64934,7 @@
         <v>96.76000000000001</v>
       </c>
       <c r="S861" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T861" t="inlineStr">
         <is>
@@ -64987,7 +64989,7 @@
       <c r="Q862" t="inlineStr"/>
       <c r="R862" t="inlineStr"/>
       <c r="S862" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T862" t="inlineStr">
         <is>
@@ -65051,16 +65053,16 @@
         <v>10771</v>
       </c>
       <c r="P863" t="n">
-        <v>11480</v>
+        <v>12764</v>
       </c>
       <c r="Q863" t="n">
-        <v>11480</v>
+        <v>12764</v>
       </c>
       <c r="R863" t="n">
-        <v>57.4</v>
+        <v>63.82</v>
       </c>
       <c r="S863" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T863" t="inlineStr">
         <is>
@@ -65071,10 +65073,10 @@
         <v>5011.27</v>
       </c>
       <c r="V863" t="n">
-        <v>129.08</v>
+        <v>154.71</v>
       </c>
       <c r="W863" t="n">
-        <v>1.499356521796608</v>
+        <v>1.522158459033336</v>
       </c>
     </row>
     <row r="864">
@@ -65139,7 +65141,7 @@
         <v>0.02</v>
       </c>
       <c r="S864" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T864" t="inlineStr">
         <is>
@@ -65198,7 +65200,7 @@
       <c r="Q865" t="inlineStr"/>
       <c r="R865" t="inlineStr"/>
       <c r="S865" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T865" t="inlineStr">
         <is>
@@ -65247,7 +65249,7 @@
       <c r="Q866" t="inlineStr"/>
       <c r="R866" t="inlineStr"/>
       <c r="S866" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T866" t="inlineStr">
         <is>
@@ -65311,7 +65313,7 @@
         <v>6268</v>
       </c>
       <c r="P867" t="n">
-        <v>4715</v>
+        <v>4852</v>
       </c>
       <c r="Q867" t="n">
         <v>6268</v>
@@ -65320,7 +65322,7 @@
         <v>52.23</v>
       </c>
       <c r="S867" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T867" t="inlineStr">
         <is>
@@ -65388,16 +65390,16 @@
         <v>4559</v>
       </c>
       <c r="P868" t="n">
-        <v>6351</v>
+        <v>5966</v>
       </c>
       <c r="Q868" t="n">
-        <v>6351</v>
+        <v>5966</v>
       </c>
       <c r="R868" t="n">
-        <v>52.92</v>
+        <v>49.72</v>
       </c>
       <c r="S868" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T868" t="inlineStr">
         <is>
@@ -65408,10 +65410,10 @@
         <v>4312.44</v>
       </c>
       <c r="V868" t="n">
-        <v>47.27</v>
+        <v>38.34</v>
       </c>
       <c r="W868" t="n">
-        <v>1.378950892279339</v>
+        <v>1.355098950866078</v>
       </c>
     </row>
     <row r="869">
@@ -65476,7 +65478,7 @@
         <v>50.62</v>
       </c>
       <c r="S869" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T869" t="inlineStr">
         <is>
@@ -65555,7 +65557,7 @@
         <v>52.58</v>
       </c>
       <c r="S870" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T870" t="inlineStr">
         <is>
@@ -65632,7 +65634,7 @@
         <v>69.53</v>
       </c>
       <c r="S871" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T871" t="inlineStr">
         <is>
@@ -65709,7 +65711,7 @@
         <v>72.03</v>
       </c>
       <c r="S872" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T872" t="inlineStr">
         <is>
@@ -65779,7 +65781,7 @@
         <v>12918</v>
       </c>
       <c r="P873" t="n">
-        <v>10859</v>
+        <v>10949</v>
       </c>
       <c r="Q873" t="n">
         <v>12918</v>
@@ -65788,7 +65790,7 @@
         <v>129.18</v>
       </c>
       <c r="S873" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T873" t="inlineStr">
         <is>
@@ -65867,7 +65869,7 @@
         <v>106.2</v>
       </c>
       <c r="S874" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T874" t="inlineStr">
         <is>

--- a/Taxa de Crescimento.xlsx
+++ b/Taxa de Crescimento.xlsx
@@ -1602,7 +1602,7 @@
         <v>12165</v>
       </c>
       <c r="P16" t="n">
-        <v>11584</v>
+        <v>13113</v>
       </c>
       <c r="Q16" t="n">
         <v>14496</v>
@@ -1681,7 +1681,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>299</v>
       </c>
       <c r="Q17" t="n">
         <v>4925</v>
@@ -1760,7 +1760,7 @@
         <v>14925</v>
       </c>
       <c r="P18" t="n">
-        <v>13690</v>
+        <v>14574</v>
       </c>
       <c r="Q18" t="n">
         <v>28370</v>
@@ -3965,13 +3965,13 @@
         <v>1625</v>
       </c>
       <c r="P49" t="n">
-        <v>1649</v>
+        <v>1724</v>
       </c>
       <c r="Q49" t="n">
-        <v>1649</v>
+        <v>1724</v>
       </c>
       <c r="R49" t="n">
-        <v>54.97</v>
+        <v>57.47</v>
       </c>
       <c r="S49" t="n">
         <v>8</v>
@@ -3985,10 +3985,10 @@
         <v>1478.58</v>
       </c>
       <c r="V49" t="n">
-        <v>11.53</v>
+        <v>16.6</v>
       </c>
       <c r="W49" t="n">
-        <v>1.225986747431812</v>
+        <v>1.263792209863485</v>
       </c>
     </row>
     <row r="50">
@@ -4168,13 +4168,13 @@
         <v>2639</v>
       </c>
       <c r="P52" t="n">
-        <v>2701</v>
+        <v>2776</v>
       </c>
       <c r="Q52" t="n">
-        <v>2726</v>
+        <v>2776</v>
       </c>
       <c r="R52" t="n">
-        <v>10.9</v>
+        <v>11.1</v>
       </c>
       <c r="S52" t="n">
         <v>8</v>
@@ -4188,7 +4188,7 @@
         <v>2979.35</v>
       </c>
       <c r="V52" t="n">
-        <v>-8.5</v>
+        <v>-6.83</v>
       </c>
       <c r="W52" t="inlineStr"/>
     </row>
@@ -6143,13 +6143,13 @@
         <v>19559</v>
       </c>
       <c r="P79" t="n">
-        <v>20590</v>
+        <v>22207</v>
       </c>
       <c r="Q79" t="n">
-        <v>20590</v>
+        <v>22207</v>
       </c>
       <c r="R79" t="n">
-        <v>45.76</v>
+        <v>49.35</v>
       </c>
       <c r="S79" t="n">
         <v>8</v>
@@ -6163,10 +6163,10 @@
         <v>19321.81</v>
       </c>
       <c r="V79" t="n">
-        <v>6.56</v>
+        <v>14.93</v>
       </c>
       <c r="W79" t="n">
-        <v>1.169702235577781</v>
+        <v>1.252674732161622</v>
       </c>
     </row>
     <row r="80">
@@ -6376,13 +6376,13 @@
         <v>36867</v>
       </c>
       <c r="P82" t="n">
-        <v>38477</v>
+        <v>38755</v>
       </c>
       <c r="Q82" t="n">
-        <v>38477</v>
+        <v>38755</v>
       </c>
       <c r="R82" t="n">
-        <v>85.5</v>
+        <v>86.12</v>
       </c>
       <c r="S82" t="n">
         <v>8</v>
@@ -6396,10 +6396,10 @@
         <v>35969.29</v>
       </c>
       <c r="V82" t="n">
-        <v>6.97</v>
+        <v>7.74</v>
       </c>
       <c r="W82" t="n">
-        <v>1.175626584341361</v>
+        <v>1.185937349296872</v>
       </c>
     </row>
     <row r="83">
@@ -8231,7 +8231,7 @@
         <v>27513</v>
       </c>
       <c r="P107" t="n">
-        <v>14564</v>
+        <v>13866</v>
       </c>
       <c r="Q107" t="n">
         <v>27513</v>
@@ -8310,7 +8310,7 @@
         <v>9607</v>
       </c>
       <c r="P108" t="n">
-        <v>3680</v>
+        <v>3616</v>
       </c>
       <c r="Q108" t="n">
         <v>9607</v>
@@ -8688,13 +8688,13 @@
         <v>11434</v>
       </c>
       <c r="P114" t="n">
-        <v>11485</v>
+        <v>11521</v>
       </c>
       <c r="Q114" t="n">
-        <v>11485</v>
+        <v>11521</v>
       </c>
       <c r="R114" t="n">
-        <v>91.88</v>
+        <v>92.17</v>
       </c>
       <c r="S114" t="n">
         <v>8</v>
@@ -8708,7 +8708,7 @@
         <v>11732.5</v>
       </c>
       <c r="V114" t="n">
-        <v>-2.11</v>
+        <v>-1.8</v>
       </c>
       <c r="W114" t="inlineStr"/>
     </row>
@@ -11929,7 +11929,7 @@
         <v>19750</v>
       </c>
       <c r="P159" t="n">
-        <v>18791</v>
+        <v>19637</v>
       </c>
       <c r="Q159" t="n">
         <v>19750</v>
@@ -15792,13 +15792,13 @@
         <v>22450</v>
       </c>
       <c r="P212" t="n">
-        <v>0</v>
+        <v>23928</v>
       </c>
       <c r="Q212" t="n">
-        <v>22789</v>
+        <v>23928</v>
       </c>
       <c r="R212" t="n">
-        <v>91.16</v>
+        <v>95.70999999999999</v>
       </c>
       <c r="S212" t="n">
         <v>8</v>
@@ -15812,10 +15812,10 @@
         <v>7305</v>
       </c>
       <c r="V212" t="n">
-        <v>211.96</v>
+        <v>227.56</v>
       </c>
       <c r="W212" t="n">
-        <v>1.562624008317012</v>
+        <v>1.571899082385014</v>
       </c>
     </row>
     <row r="213">
@@ -15973,13 +15973,13 @@
         <v>2584</v>
       </c>
       <c r="P215" t="n">
-        <v>2639</v>
+        <v>2828</v>
       </c>
       <c r="Q215" t="n">
-        <v>2639</v>
+        <v>2828</v>
       </c>
       <c r="R215" t="n">
-        <v>87.97</v>
+        <v>94.27</v>
       </c>
       <c r="S215" t="n">
         <v>8</v>
@@ -15993,10 +15993,10 @@
         <v>2510.67</v>
       </c>
       <c r="V215" t="n">
-        <v>5.11</v>
+        <v>12.64</v>
       </c>
       <c r="W215" t="n">
-        <v>1.145605460470037</v>
+        <v>1.23541325358259</v>
       </c>
     </row>
     <row r="216">
@@ -16443,13 +16443,13 @@
         <v>4639</v>
       </c>
       <c r="P221" t="n">
-        <v>4878</v>
+        <v>5240</v>
       </c>
       <c r="Q221" t="n">
-        <v>4878</v>
+        <v>5240</v>
       </c>
       <c r="R221" t="n">
-        <v>52.03</v>
+        <v>55.89</v>
       </c>
       <c r="S221" t="n">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>5598.92</v>
       </c>
       <c r="V221" t="n">
-        <v>-12.88</v>
+        <v>-6.41</v>
       </c>
       <c r="W221" t="inlineStr"/>
     </row>
@@ -19153,7 +19153,7 @@
         <v>1797</v>
       </c>
       <c r="P257" t="n">
-        <v>1220</v>
+        <v>1215</v>
       </c>
       <c r="Q257" t="n">
         <v>1930</v>
@@ -20097,7 +20097,7 @@
         <v>5986</v>
       </c>
       <c r="P269" t="n">
-        <v>4716</v>
+        <v>5695</v>
       </c>
       <c r="Q269" t="n">
         <v>7429</v>
@@ -23271,13 +23271,13 @@
         <v>6140</v>
       </c>
       <c r="P311" t="n">
-        <v>6016</v>
+        <v>6267</v>
       </c>
       <c r="Q311" t="n">
-        <v>6140</v>
+        <v>6267</v>
       </c>
       <c r="R311" t="n">
-        <v>61.4</v>
+        <v>62.67</v>
       </c>
       <c r="S311" t="n">
         <v>8</v>
@@ -23291,10 +23291,10 @@
         <v>4483.32</v>
       </c>
       <c r="V311" t="n">
-        <v>36.95</v>
+        <v>39.78</v>
       </c>
       <c r="W311" t="n">
-        <v>1.350935259341024</v>
+        <v>1.359268955881436</v>
       </c>
     </row>
     <row r="312">
@@ -23427,13 +23427,13 @@
         <v>3754</v>
       </c>
       <c r="P313" t="n">
-        <v>3843</v>
+        <v>4124</v>
       </c>
       <c r="Q313" t="n">
-        <v>3843</v>
+        <v>4124</v>
       </c>
       <c r="R313" t="n">
-        <v>38.43</v>
+        <v>41.24</v>
       </c>
       <c r="S313" t="n">
         <v>8</v>
@@ -23447,7 +23447,7 @@
         <v>4882.03</v>
       </c>
       <c r="V313" t="n">
-        <v>-21.28</v>
+        <v>-15.53</v>
       </c>
       <c r="W313" t="inlineStr"/>
     </row>
@@ -24434,7 +24434,7 @@
         <v>1176</v>
       </c>
       <c r="P328" t="n">
-        <v>1366</v>
+        <v>1450</v>
       </c>
       <c r="Q328" t="n">
         <v>1637</v>
@@ -25109,13 +25109,13 @@
         <v>5311</v>
       </c>
       <c r="P337" t="n">
-        <v>4993</v>
+        <v>6185</v>
       </c>
       <c r="Q337" t="n">
-        <v>5311</v>
+        <v>6185</v>
       </c>
       <c r="R337" t="n">
-        <v>44.26</v>
+        <v>51.54</v>
       </c>
       <c r="S337" t="n">
         <v>8</v>
@@ -25129,10 +25129,10 @@
         <v>4336.29</v>
       </c>
       <c r="V337" t="n">
-        <v>22.48</v>
+        <v>42.63</v>
       </c>
       <c r="W337" t="n">
-        <v>1.296133370647445</v>
+        <v>1.367129362810221</v>
       </c>
     </row>
     <row r="338">
@@ -26271,7 +26271,7 @@
         <v>3755</v>
       </c>
       <c r="P353" t="n">
-        <v>3672</v>
+        <v>3753</v>
       </c>
       <c r="Q353" t="n">
         <v>3782</v>
@@ -26662,13 +26662,13 @@
         <v>1958</v>
       </c>
       <c r="P358" t="n">
-        <v>2096</v>
+        <v>2270</v>
       </c>
       <c r="Q358" t="n">
-        <v>2096</v>
+        <v>2270</v>
       </c>
       <c r="R358" t="n">
-        <v>20.96</v>
+        <v>22.7</v>
       </c>
       <c r="S358" t="n">
         <v>8</v>
@@ -26682,9 +26682,11 @@
         <v>2182.6</v>
       </c>
       <c r="V358" t="n">
-        <v>-3.97</v>
-      </c>
-      <c r="W358" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="W358" t="n">
+        <v>1.122462048309373</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -27515,7 +27517,7 @@
         <v>6493</v>
       </c>
       <c r="P369" t="n">
-        <v>6433</v>
+        <v>6490</v>
       </c>
       <c r="Q369" t="n">
         <v>6493</v>
@@ -29229,7 +29231,7 @@
         <v>2537</v>
       </c>
       <c r="P391" t="n">
-        <v>2442</v>
+        <v>2486</v>
       </c>
       <c r="Q391" t="n">
         <v>2537</v>
@@ -29306,7 +29308,7 @@
         <v>7403</v>
       </c>
       <c r="P392" t="n">
-        <v>6727</v>
+        <v>6105</v>
       </c>
       <c r="Q392" t="n">
         <v>7403</v>
@@ -30601,13 +30603,13 @@
         <v>875</v>
       </c>
       <c r="P409" t="n">
-        <v>1504</v>
+        <v>1469</v>
       </c>
       <c r="Q409" t="n">
-        <v>1504</v>
+        <v>1469</v>
       </c>
       <c r="R409" t="n">
-        <v>8.85</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="S409" t="n">
         <v>8</v>
@@ -30621,7 +30623,7 @@
         <v>1512.99</v>
       </c>
       <c r="V409" t="n">
-        <v>-0.59</v>
+        <v>-2.91</v>
       </c>
       <c r="W409" t="inlineStr"/>
     </row>
@@ -31221,7 +31223,7 @@
         <v>7301</v>
       </c>
       <c r="P417" t="n">
-        <v>7004</v>
+        <v>7063</v>
       </c>
       <c r="Q417" t="n">
         <v>7501</v>
@@ -32313,13 +32315,13 @@
         <v>5628</v>
       </c>
       <c r="P431" t="n">
-        <v>5869</v>
+        <v>6049</v>
       </c>
       <c r="Q431" t="n">
-        <v>5869</v>
+        <v>6049</v>
       </c>
       <c r="R431" t="n">
-        <v>58.69</v>
+        <v>60.49</v>
       </c>
       <c r="S431" t="n">
         <v>8</v>
@@ -32333,7 +32335,7 @@
         <v>8447.5</v>
       </c>
       <c r="V431" t="n">
-        <v>-30.52</v>
+        <v>-28.39</v>
       </c>
       <c r="W431" t="inlineStr"/>
     </row>
@@ -33948,13 +33950,13 @@
         <v>4114</v>
       </c>
       <c r="P452" t="n">
-        <v>5106</v>
+        <v>5598</v>
       </c>
       <c r="Q452" t="n">
-        <v>5106</v>
+        <v>5598</v>
       </c>
       <c r="R452" t="n">
-        <v>51.06</v>
+        <v>55.98</v>
       </c>
       <c r="S452" t="n">
         <v>8</v>
@@ -33968,10 +33970,10 @@
         <v>4416.41</v>
       </c>
       <c r="V452" t="n">
-        <v>15.61</v>
+        <v>26.75</v>
       </c>
       <c r="W452" t="n">
-        <v>1.257332790719738</v>
+        <v>1.315054188517107</v>
       </c>
     </row>
     <row r="453">
@@ -34880,7 +34882,7 @@
         <v>5366</v>
       </c>
       <c r="P464" t="n">
-        <v>3176</v>
+        <v>4367</v>
       </c>
       <c r="Q464" t="n">
         <v>5366</v>
@@ -34957,13 +34959,13 @@
         <v>525</v>
       </c>
       <c r="P465" t="n">
-        <v>578</v>
+        <v>586</v>
       </c>
       <c r="Q465" t="n">
-        <v>578</v>
+        <v>586</v>
       </c>
       <c r="R465" t="n">
-        <v>28.9</v>
+        <v>29.3</v>
       </c>
       <c r="S465" t="n">
         <v>8</v>
@@ -34977,7 +34979,7 @@
         <v>620.76</v>
       </c>
       <c r="V465" t="n">
-        <v>-6.89</v>
+        <v>-5.6</v>
       </c>
       <c r="W465" t="inlineStr"/>
     </row>
@@ -36355,7 +36357,7 @@
         <v>8975</v>
       </c>
       <c r="P483" t="n">
-        <v>8897</v>
+        <v>8942</v>
       </c>
       <c r="Q483" t="n">
         <v>8975</v>
@@ -37058,13 +37060,13 @@
         <v>4966</v>
       </c>
       <c r="P492" t="n">
-        <v>5269</v>
+        <v>5379</v>
       </c>
       <c r="Q492" t="n">
-        <v>5269</v>
+        <v>5379</v>
       </c>
       <c r="R492" t="n">
-        <v>52.69</v>
+        <v>53.79</v>
       </c>
       <c r="S492" t="n">
         <v>8</v>
@@ -37078,10 +37080,10 @@
         <v>4910.37</v>
       </c>
       <c r="V492" t="n">
-        <v>7.3</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="W492" t="n">
-        <v>1.180167285354979</v>
+        <v>1.206782576531111</v>
       </c>
     </row>
     <row r="493">
@@ -37370,13 +37372,13 @@
         <v>4717</v>
       </c>
       <c r="P496" t="n">
-        <v>4727</v>
+        <v>4744</v>
       </c>
       <c r="Q496" t="n">
-        <v>4727</v>
+        <v>4744</v>
       </c>
       <c r="R496" t="n">
-        <v>47.09</v>
+        <v>47.26</v>
       </c>
       <c r="S496" t="n">
         <v>8</v>
@@ -37390,10 +37392,10 @@
         <v>4343.4</v>
       </c>
       <c r="V496" t="n">
-        <v>8.83</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="W496" t="n">
-        <v>1.199030025541241</v>
+        <v>1.203356320573685</v>
       </c>
     </row>
     <row r="497">
@@ -37994,7 +37996,7 @@
         <v>3660</v>
       </c>
       <c r="P504" t="n">
-        <v>3555</v>
+        <v>3569</v>
       </c>
       <c r="Q504" t="n">
         <v>3660</v>
@@ -38460,13 +38462,13 @@
         <v>2776</v>
       </c>
       <c r="P510" t="n">
-        <v>3336</v>
+        <v>3344</v>
       </c>
       <c r="Q510" t="n">
-        <v>3336</v>
+        <v>3344</v>
       </c>
       <c r="R510" t="n">
-        <v>33.36</v>
+        <v>33.44</v>
       </c>
       <c r="S510" t="n">
         <v>8</v>
@@ -38480,7 +38482,7 @@
         <v>6017.96</v>
       </c>
       <c r="V510" t="n">
-        <v>-44.57</v>
+        <v>-44.43</v>
       </c>
       <c r="W510" t="inlineStr"/>
     </row>
@@ -39157,7 +39159,7 @@
         <v>5093</v>
       </c>
       <c r="P519" t="n">
-        <v>4880</v>
+        <v>4911</v>
       </c>
       <c r="Q519" t="n">
         <v>5093</v>
@@ -39623,13 +39625,13 @@
         <v>6020</v>
       </c>
       <c r="P525" t="n">
-        <v>5940</v>
+        <v>6033</v>
       </c>
       <c r="Q525" t="n">
-        <v>6020</v>
+        <v>6033</v>
       </c>
       <c r="R525" t="n">
-        <v>60.2</v>
+        <v>60.33</v>
       </c>
       <c r="S525" t="n">
         <v>8</v>
@@ -39643,7 +39645,7 @@
         <v>8209.059999999999</v>
       </c>
       <c r="V525" t="n">
-        <v>-26.67</v>
+        <v>-26.51</v>
       </c>
       <c r="W525" t="inlineStr"/>
     </row>
@@ -40468,13 +40470,13 @@
         <v>665</v>
       </c>
       <c r="P536" t="n">
-        <v>657</v>
+        <v>919</v>
       </c>
       <c r="Q536" t="n">
-        <v>707</v>
+        <v>919</v>
       </c>
       <c r="R536" t="n">
-        <v>35.35</v>
+        <v>45.95</v>
       </c>
       <c r="S536" t="n">
         <v>8</v>
@@ -40488,7 +40490,7 @@
         <v>1663.67</v>
       </c>
       <c r="V536" t="n">
-        <v>-57.5</v>
+        <v>-44.76</v>
       </c>
       <c r="W536" t="inlineStr"/>
     </row>
@@ -41237,7 +41239,7 @@
         <v>5417</v>
       </c>
       <c r="P547" t="n">
-        <v>2691</v>
+        <v>2663</v>
       </c>
       <c r="Q547" t="n">
         <v>6510</v>
@@ -41314,7 +41316,7 @@
         <v>6861</v>
       </c>
       <c r="P548" t="n">
-        <v>2531</v>
+        <v>2427</v>
       </c>
       <c r="Q548" t="n">
         <v>6861</v>
@@ -42517,7 +42519,7 @@
         <v>4348</v>
       </c>
       <c r="P565" t="n">
-        <v>3938</v>
+        <v>4224</v>
       </c>
       <c r="Q565" t="n">
         <v>4348</v>
@@ -43192,13 +43194,13 @@
         <v>5101</v>
       </c>
       <c r="P574" t="n">
-        <v>5939</v>
+        <v>6088</v>
       </c>
       <c r="Q574" t="n">
-        <v>5939</v>
+        <v>6088</v>
       </c>
       <c r="R574" t="n">
-        <v>84.84</v>
+        <v>86.97</v>
       </c>
       <c r="S574" t="n">
         <v>8</v>
@@ -43212,10 +43214,10 @@
         <v>5121.94</v>
       </c>
       <c r="V574" t="n">
-        <v>15.95</v>
+        <v>18.86</v>
       </c>
       <c r="W574" t="n">
-        <v>1.259592474573147</v>
+        <v>1.277306554312118</v>
       </c>
     </row>
     <row r="575">
@@ -44408,7 +44410,7 @@
         <v>2423</v>
       </c>
       <c r="P590" t="n">
-        <v>1213</v>
+        <v>1970</v>
       </c>
       <c r="Q590" t="n">
         <v>3670</v>
@@ -44793,7 +44795,7 @@
         <v>398</v>
       </c>
       <c r="P595" t="n">
-        <v>398</v>
+        <v>349</v>
       </c>
       <c r="Q595" t="n">
         <v>398</v>
@@ -48394,7 +48396,7 @@
         <v>7734</v>
       </c>
       <c r="P642" t="n">
-        <v>7157</v>
+        <v>7593</v>
       </c>
       <c r="Q642" t="n">
         <v>8193</v>
@@ -49837,7 +49839,7 @@
         <v>8291</v>
       </c>
       <c r="P661" t="n">
-        <v>6230</v>
+        <v>7026</v>
       </c>
       <c r="Q661" t="n">
         <v>9245</v>
@@ -52970,13 +52972,13 @@
         <v>6744</v>
       </c>
       <c r="P702" t="n">
-        <v>6642</v>
+        <v>6882</v>
       </c>
       <c r="Q702" t="n">
-        <v>6813</v>
+        <v>6882</v>
       </c>
       <c r="R702" t="n">
-        <v>68.13</v>
+        <v>68.81999999999999</v>
       </c>
       <c r="S702" t="n">
         <v>8</v>
@@ -52990,7 +52992,7 @@
         <v>9010.68</v>
       </c>
       <c r="V702" t="n">
-        <v>-24.39</v>
+        <v>-23.62</v>
       </c>
       <c r="W702" t="inlineStr"/>
     </row>
@@ -53201,13 +53203,13 @@
         <v>2843</v>
       </c>
       <c r="P705" t="n">
-        <v>2940</v>
+        <v>2632</v>
       </c>
       <c r="Q705" t="n">
-        <v>2940</v>
+        <v>2843</v>
       </c>
       <c r="R705" t="n">
-        <v>42</v>
+        <v>40.61</v>
       </c>
       <c r="S705" t="n">
         <v>8</v>
@@ -53221,11 +53223,9 @@
         <v>2866.48</v>
       </c>
       <c r="V705" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="W705" t="n">
-        <v>1.081483747120199</v>
-      </c>
+        <v>-0.82</v>
+      </c>
+      <c r="W705" t="inlineStr"/>
     </row>
     <row r="706">
       <c r="A706" t="inlineStr">
@@ -55454,7 +55454,7 @@
         <v>6867</v>
       </c>
       <c r="P734" t="n">
-        <v>6273</v>
+        <v>6286</v>
       </c>
       <c r="Q734" t="n">
         <v>7742</v>
@@ -55841,13 +55841,13 @@
         <v>7507</v>
       </c>
       <c r="P739" t="n">
-        <v>7521</v>
+        <v>7604</v>
       </c>
       <c r="Q739" t="n">
-        <v>7577</v>
+        <v>7604</v>
       </c>
       <c r="R739" t="n">
-        <v>75.48</v>
+        <v>75.73999999999999</v>
       </c>
       <c r="S739" t="n">
         <v>8</v>
@@ -55861,10 +55861,10 @@
         <v>7500.45</v>
       </c>
       <c r="V739" t="n">
-        <v>1.02</v>
+        <v>1.38</v>
       </c>
       <c r="W739" t="n">
-        <v>1.00165158130192</v>
+        <v>1.027203736594576</v>
       </c>
     </row>
     <row r="740">
@@ -56234,7 +56234,7 @@
         <v>1267</v>
       </c>
       <c r="P744" t="n">
-        <v>1122</v>
+        <v>1400</v>
       </c>
       <c r="Q744" t="n">
         <v>1610</v>
@@ -56692,7 +56692,7 @@
         <v>4170</v>
       </c>
       <c r="P750" t="n">
-        <v>3596</v>
+        <v>3820</v>
       </c>
       <c r="Q750" t="n">
         <v>5747</v>
@@ -56771,7 +56771,7 @@
         <v>5858</v>
       </c>
       <c r="P751" t="n">
-        <v>4085</v>
+        <v>4788</v>
       </c>
       <c r="Q751" t="n">
         <v>5858</v>
@@ -56848,7 +56848,7 @@
         <v>5114</v>
       </c>
       <c r="P752" t="n">
-        <v>2184</v>
+        <v>2143</v>
       </c>
       <c r="Q752" t="n">
         <v>5114</v>
@@ -59863,7 +59863,7 @@
         <v>3176</v>
       </c>
       <c r="P793" t="n">
-        <v>0</v>
+        <v>3083</v>
       </c>
       <c r="Q793" t="n">
         <v>3176</v>
@@ -59940,7 +59940,7 @@
         <v>7184</v>
       </c>
       <c r="P794" t="n">
-        <v>1068</v>
+        <v>6765</v>
       </c>
       <c r="Q794" t="n">
         <v>7184</v>
@@ -60017,7 +60017,7 @@
         <v>1241</v>
       </c>
       <c r="P795" t="n">
-        <v>0</v>
+        <v>325</v>
       </c>
       <c r="Q795" t="n">
         <v>1907</v>
@@ -60094,7 +60094,7 @@
         <v>1972</v>
       </c>
       <c r="P796" t="n">
-        <v>0</v>
+        <v>1990</v>
       </c>
       <c r="Q796" t="n">
         <v>2531</v>
@@ -60481,7 +60481,7 @@
         <v>7168</v>
       </c>
       <c r="P801" t="n">
-        <v>5432</v>
+        <v>5629</v>
       </c>
       <c r="Q801" t="n">
         <v>7168</v>
@@ -60953,7 +60953,7 @@
         <v>2103</v>
       </c>
       <c r="P807" t="n">
-        <v>2161</v>
+        <v>2167</v>
       </c>
       <c r="Q807" t="n">
         <v>2316</v>
@@ -61030,13 +61030,13 @@
         <v>2696</v>
       </c>
       <c r="P808" t="n">
-        <v>2860</v>
+        <v>3008</v>
       </c>
       <c r="Q808" t="n">
-        <v>2860</v>
+        <v>3008</v>
       </c>
       <c r="R808" t="n">
-        <v>71.5</v>
+        <v>75.2</v>
       </c>
       <c r="S808" t="n">
         <v>8</v>
@@ -61050,7 +61050,7 @@
         <v>3309.36</v>
       </c>
       <c r="V808" t="n">
-        <v>-13.58</v>
+        <v>-9.109999999999999</v>
       </c>
       <c r="W808" t="inlineStr"/>
     </row>
@@ -61265,13 +61265,13 @@
         <v>5289</v>
       </c>
       <c r="P811" t="n">
-        <v>5571</v>
+        <v>5579</v>
       </c>
       <c r="Q811" t="n">
-        <v>5571</v>
+        <v>5579</v>
       </c>
       <c r="R811" t="n">
-        <v>77.38</v>
+        <v>77.48999999999999</v>
       </c>
       <c r="S811" t="n">
         <v>8</v>
@@ -61285,7 +61285,7 @@
         <v>6089.51</v>
       </c>
       <c r="V811" t="n">
-        <v>-8.51</v>
+        <v>-8.380000000000001</v>
       </c>
       <c r="W811" t="inlineStr"/>
     </row>
@@ -61470,7 +61470,7 @@
         <v>128</v>
       </c>
       <c r="P814" t="n">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="Q814" t="n">
         <v>4173</v>
@@ -62443,7 +62443,7 @@
         <v>3235</v>
       </c>
       <c r="P829" t="n">
-        <v>3276</v>
+        <v>3384</v>
       </c>
       <c r="Q829" t="n">
         <v>3976</v>
@@ -63606,7 +63606,7 @@
         <v>4910</v>
       </c>
       <c r="P844" t="n">
-        <v>4590</v>
+        <v>4716</v>
       </c>
       <c r="Q844" t="n">
         <v>5470</v>
@@ -64228,7 +64228,7 @@
         <v>4278</v>
       </c>
       <c r="P852" t="n">
-        <v>4051</v>
+        <v>4169</v>
       </c>
       <c r="Q852" t="n">
         <v>4278</v>
@@ -65313,7 +65313,7 @@
         <v>6268</v>
       </c>
       <c r="P867" t="n">
-        <v>4852</v>
+        <v>4927</v>
       </c>
       <c r="Q867" t="n">
         <v>6268</v>

--- a/Taxa de Crescimento.xlsx
+++ b/Taxa de Crescimento.xlsx
@@ -1369,13 +1369,13 @@
         <v>1036</v>
       </c>
       <c r="P13" t="n">
-        <v>1077</v>
+        <v>1366</v>
       </c>
       <c r="Q13" t="n">
-        <v>1077</v>
+        <v>1366</v>
       </c>
       <c r="R13" t="n">
-        <v>35.9</v>
+        <v>45.53</v>
       </c>
       <c r="S13" t="n">
         <v>8</v>
@@ -1389,7 +1389,7 @@
         <v>1471.72</v>
       </c>
       <c r="V13" t="n">
-        <v>-26.82</v>
+        <v>-7.18</v>
       </c>
       <c r="W13" t="inlineStr"/>
     </row>
@@ -1602,13 +1602,13 @@
         <v>12165</v>
       </c>
       <c r="P16" t="n">
-        <v>13113</v>
+        <v>14796</v>
       </c>
       <c r="Q16" t="n">
-        <v>14496</v>
+        <v>14796</v>
       </c>
       <c r="R16" t="n">
-        <v>57.98</v>
+        <v>59.18</v>
       </c>
       <c r="S16" t="n">
         <v>8</v>
@@ -1622,10 +1622,10 @@
         <v>13488.35</v>
       </c>
       <c r="V16" t="n">
-        <v>7.47</v>
+        <v>9.69</v>
       </c>
       <c r="W16" t="n">
-        <v>1.182433476642122</v>
+        <v>1.208352508752738</v>
       </c>
     </row>
     <row r="17">
@@ -1681,7 +1681,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>299</v>
+        <v>1377</v>
       </c>
       <c r="Q17" t="n">
         <v>4925</v>
@@ -1760,7 +1760,7 @@
         <v>14925</v>
       </c>
       <c r="P18" t="n">
-        <v>14574</v>
+        <v>15662</v>
       </c>
       <c r="Q18" t="n">
         <v>28370</v>
@@ -2608,7 +2608,7 @@
         <v>12217</v>
       </c>
       <c r="P30" t="n">
-        <v>12017</v>
+        <v>12085</v>
       </c>
       <c r="Q30" t="n">
         <v>12217</v>
@@ -5545,7 +5545,7 @@
         <v>12752</v>
       </c>
       <c r="P71" t="n">
-        <v>11592</v>
+        <v>11260</v>
       </c>
       <c r="Q71" t="n">
         <v>12752</v>
@@ -6143,13 +6143,13 @@
         <v>19559</v>
       </c>
       <c r="P79" t="n">
-        <v>22207</v>
+        <v>24841</v>
       </c>
       <c r="Q79" t="n">
-        <v>22207</v>
+        <v>24841</v>
       </c>
       <c r="R79" t="n">
-        <v>49.35</v>
+        <v>55.2</v>
       </c>
       <c r="S79" t="n">
         <v>8</v>
@@ -6163,10 +6163,10 @@
         <v>19321.81</v>
       </c>
       <c r="V79" t="n">
-        <v>14.93</v>
+        <v>28.56</v>
       </c>
       <c r="W79" t="n">
-        <v>1.252674732161622</v>
+        <v>1.322248806218581</v>
       </c>
     </row>
     <row r="80">
@@ -6921,13 +6921,13 @@
         <v>3914</v>
       </c>
       <c r="P89" t="n">
-        <v>4095</v>
+        <v>3534</v>
       </c>
       <c r="Q89" t="n">
-        <v>4095</v>
+        <v>3914</v>
       </c>
       <c r="R89" t="n">
-        <v>54.6</v>
+        <v>52.19</v>
       </c>
       <c r="S89" t="n">
         <v>8</v>
@@ -6941,10 +6941,10 @@
         <v>3728.44</v>
       </c>
       <c r="V89" t="n">
-        <v>9.83</v>
+        <v>4.98</v>
       </c>
       <c r="W89" t="n">
-        <v>1.209797807629743</v>
+        <v>1.143147958855996</v>
       </c>
     </row>
     <row r="90">
@@ -8231,7 +8231,7 @@
         <v>27513</v>
       </c>
       <c r="P107" t="n">
-        <v>13866</v>
+        <v>12812</v>
       </c>
       <c r="Q107" t="n">
         <v>27513</v>
@@ -8310,7 +8310,7 @@
         <v>9607</v>
       </c>
       <c r="P108" t="n">
-        <v>3616</v>
+        <v>3269</v>
       </c>
       <c r="Q108" t="n">
         <v>9607</v>
@@ -8513,7 +8513,7 @@
         <v>14456</v>
       </c>
       <c r="P111" t="n">
-        <v>13449</v>
+        <v>14217</v>
       </c>
       <c r="Q111" t="n">
         <v>14508</v>
@@ -9177,13 +9177,13 @@
         <v>12244</v>
       </c>
       <c r="P121" t="n">
-        <v>14144</v>
+        <v>11188</v>
       </c>
       <c r="Q121" t="n">
-        <v>14144</v>
+        <v>14086</v>
       </c>
       <c r="R121" t="n">
-        <v>56.58</v>
+        <v>56.34</v>
       </c>
       <c r="S121" t="n">
         <v>8</v>
@@ -9197,10 +9197,10 @@
         <v>13640.43</v>
       </c>
       <c r="V121" t="n">
-        <v>3.69</v>
+        <v>3.27</v>
       </c>
       <c r="W121" t="n">
-        <v>1.114941798436144</v>
+        <v>1.103770999933581</v>
       </c>
     </row>
     <row r="122">
@@ -9613,13 +9613,13 @@
         <v>26571</v>
       </c>
       <c r="P127" t="n">
-        <v>27375</v>
+        <v>28173</v>
       </c>
       <c r="Q127" t="n">
-        <v>27375</v>
+        <v>28173</v>
       </c>
       <c r="R127" t="n">
-        <v>109.5</v>
+        <v>112.69</v>
       </c>
       <c r="S127" t="n">
         <v>8</v>
@@ -9633,10 +9633,10 @@
         <v>23903.71</v>
       </c>
       <c r="V127" t="n">
-        <v>14.52</v>
+        <v>17.86</v>
       </c>
       <c r="W127" t="n">
-        <v>1.249771311924568</v>
+        <v>1.271520757924855</v>
       </c>
     </row>
     <row r="128">
@@ -10361,7 +10361,7 @@
         <v>6372</v>
       </c>
       <c r="P137" t="n">
-        <v>1643</v>
+        <v>1801</v>
       </c>
       <c r="Q137" t="n">
         <v>9526</v>
@@ -10773,7 +10773,7 @@
         <v>4729</v>
       </c>
       <c r="P143" t="n">
-        <v>4977</v>
+        <v>5067</v>
       </c>
       <c r="Q143" t="n">
         <v>5336</v>
@@ -11519,7 +11519,7 @@
         <v>4276</v>
       </c>
       <c r="P153" t="n">
-        <v>4046</v>
+        <v>4144</v>
       </c>
       <c r="Q153" t="n">
         <v>4768</v>
@@ -12724,13 +12724,13 @@
         <v>11635</v>
       </c>
       <c r="P170" t="n">
-        <v>11893</v>
+        <v>11975</v>
       </c>
       <c r="Q170" t="n">
-        <v>11893</v>
+        <v>11975</v>
       </c>
       <c r="R170" t="n">
-        <v>47.57</v>
+        <v>47.9</v>
       </c>
       <c r="S170" t="n">
         <v>8</v>
@@ -12744,10 +12744,10 @@
         <v>11219.45</v>
       </c>
       <c r="V170" t="n">
-        <v>6</v>
+        <v>6.73</v>
       </c>
       <c r="W170" t="n">
-        <v>1.161036672373994</v>
+        <v>1.172198753847965</v>
       </c>
     </row>
     <row r="171">
@@ -12803,13 +12803,13 @@
         <v>2788</v>
       </c>
       <c r="P171" t="n">
-        <v>2764</v>
+        <v>3495</v>
       </c>
       <c r="Q171" t="n">
-        <v>2788</v>
+        <v>3495</v>
       </c>
       <c r="R171" t="n">
-        <v>29.74</v>
+        <v>37.28</v>
       </c>
       <c r="S171" t="n">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>4432.32</v>
       </c>
       <c r="V171" t="n">
-        <v>-37.1</v>
+        <v>-21.15</v>
       </c>
       <c r="W171" t="inlineStr"/>
     </row>
@@ -13264,7 +13264,7 @@
         <v>6068</v>
       </c>
       <c r="P178" t="n">
-        <v>3247</v>
+        <v>2859</v>
       </c>
       <c r="Q178" t="n">
         <v>6068</v>
@@ -13420,7 +13420,7 @@
         <v>19578</v>
       </c>
       <c r="P180" t="n">
-        <v>15584</v>
+        <v>16659</v>
       </c>
       <c r="Q180" t="n">
         <v>19578</v>
@@ -14125,7 +14125,7 @@
         <v>19286</v>
       </c>
       <c r="P189" t="n">
-        <v>16782</v>
+        <v>17525</v>
       </c>
       <c r="Q189" t="n">
         <v>23208</v>
@@ -14281,7 +14281,7 @@
         <v>26734</v>
       </c>
       <c r="P191" t="n">
-        <v>24093</v>
+        <v>27216</v>
       </c>
       <c r="Q191" t="n">
         <v>27359</v>
@@ -16052,7 +16052,7 @@
         <v>12128</v>
       </c>
       <c r="P216" t="n">
-        <v>11874</v>
+        <v>11883</v>
       </c>
       <c r="Q216" t="n">
         <v>12128</v>
@@ -16569,7 +16569,7 @@
         <v>2047</v>
       </c>
       <c r="P223" t="n">
-        <v>1876</v>
+        <v>1927</v>
       </c>
       <c r="Q223" t="n">
         <v>2306</v>
@@ -17003,7 +17003,7 @@
         <v>27054</v>
       </c>
       <c r="P229" t="n">
-        <v>23057</v>
+        <v>23717</v>
       </c>
       <c r="Q229" t="n">
         <v>27054</v>
@@ -18217,7 +18217,7 @@
         <v>7078</v>
       </c>
       <c r="P245" t="n">
-        <v>6784</v>
+        <v>6131</v>
       </c>
       <c r="Q245" t="n">
         <v>7078</v>
@@ -18296,7 +18296,7 @@
         <v>7330</v>
       </c>
       <c r="P246" t="n">
-        <v>6332</v>
+        <v>5759</v>
       </c>
       <c r="Q246" t="n">
         <v>7330</v>
@@ -18373,7 +18373,7 @@
         <v>3733</v>
       </c>
       <c r="P247" t="n">
-        <v>3226</v>
+        <v>2660</v>
       </c>
       <c r="Q247" t="n">
         <v>3733</v>
@@ -18450,7 +18450,7 @@
         <v>3899</v>
       </c>
       <c r="P248" t="n">
-        <v>3379</v>
+        <v>2946</v>
       </c>
       <c r="Q248" t="n">
         <v>3899</v>
@@ -18606,13 +18606,13 @@
         <v>4579</v>
       </c>
       <c r="P250" t="n">
-        <v>5033</v>
+        <v>4327</v>
       </c>
       <c r="Q250" t="n">
-        <v>5033</v>
+        <v>4579</v>
       </c>
       <c r="R250" t="n">
-        <v>50.13</v>
+        <v>45.61</v>
       </c>
       <c r="S250" t="n">
         <v>8</v>
@@ -18626,11 +18626,9 @@
         <v>4714.71</v>
       </c>
       <c r="V250" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="W250" t="n">
-        <v>1.172488651117188</v>
-      </c>
+        <v>-2.88</v>
+      </c>
+      <c r="W250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -18995,13 +18993,13 @@
         <v>2187</v>
       </c>
       <c r="P255" t="n">
-        <v>2445</v>
+        <v>2499</v>
       </c>
       <c r="Q255" t="n">
-        <v>2445</v>
+        <v>2499</v>
       </c>
       <c r="R255" t="n">
-        <v>51.15</v>
+        <v>52.28</v>
       </c>
       <c r="S255" t="n">
         <v>8</v>
@@ -19015,10 +19013,10 @@
         <v>1805</v>
       </c>
       <c r="V255" t="n">
-        <v>35.46</v>
+        <v>38.45</v>
       </c>
       <c r="W255" t="n">
-        <v>1.346309450230008</v>
+        <v>1.355422514658814</v>
       </c>
     </row>
     <row r="256">
@@ -19153,7 +19151,7 @@
         <v>1797</v>
       </c>
       <c r="P257" t="n">
-        <v>1215</v>
+        <v>1051</v>
       </c>
       <c r="Q257" t="n">
         <v>1930</v>
@@ -19467,7 +19465,7 @@
         <v>5648</v>
       </c>
       <c r="P261" t="n">
-        <v>5424</v>
+        <v>5437</v>
       </c>
       <c r="Q261" t="n">
         <v>5648</v>
@@ -19702,7 +19700,7 @@
         <v>2164</v>
       </c>
       <c r="P264" t="n">
-        <v>1838</v>
+        <v>1993</v>
       </c>
       <c r="Q264" t="n">
         <v>3044</v>
@@ -20097,7 +20095,7 @@
         <v>5986</v>
       </c>
       <c r="P269" t="n">
-        <v>5695</v>
+        <v>6519</v>
       </c>
       <c r="Q269" t="n">
         <v>7429</v>
@@ -20725,7 +20723,7 @@
         <v>4586</v>
       </c>
       <c r="P277" t="n">
-        <v>5097</v>
+        <v>4991</v>
       </c>
       <c r="Q277" t="n">
         <v>8427</v>
@@ -21163,7 +21161,7 @@
         <v>84</v>
       </c>
       <c r="P283" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="Q283" t="n">
         <v>807</v>
@@ -21317,13 +21315,13 @@
         <v>5453</v>
       </c>
       <c r="P285" t="n">
-        <v>5710</v>
+        <v>5717</v>
       </c>
       <c r="Q285" t="n">
-        <v>5710</v>
+        <v>5717</v>
       </c>
       <c r="R285" t="n">
-        <v>79.63</v>
+        <v>79.73</v>
       </c>
       <c r="S285" t="n">
         <v>8</v>
@@ -21337,10 +21335,10 @@
         <v>5400.05</v>
       </c>
       <c r="V285" t="n">
-        <v>5.74</v>
+        <v>5.87</v>
       </c>
       <c r="W285" t="n">
-        <v>1.156758388846178</v>
+        <v>1.158919245774676</v>
       </c>
     </row>
     <row r="286">
@@ -21708,7 +21706,7 @@
         <v>3215</v>
       </c>
       <c r="P290" t="n">
-        <v>3051</v>
+        <v>3080</v>
       </c>
       <c r="Q290" t="n">
         <v>3215</v>
@@ -21958,13 +21956,13 @@
         <v>664</v>
       </c>
       <c r="P294" t="n">
-        <v>684</v>
+        <v>734</v>
       </c>
       <c r="Q294" t="n">
-        <v>684</v>
+        <v>734</v>
       </c>
       <c r="R294" t="n">
-        <v>28.62</v>
+        <v>30.71</v>
       </c>
       <c r="S294" t="n">
         <v>8</v>
@@ -22183,7 +22181,7 @@
         <v>250</v>
       </c>
       <c r="P297" t="n">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="Q297" t="n">
         <v>874</v>
@@ -23427,13 +23425,13 @@
         <v>3754</v>
       </c>
       <c r="P313" t="n">
-        <v>4124</v>
+        <v>3696</v>
       </c>
       <c r="Q313" t="n">
-        <v>4124</v>
+        <v>3754</v>
       </c>
       <c r="R313" t="n">
-        <v>41.24</v>
+        <v>37.54</v>
       </c>
       <c r="S313" t="n">
         <v>8</v>
@@ -23447,7 +23445,7 @@
         <v>4882.03</v>
       </c>
       <c r="V313" t="n">
-        <v>-15.53</v>
+        <v>-23.11</v>
       </c>
       <c r="W313" t="inlineStr"/>
     </row>
@@ -25032,13 +25030,13 @@
         <v>4717</v>
       </c>
       <c r="P336" t="n">
-        <v>4813</v>
+        <v>5115</v>
       </c>
       <c r="Q336" t="n">
-        <v>4879</v>
+        <v>5115</v>
       </c>
       <c r="R336" t="n">
-        <v>48.79</v>
+        <v>51.15</v>
       </c>
       <c r="S336" t="n">
         <v>8</v>
@@ -25052,7 +25050,7 @@
         <v>5636</v>
       </c>
       <c r="V336" t="n">
-        <v>-13.43</v>
+        <v>-9.24</v>
       </c>
       <c r="W336" t="inlineStr"/>
     </row>
@@ -25423,7 +25421,7 @@
         <v>4083</v>
       </c>
       <c r="P341" t="n">
-        <v>4005</v>
+        <v>4013</v>
       </c>
       <c r="Q341" t="n">
         <v>4083</v>
@@ -26192,13 +26190,13 @@
         <v>6030</v>
       </c>
       <c r="P352" t="n">
-        <v>9101</v>
+        <v>8182</v>
       </c>
       <c r="Q352" t="n">
-        <v>9101</v>
+        <v>8182</v>
       </c>
       <c r="R352" t="n">
-        <v>90.66</v>
+        <v>81.5</v>
       </c>
       <c r="S352" t="n">
         <v>8</v>
@@ -26212,10 +26210,10 @@
         <v>5603.53</v>
       </c>
       <c r="V352" t="n">
-        <v>62.42</v>
+        <v>46.02</v>
       </c>
       <c r="W352" t="n">
-        <v>1.411270663093019</v>
+        <v>1.375874699173012</v>
       </c>
     </row>
     <row r="353">
@@ -26348,7 +26346,7 @@
         <v>2641</v>
       </c>
       <c r="P354" t="n">
-        <v>3225</v>
+        <v>3164</v>
       </c>
       <c r="Q354" t="n">
         <v>4698</v>
@@ -28145,13 +28143,13 @@
         <v>3531</v>
       </c>
       <c r="P377" t="n">
-        <v>5346</v>
+        <v>5191</v>
       </c>
       <c r="Q377" t="n">
-        <v>5346</v>
+        <v>5191</v>
       </c>
       <c r="R377" t="n">
-        <v>53.46</v>
+        <v>51.91</v>
       </c>
       <c r="S377" t="n">
         <v>8</v>
@@ -28165,10 +28163,10 @@
         <v>4606.28</v>
       </c>
       <c r="V377" t="n">
-        <v>16.06</v>
+        <v>12.69</v>
       </c>
       <c r="W377" t="n">
-        <v>1.260314100124435</v>
+        <v>1.235819760392923</v>
       </c>
     </row>
     <row r="378">
@@ -28380,13 +28378,13 @@
         <v>6423</v>
       </c>
       <c r="P380" t="n">
-        <v>4894</v>
+        <v>6448</v>
       </c>
       <c r="Q380" t="n">
-        <v>6423</v>
+        <v>6448</v>
       </c>
       <c r="R380" t="n">
-        <v>53.52</v>
+        <v>53.73</v>
       </c>
       <c r="S380" t="n">
         <v>8</v>
@@ -28400,10 +28398,10 @@
         <v>4615.14</v>
       </c>
       <c r="V380" t="n">
-        <v>39.17</v>
+        <v>39.71</v>
       </c>
       <c r="W380" t="n">
-        <v>1.357519669612313</v>
+        <v>1.359069471943422</v>
       </c>
     </row>
     <row r="381">
@@ -28459,13 +28457,13 @@
         <v>6570</v>
       </c>
       <c r="P381" t="n">
-        <v>7077</v>
+        <v>7173</v>
       </c>
       <c r="Q381" t="n">
-        <v>7077</v>
+        <v>7173</v>
       </c>
       <c r="R381" t="n">
-        <v>58.98</v>
+        <v>59.78</v>
       </c>
       <c r="S381" t="n">
         <v>8</v>
@@ -28479,7 +28477,7 @@
         <v>7946.24</v>
       </c>
       <c r="V381" t="n">
-        <v>-10.94</v>
+        <v>-9.73</v>
       </c>
       <c r="W381" t="inlineStr"/>
     </row>
@@ -29231,13 +29229,13 @@
         <v>2537</v>
       </c>
       <c r="P391" t="n">
-        <v>2486</v>
+        <v>2905</v>
       </c>
       <c r="Q391" t="n">
-        <v>2537</v>
+        <v>2905</v>
       </c>
       <c r="R391" t="n">
-        <v>42.46</v>
+        <v>48.61</v>
       </c>
       <c r="S391" t="n">
         <v>8</v>
@@ -29251,7 +29249,7 @@
         <v>4096.65</v>
       </c>
       <c r="V391" t="n">
-        <v>-38.07</v>
+        <v>-29.09</v>
       </c>
       <c r="W391" t="inlineStr"/>
     </row>
@@ -29308,7 +29306,7 @@
         <v>7403</v>
       </c>
       <c r="P392" t="n">
-        <v>6105</v>
+        <v>5725</v>
       </c>
       <c r="Q392" t="n">
         <v>7403</v>
@@ -29462,13 +29460,13 @@
         <v>172</v>
       </c>
       <c r="P394" t="n">
-        <v>1133</v>
+        <v>1020</v>
       </c>
       <c r="Q394" t="n">
-        <v>1133</v>
+        <v>1020</v>
       </c>
       <c r="R394" t="n">
-        <v>11.33</v>
+        <v>10.2</v>
       </c>
       <c r="S394" t="n">
         <v>8</v>
@@ -29482,10 +29480,10 @@
         <v>182.26</v>
       </c>
       <c r="V394" t="n">
-        <v>521.64</v>
+        <v>459.64</v>
       </c>
       <c r="W394" t="n">
-        <v>1.684409079940034</v>
+        <v>1.66674112516283</v>
       </c>
     </row>
     <row r="395">
@@ -29618,7 +29616,7 @@
         <v>5981</v>
       </c>
       <c r="P396" t="n">
-        <v>5776</v>
+        <v>5627</v>
       </c>
       <c r="Q396" t="n">
         <v>5981</v>
@@ -30834,13 +30832,13 @@
         <v>3223</v>
       </c>
       <c r="P412" t="n">
-        <v>3299</v>
+        <v>3500</v>
       </c>
       <c r="Q412" t="n">
-        <v>3299</v>
+        <v>3500</v>
       </c>
       <c r="R412" t="n">
-        <v>32.99</v>
+        <v>35</v>
       </c>
       <c r="S412" t="n">
         <v>8</v>
@@ -30854,7 +30852,7 @@
         <v>5182</v>
       </c>
       <c r="V412" t="n">
-        <v>-36.34</v>
+        <v>-32.46</v>
       </c>
       <c r="W412" t="inlineStr"/>
     </row>
@@ -31300,7 +31298,7 @@
         <v>3854</v>
       </c>
       <c r="P418" t="n">
-        <v>3609</v>
+        <v>3812</v>
       </c>
       <c r="Q418" t="n">
         <v>3854</v>
@@ -33794,13 +33792,13 @@
         <v>4704</v>
       </c>
       <c r="P450" t="n">
-        <v>5077</v>
+        <v>5708</v>
       </c>
       <c r="Q450" t="n">
-        <v>5077</v>
+        <v>5708</v>
       </c>
       <c r="R450" t="n">
-        <v>50.57</v>
+        <v>56.86</v>
       </c>
       <c r="S450" t="n">
         <v>8</v>
@@ -33814,7 +33812,7 @@
         <v>5969.77</v>
       </c>
       <c r="V450" t="n">
-        <v>-14.95</v>
+        <v>-4.38</v>
       </c>
       <c r="W450" t="inlineStr"/>
     </row>
@@ -33950,13 +33948,13 @@
         <v>4114</v>
       </c>
       <c r="P452" t="n">
-        <v>5598</v>
+        <v>6442</v>
       </c>
       <c r="Q452" t="n">
-        <v>5598</v>
+        <v>6442</v>
       </c>
       <c r="R452" t="n">
-        <v>55.98</v>
+        <v>64.42</v>
       </c>
       <c r="S452" t="n">
         <v>8</v>
@@ -33970,10 +33968,10 @@
         <v>4416.41</v>
       </c>
       <c r="V452" t="n">
-        <v>26.75</v>
+        <v>45.87</v>
       </c>
       <c r="W452" t="n">
-        <v>1.315054188517107</v>
+        <v>1.375500423197763</v>
       </c>
     </row>
     <row r="453">
@@ -34339,13 +34337,13 @@
         <v>6391</v>
       </c>
       <c r="P457" t="n">
-        <v>7740</v>
+        <v>6249</v>
       </c>
       <c r="Q457" t="n">
-        <v>7740</v>
+        <v>6391</v>
       </c>
       <c r="R457" t="n">
-        <v>77.40000000000001</v>
+        <v>63.91</v>
       </c>
       <c r="S457" t="n">
         <v>8</v>
@@ -34359,7 +34357,7 @@
         <v>9919.860000000001</v>
       </c>
       <c r="V457" t="n">
-        <v>-21.97</v>
+        <v>-35.57</v>
       </c>
       <c r="W457" t="inlineStr"/>
     </row>
@@ -36983,7 +36981,7 @@
         <v>905</v>
       </c>
       <c r="P491" t="n">
-        <v>930</v>
+        <v>957</v>
       </c>
       <c r="Q491" t="n">
         <v>958</v>
@@ -37607,13 +37605,13 @@
         <v>5058</v>
       </c>
       <c r="P499" t="n">
-        <v>5311</v>
+        <v>6431</v>
       </c>
       <c r="Q499" t="n">
-        <v>5311</v>
+        <v>6431</v>
       </c>
       <c r="R499" t="n">
-        <v>52.9</v>
+        <v>64.06</v>
       </c>
       <c r="S499" t="n">
         <v>8</v>
@@ -37627,7 +37625,7 @@
         <v>6697.48</v>
       </c>
       <c r="V499" t="n">
-        <v>-20.7</v>
+        <v>-3.98</v>
       </c>
       <c r="W499" t="inlineStr"/>
     </row>
@@ -37761,13 +37759,13 @@
         <v>4963</v>
       </c>
       <c r="P501" t="n">
-        <v>5443</v>
+        <v>6149</v>
       </c>
       <c r="Q501" t="n">
-        <v>5443</v>
+        <v>6149</v>
       </c>
       <c r="R501" t="n">
-        <v>41.87</v>
+        <v>47.3</v>
       </c>
       <c r="S501" t="n">
         <v>8</v>
@@ -37781,7 +37779,7 @@
         <v>10552.47</v>
       </c>
       <c r="V501" t="n">
-        <v>-48.42</v>
+        <v>-41.73</v>
       </c>
       <c r="W501" t="inlineStr"/>
     </row>
@@ -38539,7 +38537,7 @@
         <v>7115</v>
       </c>
       <c r="P511" t="n">
-        <v>7358</v>
+        <v>7535</v>
       </c>
       <c r="Q511" t="n">
         <v>8169</v>
@@ -39003,7 +39001,7 @@
         <v>1</v>
       </c>
       <c r="P517" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q517" t="n">
         <v>1</v>
@@ -39935,13 +39933,13 @@
         <v>4832</v>
       </c>
       <c r="P529" t="n">
-        <v>5604</v>
+        <v>5653</v>
       </c>
       <c r="Q529" t="n">
-        <v>5604</v>
+        <v>5653</v>
       </c>
       <c r="R529" t="n">
-        <v>62.27</v>
+        <v>62.81</v>
       </c>
       <c r="S529" t="n">
         <v>8</v>
@@ -39955,7 +39953,7 @@
         <v>5997.18</v>
       </c>
       <c r="V529" t="n">
-        <v>-6.56</v>
+        <v>-5.74</v>
       </c>
       <c r="W529" t="inlineStr"/>
     </row>
@@ -40470,13 +40468,13 @@
         <v>665</v>
       </c>
       <c r="P536" t="n">
-        <v>919</v>
+        <v>876</v>
       </c>
       <c r="Q536" t="n">
-        <v>919</v>
+        <v>876</v>
       </c>
       <c r="R536" t="n">
-        <v>45.95</v>
+        <v>43.8</v>
       </c>
       <c r="S536" t="n">
         <v>8</v>
@@ -40490,7 +40488,7 @@
         <v>1663.67</v>
       </c>
       <c r="V536" t="n">
-        <v>-44.76</v>
+        <v>-47.35</v>
       </c>
       <c r="W536" t="inlineStr"/>
     </row>
@@ -40596,7 +40594,7 @@
         <v>3366</v>
       </c>
       <c r="P538" t="n">
-        <v>3339</v>
+        <v>3485</v>
       </c>
       <c r="Q538" t="n">
         <v>4223</v>
@@ -40959,13 +40957,13 @@
         <v>4608</v>
       </c>
       <c r="P543" t="n">
-        <v>4605</v>
+        <v>4761</v>
       </c>
       <c r="Q543" t="n">
-        <v>4753</v>
+        <v>4761</v>
       </c>
       <c r="R543" t="n">
-        <v>39.61</v>
+        <v>39.68</v>
       </c>
       <c r="S543" t="n">
         <v>8</v>
@@ -40979,7 +40977,7 @@
         <v>7710.35</v>
       </c>
       <c r="V543" t="n">
-        <v>-38.36</v>
+        <v>-38.25</v>
       </c>
       <c r="W543" t="inlineStr"/>
     </row>
@@ -41085,7 +41083,7 @@
         <v>435</v>
       </c>
       <c r="P545" t="n">
-        <v>151</v>
+        <v>113</v>
       </c>
       <c r="Q545" t="n">
         <v>3755</v>
@@ -41162,7 +41160,7 @@
         <v>2804</v>
       </c>
       <c r="P546" t="n">
-        <v>824</v>
+        <v>711</v>
       </c>
       <c r="Q546" t="n">
         <v>5012</v>
@@ -41239,7 +41237,7 @@
         <v>5417</v>
       </c>
       <c r="P547" t="n">
-        <v>2663</v>
+        <v>2415</v>
       </c>
       <c r="Q547" t="n">
         <v>6510</v>
@@ -41316,7 +41314,7 @@
         <v>6861</v>
       </c>
       <c r="P548" t="n">
-        <v>2427</v>
+        <v>2154</v>
       </c>
       <c r="Q548" t="n">
         <v>6861</v>
@@ -41632,7 +41630,7 @@
         <v>3810</v>
       </c>
       <c r="P552" t="n">
-        <v>791</v>
+        <v>610</v>
       </c>
       <c r="Q552" t="n">
         <v>3847</v>
@@ -41908,13 +41906,13 @@
         <v>2857</v>
       </c>
       <c r="P556" t="n">
-        <v>2840</v>
+        <v>3039</v>
       </c>
       <c r="Q556" t="n">
-        <v>2857</v>
+        <v>3039</v>
       </c>
       <c r="R556" t="n">
-        <v>57.14</v>
+        <v>60.78</v>
       </c>
       <c r="S556" t="n">
         <v>8</v>
@@ -41981,7 +41979,7 @@
         <v>529</v>
       </c>
       <c r="P557" t="n">
-        <v>435</v>
+        <v>454</v>
       </c>
       <c r="Q557" t="n">
         <v>603</v>
@@ -42158,13 +42156,13 @@
         <v>1904</v>
       </c>
       <c r="P560" t="n">
-        <v>2338</v>
+        <v>3456</v>
       </c>
       <c r="Q560" t="n">
-        <v>2338</v>
+        <v>3456</v>
       </c>
       <c r="R560" t="n">
-        <v>11.69</v>
+        <v>17.28</v>
       </c>
       <c r="S560" t="n">
         <v>8</v>
@@ -42178,7 +42176,7 @@
         <v>4921.4</v>
       </c>
       <c r="V560" t="n">
-        <v>-52.49</v>
+        <v>-29.78</v>
       </c>
       <c r="W560" t="inlineStr"/>
     </row>
@@ -42675,13 +42673,13 @@
         <v>3465</v>
       </c>
       <c r="P567" t="n">
-        <v>3466</v>
+        <v>3651</v>
       </c>
       <c r="Q567" t="n">
-        <v>3466</v>
+        <v>3651</v>
       </c>
       <c r="R567" t="n">
-        <v>57.77</v>
+        <v>60.85</v>
       </c>
       <c r="S567" t="n">
         <v>8</v>
@@ -42695,7 +42693,7 @@
         <v>8864.719999999999</v>
       </c>
       <c r="V567" t="n">
-        <v>-60.9</v>
+        <v>-58.81</v>
       </c>
       <c r="W567" t="inlineStr"/>
     </row>
@@ -43117,7 +43115,7 @@
         <v>3766</v>
       </c>
       <c r="P573" t="n">
-        <v>2623</v>
+        <v>3008</v>
       </c>
       <c r="Q573" t="n">
         <v>3836</v>
@@ -43194,13 +43192,13 @@
         <v>5101</v>
       </c>
       <c r="P574" t="n">
-        <v>6088</v>
+        <v>6670</v>
       </c>
       <c r="Q574" t="n">
-        <v>6088</v>
+        <v>6670</v>
       </c>
       <c r="R574" t="n">
-        <v>86.97</v>
+        <v>95.29000000000001</v>
       </c>
       <c r="S574" t="n">
         <v>8</v>
@@ -43214,10 +43212,10 @@
         <v>5121.94</v>
       </c>
       <c r="V574" t="n">
-        <v>18.86</v>
+        <v>30.22</v>
       </c>
       <c r="W574" t="n">
-        <v>1.277306554312118</v>
+        <v>1.328488721329958</v>
       </c>
     </row>
     <row r="575">
@@ -44410,13 +44408,13 @@
         <v>2423</v>
       </c>
       <c r="P590" t="n">
-        <v>1970</v>
+        <v>3744</v>
       </c>
       <c r="Q590" t="n">
-        <v>3670</v>
+        <v>3744</v>
       </c>
       <c r="R590" t="n">
-        <v>36.7</v>
+        <v>37.44</v>
       </c>
       <c r="S590" t="n">
         <v>8</v>
@@ -44430,7 +44428,7 @@
         <v>7352.25</v>
       </c>
       <c r="V590" t="n">
-        <v>-50.08</v>
+        <v>-49.08</v>
       </c>
       <c r="W590" t="inlineStr"/>
     </row>
@@ -44795,7 +44793,7 @@
         <v>398</v>
       </c>
       <c r="P595" t="n">
-        <v>349</v>
+        <v>167</v>
       </c>
       <c r="Q595" t="n">
         <v>398</v>
@@ -45421,13 +45419,13 @@
         <v>5124</v>
       </c>
       <c r="P603" t="n">
-        <v>7646</v>
+        <v>7268</v>
       </c>
       <c r="Q603" t="n">
-        <v>7646</v>
+        <v>7268</v>
       </c>
       <c r="R603" t="n">
-        <v>76.45999999999999</v>
+        <v>72.68000000000001</v>
       </c>
       <c r="S603" t="n">
         <v>8</v>
@@ -45441,7 +45439,7 @@
         <v>8054.65</v>
       </c>
       <c r="V603" t="n">
-        <v>-5.07</v>
+        <v>-9.77</v>
       </c>
       <c r="W603" t="inlineStr"/>
     </row>
@@ -45733,13 +45731,13 @@
         <v>6402</v>
       </c>
       <c r="P607" t="n">
-        <v>8600</v>
+        <v>7580</v>
       </c>
       <c r="Q607" t="n">
-        <v>8600</v>
+        <v>7580</v>
       </c>
       <c r="R607" t="n">
-        <v>66.15000000000001</v>
+        <v>58.31</v>
       </c>
       <c r="S607" t="n">
         <v>8</v>
@@ -45753,10 +45751,10 @@
         <v>6560.03</v>
       </c>
       <c r="V607" t="n">
-        <v>31.1</v>
+        <v>15.55</v>
       </c>
       <c r="W607" t="n">
-        <v>1.331670254690158</v>
+        <v>1.256929346364329</v>
       </c>
     </row>
     <row r="608">
@@ -46205,7 +46203,7 @@
         <v>3274</v>
       </c>
       <c r="P613" t="n">
-        <v>2933</v>
+        <v>2532</v>
       </c>
       <c r="Q613" t="n">
         <v>3274</v>
@@ -47235,7 +47233,7 @@
         <v>4097</v>
       </c>
       <c r="P627" t="n">
-        <v>3993</v>
+        <v>3527</v>
       </c>
       <c r="Q627" t="n">
         <v>5528</v>
@@ -48003,13 +48001,13 @@
         <v>447</v>
       </c>
       <c r="P637" t="n">
-        <v>334</v>
+        <v>687</v>
       </c>
       <c r="Q637" t="n">
-        <v>641</v>
+        <v>687</v>
       </c>
       <c r="R637" t="n">
-        <v>10.68</v>
+        <v>11.45</v>
       </c>
       <c r="S637" t="n">
         <v>8</v>
@@ -48023,7 +48021,7 @@
         <v>964.63</v>
       </c>
       <c r="V637" t="n">
-        <v>-33.55</v>
+        <v>-28.78</v>
       </c>
       <c r="W637" t="inlineStr"/>
     </row>
@@ -48396,13 +48394,13 @@
         <v>7734</v>
       </c>
       <c r="P642" t="n">
-        <v>7593</v>
+        <v>8908</v>
       </c>
       <c r="Q642" t="n">
-        <v>8193</v>
+        <v>8908</v>
       </c>
       <c r="R642" t="n">
-        <v>85.69</v>
+        <v>93.17</v>
       </c>
       <c r="S642" t="n">
         <v>8</v>
@@ -48416,10 +48414,10 @@
         <v>7061.23</v>
       </c>
       <c r="V642" t="n">
-        <v>16.03</v>
+        <v>26.15</v>
       </c>
       <c r="W642" t="n">
-        <v>1.260117743582453</v>
+        <v>1.312570505533511</v>
       </c>
     </row>
     <row r="643">
@@ -49249,13 +49247,13 @@
         <v>2379</v>
       </c>
       <c r="P653" t="n">
-        <v>2361</v>
+        <v>2390</v>
       </c>
       <c r="Q653" t="n">
-        <v>2379</v>
+        <v>2390</v>
       </c>
       <c r="R653" t="n">
-        <v>29.74</v>
+        <v>29.88</v>
       </c>
       <c r="S653" t="n">
         <v>8</v>
@@ -49269,7 +49267,7 @@
         <v>7587.32</v>
       </c>
       <c r="V653" t="n">
-        <v>-68.65000000000001</v>
+        <v>-68.5</v>
       </c>
       <c r="W653" t="inlineStr"/>
     </row>
@@ -49482,7 +49480,7 @@
         <v>2204</v>
       </c>
       <c r="P656" t="n">
-        <v>2140</v>
+        <v>2164</v>
       </c>
       <c r="Q656" t="n">
         <v>2204</v>
@@ -50935,7 +50933,7 @@
         <v>4216</v>
       </c>
       <c r="P675" t="n">
-        <v>2632</v>
+        <v>3585</v>
       </c>
       <c r="Q675" t="n">
         <v>5639</v>
@@ -51162,13 +51160,13 @@
         <v>3710</v>
       </c>
       <c r="P678" t="n">
-        <v>3893</v>
+        <v>3955</v>
       </c>
       <c r="Q678" t="n">
-        <v>3893</v>
+        <v>3955</v>
       </c>
       <c r="R678" t="n">
-        <v>77.86</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="S678" t="n">
         <v>8</v>
@@ -51182,10 +51180,10 @@
         <v>3456</v>
       </c>
       <c r="V678" t="n">
-        <v>12.64</v>
+        <v>14.44</v>
       </c>
       <c r="W678" t="n">
-        <v>1.23541325358259</v>
+        <v>1.249196041743603</v>
       </c>
     </row>
     <row r="679">
@@ -51711,7 +51709,7 @@
         <v>4565</v>
       </c>
       <c r="P685" t="n">
-        <v>3615</v>
+        <v>4536</v>
       </c>
       <c r="Q685" t="n">
         <v>5228</v>
@@ -52121,13 +52119,13 @@
         <v>372</v>
       </c>
       <c r="P691" t="n">
-        <v>385</v>
+        <v>687</v>
       </c>
       <c r="Q691" t="n">
-        <v>385</v>
+        <v>687</v>
       </c>
       <c r="R691" t="n">
-        <v>8.949999999999999</v>
+        <v>15.98</v>
       </c>
       <c r="S691" t="n">
         <v>8</v>
@@ -52141,7 +52139,7 @@
         <v>1851.79</v>
       </c>
       <c r="V691" t="n">
-        <v>-79.20999999999999</v>
+        <v>-62.9</v>
       </c>
       <c r="W691" t="inlineStr"/>
     </row>
@@ -53203,13 +53201,13 @@
         <v>2843</v>
       </c>
       <c r="P705" t="n">
-        <v>2632</v>
+        <v>2954</v>
       </c>
       <c r="Q705" t="n">
-        <v>2843</v>
+        <v>2954</v>
       </c>
       <c r="R705" t="n">
-        <v>40.61</v>
+        <v>42.2</v>
       </c>
       <c r="S705" t="n">
         <v>8</v>
@@ -53223,9 +53221,11 @@
         <v>2866.48</v>
       </c>
       <c r="V705" t="n">
-        <v>-0.82</v>
-      </c>
-      <c r="W705" t="inlineStr"/>
+        <v>3.05</v>
+      </c>
+      <c r="W705" t="n">
+        <v>1.097383232121901</v>
+      </c>
     </row>
     <row r="706">
       <c r="A706" t="inlineStr">
@@ -54135,13 +54135,13 @@
         <v>9341</v>
       </c>
       <c r="P717" t="n">
-        <v>7740</v>
+        <v>9639</v>
       </c>
       <c r="Q717" t="n">
-        <v>9341</v>
+        <v>9639</v>
       </c>
       <c r="R717" t="n">
-        <v>87.3</v>
+        <v>90.08</v>
       </c>
       <c r="S717" t="n">
         <v>8</v>
@@ -54155,7 +54155,7 @@
         <v>9694.15</v>
       </c>
       <c r="V717" t="n">
-        <v>-3.64</v>
+        <v>-0.57</v>
       </c>
       <c r="W717" t="inlineStr"/>
     </row>
@@ -54370,7 +54370,7 @@
         <v>1355</v>
       </c>
       <c r="P720" t="n">
-        <v>1276</v>
+        <v>1334</v>
       </c>
       <c r="Q720" t="n">
         <v>1486</v>
@@ -54757,7 +54757,7 @@
         <v>4643</v>
       </c>
       <c r="P725" t="n">
-        <v>4352</v>
+        <v>4422</v>
       </c>
       <c r="Q725" t="n">
         <v>4643</v>
@@ -55454,7 +55454,7 @@
         <v>6867</v>
       </c>
       <c r="P734" t="n">
-        <v>6286</v>
+        <v>6370</v>
       </c>
       <c r="Q734" t="n">
         <v>7742</v>
@@ -56234,13 +56234,13 @@
         <v>1267</v>
       </c>
       <c r="P744" t="n">
-        <v>1400</v>
+        <v>1746</v>
       </c>
       <c r="Q744" t="n">
-        <v>1610</v>
+        <v>1746</v>
       </c>
       <c r="R744" t="n">
-        <v>13.42</v>
+        <v>14.55</v>
       </c>
       <c r="S744" t="n">
         <v>8</v>
@@ -56254,7 +56254,7 @@
         <v>11460.22</v>
       </c>
       <c r="V744" t="n">
-        <v>-85.95</v>
+        <v>-84.76000000000001</v>
       </c>
       <c r="W744" t="inlineStr"/>
     </row>
@@ -56311,7 +56311,7 @@
         <v>6356</v>
       </c>
       <c r="P745" t="n">
-        <v>7070</v>
+        <v>6822</v>
       </c>
       <c r="Q745" t="n">
         <v>11079</v>
@@ -56465,7 +56465,7 @@
         <v>3932</v>
       </c>
       <c r="P747" t="n">
-        <v>4043</v>
+        <v>4054</v>
       </c>
       <c r="Q747" t="n">
         <v>5457</v>
@@ -56542,7 +56542,7 @@
         <v>7046</v>
       </c>
       <c r="P748" t="n">
-        <v>6620</v>
+        <v>6912</v>
       </c>
       <c r="Q748" t="n">
         <v>7787</v>
@@ -56619,7 +56619,7 @@
         <v>2365</v>
       </c>
       <c r="P749" t="n">
-        <v>2986</v>
+        <v>2753</v>
       </c>
       <c r="Q749" t="n">
         <v>4293</v>
@@ -56692,7 +56692,7 @@
         <v>4170</v>
       </c>
       <c r="P750" t="n">
-        <v>3820</v>
+        <v>4002</v>
       </c>
       <c r="Q750" t="n">
         <v>5747</v>
@@ -56771,7 +56771,7 @@
         <v>5858</v>
       </c>
       <c r="P751" t="n">
-        <v>4788</v>
+        <v>4821</v>
       </c>
       <c r="Q751" t="n">
         <v>5858</v>
@@ -56848,7 +56848,7 @@
         <v>5114</v>
       </c>
       <c r="P752" t="n">
-        <v>2143</v>
+        <v>1917</v>
       </c>
       <c r="Q752" t="n">
         <v>5114</v>
@@ -56921,7 +56921,7 @@
         <v>1154</v>
       </c>
       <c r="P753" t="n">
-        <v>1089</v>
+        <v>910</v>
       </c>
       <c r="Q753" t="n">
         <v>1431</v>
@@ -60017,7 +60017,7 @@
         <v>1241</v>
       </c>
       <c r="P795" t="n">
-        <v>325</v>
+        <v>1699</v>
       </c>
       <c r="Q795" t="n">
         <v>1907</v>
@@ -60327,13 +60327,13 @@
         <v>3990</v>
       </c>
       <c r="P799" t="n">
-        <v>4057</v>
+        <v>4082</v>
       </c>
       <c r="Q799" t="n">
-        <v>4057</v>
+        <v>4082</v>
       </c>
       <c r="R799" t="n">
-        <v>40.57</v>
+        <v>40.82</v>
       </c>
       <c r="S799" t="n">
         <v>8</v>
@@ -60347,7 +60347,7 @@
         <v>4577.98</v>
       </c>
       <c r="V799" t="n">
-        <v>-11.38</v>
+        <v>-10.83</v>
       </c>
       <c r="W799" t="inlineStr"/>
     </row>
@@ -61470,7 +61470,7 @@
         <v>128</v>
       </c>
       <c r="P814" t="n">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="Q814" t="n">
         <v>4173</v>
@@ -62287,13 +62287,13 @@
         <v>5628</v>
       </c>
       <c r="P827" t="n">
-        <v>5802</v>
+        <v>5870</v>
       </c>
       <c r="Q827" t="n">
-        <v>5802</v>
+        <v>5870</v>
       </c>
       <c r="R827" t="n">
-        <v>95.19</v>
+        <v>96.31</v>
       </c>
       <c r="S827" t="n">
         <v>8</v>
@@ -62307,9 +62307,11 @@
         <v>5848.46</v>
       </c>
       <c r="V827" t="n">
-        <v>-0.79</v>
-      </c>
-      <c r="W827" t="inlineStr"/>
+        <v>0.37</v>
+      </c>
+      <c r="W827" t="n">
+        <v>0.9204852005013249</v>
+      </c>
     </row>
     <row r="828">
       <c r="A828" t="inlineStr">
@@ -62520,13 +62522,13 @@
         <v>7717</v>
       </c>
       <c r="P830" t="n">
-        <v>7874</v>
+        <v>8001</v>
       </c>
       <c r="Q830" t="n">
-        <v>7907</v>
+        <v>8001</v>
       </c>
       <c r="R830" t="n">
-        <v>88.20999999999999</v>
+        <v>89.26000000000001</v>
       </c>
       <c r="S830" t="n">
         <v>8</v>
@@ -62540,7 +62542,7 @@
         <v>8427.66</v>
       </c>
       <c r="V830" t="n">
-        <v>-6.18</v>
+        <v>-5.06</v>
       </c>
       <c r="W830" t="inlineStr"/>
     </row>
@@ -62674,7 +62676,7 @@
         <v>7806</v>
       </c>
       <c r="P832" t="n">
-        <v>6618</v>
+        <v>7480</v>
       </c>
       <c r="Q832" t="n">
         <v>7806</v>
@@ -62753,7 +62755,7 @@
         <v>258</v>
       </c>
       <c r="P833" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q833" t="n">
         <v>3542</v>
@@ -62832,13 +62834,13 @@
         <v>7814</v>
       </c>
       <c r="P834" t="n">
-        <v>7948</v>
+        <v>8116</v>
       </c>
       <c r="Q834" t="n">
-        <v>7948</v>
+        <v>8116</v>
       </c>
       <c r="R834" t="n">
-        <v>55.58</v>
+        <v>56.76</v>
       </c>
       <c r="S834" t="n">
         <v>8</v>
@@ -62852,7 +62854,7 @@
         <v>8251.459999999999</v>
       </c>
       <c r="V834" t="n">
-        <v>-3.68</v>
+        <v>-1.64</v>
       </c>
       <c r="W834" t="inlineStr"/>
     </row>
@@ -62909,13 +62911,13 @@
         <v>1722</v>
       </c>
       <c r="P835" t="n">
-        <v>1642</v>
+        <v>1891</v>
       </c>
       <c r="Q835" t="n">
-        <v>1722</v>
+        <v>1891</v>
       </c>
       <c r="R835" t="n">
-        <v>19.13</v>
+        <v>21.01</v>
       </c>
       <c r="S835" t="n">
         <v>8</v>
@@ -62929,7 +62931,7 @@
         <v>3162.28</v>
       </c>
       <c r="V835" t="n">
-        <v>-45.55</v>
+        <v>-40.2</v>
       </c>
       <c r="W835" t="inlineStr"/>
     </row>
@@ -64769,7 +64771,7 @@
         <v>10395</v>
       </c>
       <c r="P859" t="n">
-        <v>9232</v>
+        <v>9640</v>
       </c>
       <c r="Q859" t="n">
         <v>10395</v>

--- a/Taxa de Crescimento.xlsx
+++ b/Taxa de Crescimento.xlsx
@@ -677,13 +677,13 @@
         <v>2102</v>
       </c>
       <c r="P3" t="n">
-        <v>2107</v>
+        <v>2131</v>
       </c>
       <c r="Q3" t="n">
-        <v>2107</v>
+        <v>2131</v>
       </c>
       <c r="R3" t="n">
-        <v>33.71</v>
+        <v>34.1</v>
       </c>
       <c r="S3" t="n">
         <v>8</v>
@@ -697,10 +697,10 @@
         <v>1921.26</v>
       </c>
       <c r="V3" t="n">
-        <v>9.67</v>
+        <v>10.92</v>
       </c>
       <c r="W3" t="n">
-        <v>1.208144476913952</v>
+        <v>1.220445957467314</v>
       </c>
     </row>
     <row r="4">
@@ -1369,13 +1369,13 @@
         <v>1036</v>
       </c>
       <c r="P13" t="n">
-        <v>1366</v>
+        <v>1539</v>
       </c>
       <c r="Q13" t="n">
-        <v>1366</v>
+        <v>1539</v>
       </c>
       <c r="R13" t="n">
-        <v>45.53</v>
+        <v>51.3</v>
       </c>
       <c r="S13" t="n">
         <v>8</v>
@@ -1389,9 +1389,11 @@
         <v>1471.72</v>
       </c>
       <c r="V13" t="n">
-        <v>-7.18</v>
-      </c>
-      <c r="W13" t="inlineStr"/>
+        <v>4.57</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.134992565179017</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1681,7 +1683,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1377</v>
+        <v>1520</v>
       </c>
       <c r="Q17" t="n">
         <v>4925</v>
@@ -1760,7 +1762,7 @@
         <v>14925</v>
       </c>
       <c r="P18" t="n">
-        <v>15662</v>
+        <v>15851</v>
       </c>
       <c r="Q18" t="n">
         <v>28370</v>
@@ -2330,13 +2332,13 @@
         <v>9466</v>
       </c>
       <c r="P26" t="n">
-        <v>9373</v>
+        <v>9471</v>
       </c>
       <c r="Q26" t="n">
-        <v>9466</v>
+        <v>9471</v>
       </c>
       <c r="R26" t="n">
-        <v>75.73</v>
+        <v>75.77</v>
       </c>
       <c r="S26" t="n">
         <v>8</v>
@@ -2350,10 +2352,10 @@
         <v>8440.110000000001</v>
       </c>
       <c r="V26" t="n">
-        <v>12.15</v>
+        <v>12.21</v>
       </c>
       <c r="W26" t="n">
-        <v>1.231349551380652</v>
+        <v>1.231855136280941</v>
       </c>
     </row>
     <row r="27">
@@ -3061,13 +3063,13 @@
         <v>2175</v>
       </c>
       <c r="P37" t="n">
-        <v>2251</v>
+        <v>2265</v>
       </c>
       <c r="Q37" t="n">
-        <v>2251</v>
+        <v>2265</v>
       </c>
       <c r="R37" t="n">
-        <v>75.03</v>
+        <v>75.5</v>
       </c>
       <c r="S37" t="n">
         <v>8</v>
@@ -3081,10 +3083,10 @@
         <v>2077.14</v>
       </c>
       <c r="V37" t="n">
-        <v>8.369999999999999</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="W37" t="n">
-        <v>1.19369613630525</v>
+        <v>1.20138084314864</v>
       </c>
     </row>
     <row r="38">
@@ -3811,13 +3813,13 @@
         <v>3477</v>
       </c>
       <c r="P47" t="n">
-        <v>4333</v>
+        <v>4079</v>
       </c>
       <c r="Q47" t="n">
-        <v>4333</v>
+        <v>4079</v>
       </c>
       <c r="R47" t="n">
-        <v>28.89</v>
+        <v>27.19</v>
       </c>
       <c r="S47" t="n">
         <v>8</v>
@@ -3831,7 +3833,7 @@
         <v>4438.47</v>
       </c>
       <c r="V47" t="n">
-        <v>-2.38</v>
+        <v>-8.1</v>
       </c>
       <c r="W47" t="inlineStr"/>
     </row>
@@ -5545,7 +5547,7 @@
         <v>12752</v>
       </c>
       <c r="P71" t="n">
-        <v>11260</v>
+        <v>11158</v>
       </c>
       <c r="Q71" t="n">
         <v>12752</v>
@@ -5622,13 +5624,13 @@
         <v>19630</v>
       </c>
       <c r="P72" t="n">
-        <v>23482</v>
+        <v>24431</v>
       </c>
       <c r="Q72" t="n">
-        <v>23482</v>
+        <v>24431</v>
       </c>
       <c r="R72" t="n">
-        <v>93.93000000000001</v>
+        <v>97.72</v>
       </c>
       <c r="S72" t="n">
         <v>8</v>
@@ -5642,10 +5644,10 @@
         <v>20423.33</v>
       </c>
       <c r="V72" t="n">
-        <v>14.98</v>
+        <v>19.62</v>
       </c>
       <c r="W72" t="n">
-        <v>1.253023793351216</v>
+        <v>1.281518608825801</v>
       </c>
     </row>
     <row r="73">
@@ -7803,7 +7805,7 @@
         <v>3522</v>
       </c>
       <c r="P101" t="n">
-        <v>3348</v>
+        <v>3414</v>
       </c>
       <c r="Q101" t="n">
         <v>3576</v>
@@ -8231,7 +8233,7 @@
         <v>27513</v>
       </c>
       <c r="P107" t="n">
-        <v>12812</v>
+        <v>12281</v>
       </c>
       <c r="Q107" t="n">
         <v>27513</v>
@@ -8310,7 +8312,7 @@
         <v>9607</v>
       </c>
       <c r="P108" t="n">
-        <v>3269</v>
+        <v>2863</v>
       </c>
       <c r="Q108" t="n">
         <v>9607</v>
@@ -10615,13 +10617,13 @@
         <v>22643</v>
       </c>
       <c r="P141" t="n">
-        <v>23453</v>
+        <v>23750</v>
       </c>
       <c r="Q141" t="n">
-        <v>23453</v>
+        <v>23750</v>
       </c>
       <c r="R141" t="n">
-        <v>93.81</v>
+        <v>95</v>
       </c>
       <c r="S141" t="n">
         <v>8</v>
@@ -10635,10 +10637,10 @@
         <v>19800.02</v>
       </c>
       <c r="V141" t="n">
-        <v>18.45</v>
+        <v>19.95</v>
       </c>
       <c r="W141" t="n">
-        <v>1.274969212007679</v>
+        <v>1.283301125039289</v>
       </c>
     </row>
     <row r="142">
@@ -10773,7 +10775,7 @@
         <v>4729</v>
       </c>
       <c r="P143" t="n">
-        <v>5067</v>
+        <v>5101</v>
       </c>
       <c r="Q143" t="n">
         <v>5336</v>
@@ -13264,7 +13266,7 @@
         <v>6068</v>
       </c>
       <c r="P178" t="n">
-        <v>2859</v>
+        <v>2762</v>
       </c>
       <c r="Q178" t="n">
         <v>6068</v>
@@ -16129,7 +16131,7 @@
         <v>13013</v>
       </c>
       <c r="P217" t="n">
-        <v>12581</v>
+        <v>12753</v>
       </c>
       <c r="Q217" t="n">
         <v>13013</v>
@@ -17514,7 +17516,7 @@
         <v>6622</v>
       </c>
       <c r="P236" t="n">
-        <v>5941</v>
+        <v>5991</v>
       </c>
       <c r="Q236" t="n">
         <v>6622</v>
@@ -17826,13 +17828,13 @@
         <v>1844</v>
       </c>
       <c r="P240" t="n">
-        <v>1863</v>
+        <v>1865</v>
       </c>
       <c r="Q240" t="n">
-        <v>1863</v>
+        <v>1865</v>
       </c>
       <c r="R240" t="n">
-        <v>46.39</v>
+        <v>46.44</v>
       </c>
       <c r="S240" t="n">
         <v>8</v>
@@ -17846,10 +17848,10 @@
         <v>1673.48</v>
       </c>
       <c r="V240" t="n">
-        <v>11.32</v>
+        <v>11.44</v>
       </c>
       <c r="W240" t="n">
-        <v>1.22411025306201</v>
+        <v>1.225186403850716</v>
       </c>
     </row>
     <row r="241">
@@ -18217,7 +18219,7 @@
         <v>7078</v>
       </c>
       <c r="P245" t="n">
-        <v>6131</v>
+        <v>5819</v>
       </c>
       <c r="Q245" t="n">
         <v>7078</v>
@@ -18296,7 +18298,7 @@
         <v>7330</v>
       </c>
       <c r="P246" t="n">
-        <v>5759</v>
+        <v>5618</v>
       </c>
       <c r="Q246" t="n">
         <v>7330</v>
@@ -18373,7 +18375,7 @@
         <v>3733</v>
       </c>
       <c r="P247" t="n">
-        <v>2660</v>
+        <v>2643</v>
       </c>
       <c r="Q247" t="n">
         <v>3733</v>
@@ -18450,7 +18452,7 @@
         <v>3899</v>
       </c>
       <c r="P248" t="n">
-        <v>2946</v>
+        <v>2850</v>
       </c>
       <c r="Q248" t="n">
         <v>3899</v>
@@ -18606,7 +18608,7 @@
         <v>4579</v>
       </c>
       <c r="P250" t="n">
-        <v>4327</v>
+        <v>4199</v>
       </c>
       <c r="Q250" t="n">
         <v>4579</v>
@@ -19623,7 +19625,7 @@
         <v>1054</v>
       </c>
       <c r="P263" t="n">
-        <v>1009</v>
+        <v>1038</v>
       </c>
       <c r="Q263" t="n">
         <v>1371</v>
@@ -19779,13 +19781,13 @@
         <v>4353</v>
       </c>
       <c r="P265" t="n">
-        <v>4488</v>
+        <v>4533</v>
       </c>
       <c r="Q265" t="n">
-        <v>4488</v>
+        <v>4533</v>
       </c>
       <c r="R265" t="n">
-        <v>89.41</v>
+        <v>90.31</v>
       </c>
       <c r="S265" t="n">
         <v>8</v>
@@ -19799,10 +19801,10 @@
         <v>3859</v>
       </c>
       <c r="V265" t="n">
-        <v>16.3</v>
+        <v>17.47</v>
       </c>
       <c r="W265" t="n">
-        <v>1.261872958581617</v>
+        <v>1.269183474639503</v>
       </c>
     </row>
     <row r="266">
@@ -20016,13 +20018,13 @@
         <v>6086</v>
       </c>
       <c r="P268" t="n">
-        <v>6309</v>
+        <v>6514</v>
       </c>
       <c r="Q268" t="n">
-        <v>6309</v>
+        <v>6514</v>
       </c>
       <c r="R268" t="n">
-        <v>78.86</v>
+        <v>81.42</v>
       </c>
       <c r="S268" t="n">
         <v>8</v>
@@ -20036,10 +20038,10 @@
         <v>5833.81</v>
       </c>
       <c r="V268" t="n">
-        <v>8.15</v>
+        <v>11.66</v>
       </c>
       <c r="W268" t="n">
-        <v>1.191049471472839</v>
+        <v>1.227132747330455</v>
       </c>
     </row>
     <row r="269">
@@ -20172,13 +20174,13 @@
         <v>2312</v>
       </c>
       <c r="P270" t="n">
-        <v>2398</v>
+        <v>2428</v>
       </c>
       <c r="Q270" t="n">
-        <v>2398</v>
+        <v>2428</v>
       </c>
       <c r="R270" t="n">
-        <v>59.95</v>
+        <v>60.7</v>
       </c>
       <c r="S270" t="n">
         <v>8</v>
@@ -20192,10 +20194,10 @@
         <v>1570.9</v>
       </c>
       <c r="V270" t="n">
-        <v>52.65</v>
+        <v>54.56</v>
       </c>
       <c r="W270" t="n">
-        <v>1.391393161806551</v>
+        <v>1.395531134604049</v>
       </c>
     </row>
     <row r="271">
@@ -20567,7 +20569,7 @@
         <v>4999</v>
       </c>
       <c r="P275" t="n">
-        <v>5018</v>
+        <v>5031</v>
       </c>
       <c r="Q275" t="n">
         <v>5324</v>
@@ -20646,7 +20648,7 @@
         <v>4413</v>
       </c>
       <c r="P276" t="n">
-        <v>4307</v>
+        <v>4400</v>
       </c>
       <c r="Q276" t="n">
         <v>4413</v>
@@ -21161,7 +21163,7 @@
         <v>84</v>
       </c>
       <c r="P283" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Q283" t="n">
         <v>807</v>
@@ -21238,7 +21240,7 @@
         <v>886</v>
       </c>
       <c r="P284" t="n">
-        <v>914</v>
+        <v>829</v>
       </c>
       <c r="Q284" t="n">
         <v>2450</v>
@@ -22102,13 +22104,13 @@
         <v>2181</v>
       </c>
       <c r="P296" t="n">
-        <v>2249</v>
+        <v>2268</v>
       </c>
       <c r="Q296" t="n">
-        <v>2249</v>
+        <v>2268</v>
       </c>
       <c r="R296" t="n">
-        <v>74.97</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="S296" t="n">
         <v>8</v>
@@ -22122,10 +22124,10 @@
         <v>2083.14</v>
       </c>
       <c r="V296" t="n">
-        <v>7.96</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="W296" t="n">
-        <v>1.188710472869853</v>
+        <v>1.199481723432723</v>
       </c>
     </row>
     <row r="297">
@@ -22181,7 +22183,7 @@
         <v>250</v>
       </c>
       <c r="P297" t="n">
-        <v>253</v>
+        <v>492</v>
       </c>
       <c r="Q297" t="n">
         <v>874</v>
@@ -25107,13 +25109,13 @@
         <v>5311</v>
       </c>
       <c r="P337" t="n">
-        <v>6185</v>
+        <v>6850</v>
       </c>
       <c r="Q337" t="n">
-        <v>6185</v>
+        <v>6850</v>
       </c>
       <c r="R337" t="n">
-        <v>51.54</v>
+        <v>57.08</v>
       </c>
       <c r="S337" t="n">
         <v>8</v>
@@ -25127,10 +25129,10 @@
         <v>4336.29</v>
       </c>
       <c r="V337" t="n">
-        <v>42.63</v>
+        <v>57.97</v>
       </c>
       <c r="W337" t="n">
-        <v>1.367129362810221</v>
+        <v>1.402599269468085</v>
       </c>
     </row>
     <row r="338">
@@ -26190,13 +26192,13 @@
         <v>6030</v>
       </c>
       <c r="P352" t="n">
-        <v>8182</v>
+        <v>7979</v>
       </c>
       <c r="Q352" t="n">
-        <v>8182</v>
+        <v>7979</v>
       </c>
       <c r="R352" t="n">
-        <v>81.5</v>
+        <v>79.48</v>
       </c>
       <c r="S352" t="n">
         <v>8</v>
@@ -26210,10 +26212,10 @@
         <v>5603.53</v>
       </c>
       <c r="V352" t="n">
-        <v>46.02</v>
+        <v>42.39</v>
       </c>
       <c r="W352" t="n">
-        <v>1.375874699173012</v>
+        <v>1.366486308733027</v>
       </c>
     </row>
     <row r="353">
@@ -26346,7 +26348,7 @@
         <v>2641</v>
       </c>
       <c r="P354" t="n">
-        <v>3164</v>
+        <v>2962</v>
       </c>
       <c r="Q354" t="n">
         <v>4698</v>
@@ -27124,13 +27126,13 @@
         <v>2223</v>
       </c>
       <c r="P364" t="n">
-        <v>2106</v>
+        <v>2702</v>
       </c>
       <c r="Q364" t="n">
-        <v>2223</v>
+        <v>2702</v>
       </c>
       <c r="R364" t="n">
-        <v>22.23</v>
+        <v>27.02</v>
       </c>
       <c r="S364" t="n">
         <v>8</v>
@@ -27144,7 +27146,7 @@
         <v>4630.52</v>
       </c>
       <c r="V364" t="n">
-        <v>-51.99</v>
+        <v>-41.65</v>
       </c>
       <c r="W364" t="inlineStr"/>
     </row>
@@ -28143,13 +28145,13 @@
         <v>3531</v>
       </c>
       <c r="P377" t="n">
-        <v>5191</v>
+        <v>5100</v>
       </c>
       <c r="Q377" t="n">
-        <v>5191</v>
+        <v>5100</v>
       </c>
       <c r="R377" t="n">
-        <v>51.91</v>
+        <v>51</v>
       </c>
       <c r="S377" t="n">
         <v>8</v>
@@ -28163,10 +28165,10 @@
         <v>4606.28</v>
       </c>
       <c r="V377" t="n">
-        <v>12.69</v>
+        <v>10.72</v>
       </c>
       <c r="W377" t="n">
-        <v>1.235819760392923</v>
+        <v>1.218567428237834</v>
       </c>
     </row>
     <row r="378">
@@ -28534,7 +28536,7 @@
         <v>5910</v>
       </c>
       <c r="P382" t="n">
-        <v>5163</v>
+        <v>5369</v>
       </c>
       <c r="Q382" t="n">
         <v>5910</v>
@@ -29306,7 +29308,7 @@
         <v>7403</v>
       </c>
       <c r="P392" t="n">
-        <v>5725</v>
+        <v>5593</v>
       </c>
       <c r="Q392" t="n">
         <v>7403</v>
@@ -29383,13 +29385,13 @@
         <v>2485</v>
       </c>
       <c r="P393" t="n">
-        <v>2886</v>
+        <v>2971</v>
       </c>
       <c r="Q393" t="n">
-        <v>2886</v>
+        <v>2971</v>
       </c>
       <c r="R393" t="n">
-        <v>28.86</v>
+        <v>29.71</v>
       </c>
       <c r="S393" t="n">
         <v>8</v>
@@ -29403,7 +29405,7 @@
         <v>3380.62</v>
       </c>
       <c r="V393" t="n">
-        <v>-14.63</v>
+        <v>-12.12</v>
       </c>
       <c r="W393" t="inlineStr"/>
     </row>
@@ -29460,13 +29462,13 @@
         <v>172</v>
       </c>
       <c r="P394" t="n">
-        <v>1020</v>
+        <v>698</v>
       </c>
       <c r="Q394" t="n">
-        <v>1020</v>
+        <v>698</v>
       </c>
       <c r="R394" t="n">
-        <v>10.2</v>
+        <v>6.98</v>
       </c>
       <c r="S394" t="n">
         <v>8</v>
@@ -29480,10 +29482,10 @@
         <v>182.26</v>
       </c>
       <c r="V394" t="n">
-        <v>459.64</v>
+        <v>282.97</v>
       </c>
       <c r="W394" t="n">
-        <v>1.66674112516283</v>
+        <v>1.600706467122624</v>
       </c>
     </row>
     <row r="395">
@@ -29695,13 +29697,13 @@
         <v>1037</v>
       </c>
       <c r="P397" t="n">
-        <v>1486</v>
+        <v>1383</v>
       </c>
       <c r="Q397" t="n">
-        <v>1486</v>
+        <v>1383</v>
       </c>
       <c r="R397" t="n">
-        <v>14.86</v>
+        <v>13.83</v>
       </c>
       <c r="S397" t="n">
         <v>8</v>
@@ -29715,10 +29717,10 @@
         <v>983.04</v>
       </c>
       <c r="V397" t="n">
-        <v>51.16</v>
+        <v>40.69</v>
       </c>
       <c r="W397" t="n">
-        <v>1.388068433753057</v>
+        <v>1.3618333773568</v>
       </c>
     </row>
     <row r="398">
@@ -31298,13 +31300,13 @@
         <v>3854</v>
       </c>
       <c r="P418" t="n">
-        <v>3812</v>
+        <v>4215</v>
       </c>
       <c r="Q418" t="n">
-        <v>3854</v>
+        <v>4215</v>
       </c>
       <c r="R418" t="n">
-        <v>38.54</v>
+        <v>42.15</v>
       </c>
       <c r="S418" t="n">
         <v>8</v>
@@ -31318,7 +31320,7 @@
         <v>7407.03</v>
       </c>
       <c r="V418" t="n">
-        <v>-47.97</v>
+        <v>-43.09</v>
       </c>
       <c r="W418" t="inlineStr"/>
     </row>
@@ -33792,13 +33794,13 @@
         <v>4704</v>
       </c>
       <c r="P450" t="n">
-        <v>5708</v>
+        <v>5716</v>
       </c>
       <c r="Q450" t="n">
-        <v>5708</v>
+        <v>5716</v>
       </c>
       <c r="R450" t="n">
-        <v>56.86</v>
+        <v>56.94</v>
       </c>
       <c r="S450" t="n">
         <v>8</v>
@@ -33812,7 +33814,7 @@
         <v>5969.77</v>
       </c>
       <c r="V450" t="n">
-        <v>-4.38</v>
+        <v>-4.25</v>
       </c>
       <c r="W450" t="inlineStr"/>
     </row>
@@ -33948,13 +33950,13 @@
         <v>4114</v>
       </c>
       <c r="P452" t="n">
-        <v>6442</v>
+        <v>6837</v>
       </c>
       <c r="Q452" t="n">
-        <v>6442</v>
+        <v>6837</v>
       </c>
       <c r="R452" t="n">
-        <v>64.42</v>
+        <v>68.37</v>
       </c>
       <c r="S452" t="n">
         <v>8</v>
@@ -33968,10 +33970,10 @@
         <v>4416.41</v>
       </c>
       <c r="V452" t="n">
-        <v>45.87</v>
+        <v>54.81</v>
       </c>
       <c r="W452" t="n">
-        <v>1.375500423197763</v>
+        <v>1.396062892028175</v>
       </c>
     </row>
     <row r="453">
@@ -35498,13 +35500,13 @@
         <v>2969</v>
       </c>
       <c r="P472" t="n">
-        <v>3423</v>
+        <v>5619</v>
       </c>
       <c r="Q472" t="n">
-        <v>3423</v>
+        <v>5619</v>
       </c>
       <c r="R472" t="n">
-        <v>42.79</v>
+        <v>70.23999999999999</v>
       </c>
       <c r="S472" t="n">
         <v>8</v>
@@ -35518,7 +35520,7 @@
         <v>5789.98</v>
       </c>
       <c r="V472" t="n">
-        <v>-40.88</v>
+        <v>-2.95</v>
       </c>
       <c r="W472" t="inlineStr"/>
     </row>
@@ -35731,13 +35733,13 @@
         <v>5733</v>
       </c>
       <c r="P475" t="n">
-        <v>6132</v>
+        <v>7796</v>
       </c>
       <c r="Q475" t="n">
-        <v>6132</v>
+        <v>7796</v>
       </c>
       <c r="R475" t="n">
-        <v>61.32</v>
+        <v>77.95999999999999</v>
       </c>
       <c r="S475" t="n">
         <v>8</v>
@@ -35751,9 +35753,11 @@
         <v>6786.37</v>
       </c>
       <c r="V475" t="n">
-        <v>-9.640000000000001</v>
-      </c>
-      <c r="W475" t="inlineStr"/>
+        <v>14.88</v>
+      </c>
+      <c r="W475" t="n">
+        <v>1.252324597746059</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -38537,13 +38541,13 @@
         <v>7115</v>
       </c>
       <c r="P511" t="n">
-        <v>7535</v>
+        <v>8280</v>
       </c>
       <c r="Q511" t="n">
-        <v>8169</v>
+        <v>8280</v>
       </c>
       <c r="R511" t="n">
-        <v>81.69</v>
+        <v>82.8</v>
       </c>
       <c r="S511" t="n">
         <v>8</v>
@@ -38557,7 +38561,7 @@
         <v>9717.57</v>
       </c>
       <c r="V511" t="n">
-        <v>-15.94</v>
+        <v>-14.79</v>
       </c>
       <c r="W511" t="inlineStr"/>
     </row>
@@ -39311,13 +39315,13 @@
         <v>4667</v>
       </c>
       <c r="P521" t="n">
-        <v>4666</v>
+        <v>4816</v>
       </c>
       <c r="Q521" t="n">
-        <v>4712</v>
+        <v>4816</v>
       </c>
       <c r="R521" t="n">
-        <v>47.12</v>
+        <v>48.16</v>
       </c>
       <c r="S521" t="n">
         <v>8</v>
@@ -39331,10 +39335,10 @@
         <v>4539.56</v>
       </c>
       <c r="V521" t="n">
-        <v>3.8</v>
+        <v>6.09</v>
       </c>
       <c r="W521" t="n">
-        <v>1.11767438985762</v>
+        <v>1.162478085141094</v>
       </c>
     </row>
     <row r="522">
@@ -41160,7 +41164,7 @@
         <v>2804</v>
       </c>
       <c r="P546" t="n">
-        <v>711</v>
+        <v>688</v>
       </c>
       <c r="Q546" t="n">
         <v>5012</v>
@@ -41237,7 +41241,7 @@
         <v>5417</v>
       </c>
       <c r="P547" t="n">
-        <v>2415</v>
+        <v>2274</v>
       </c>
       <c r="Q547" t="n">
         <v>6510</v>
@@ -41472,7 +41476,7 @@
         <v>6600</v>
       </c>
       <c r="P550" t="n">
-        <v>5751</v>
+        <v>5188</v>
       </c>
       <c r="Q550" t="n">
         <v>8472</v>
@@ -41551,7 +41555,7 @@
         <v>3233</v>
       </c>
       <c r="P551" t="n">
-        <v>2219</v>
+        <v>742</v>
       </c>
       <c r="Q551" t="n">
         <v>3752</v>
@@ -41979,7 +41983,7 @@
         <v>529</v>
       </c>
       <c r="P557" t="n">
-        <v>454</v>
+        <v>435</v>
       </c>
       <c r="Q557" t="n">
         <v>603</v>
@@ -42156,13 +42160,13 @@
         <v>1904</v>
       </c>
       <c r="P560" t="n">
-        <v>3456</v>
+        <v>3563</v>
       </c>
       <c r="Q560" t="n">
-        <v>3456</v>
+        <v>3563</v>
       </c>
       <c r="R560" t="n">
-        <v>17.28</v>
+        <v>17.82</v>
       </c>
       <c r="S560" t="n">
         <v>8</v>
@@ -42176,7 +42180,7 @@
         <v>4921.4</v>
       </c>
       <c r="V560" t="n">
-        <v>-29.78</v>
+        <v>-27.6</v>
       </c>
       <c r="W560" t="inlineStr"/>
     </row>
@@ -43115,7 +43119,7 @@
         <v>3766</v>
       </c>
       <c r="P573" t="n">
-        <v>3008</v>
+        <v>2695</v>
       </c>
       <c r="Q573" t="n">
         <v>3836</v>
@@ -43350,13 +43354,13 @@
         <v>4368</v>
       </c>
       <c r="P576" t="n">
-        <v>4456</v>
+        <v>4606</v>
       </c>
       <c r="Q576" t="n">
-        <v>4456</v>
+        <v>4606</v>
       </c>
       <c r="R576" t="n">
-        <v>67.55</v>
+        <v>69.81999999999999</v>
       </c>
       <c r="S576" t="n">
         <v>8</v>
@@ -43370,7 +43374,7 @@
         <v>5866.41</v>
       </c>
       <c r="V576" t="n">
-        <v>-24.04</v>
+        <v>-21.49</v>
       </c>
       <c r="W576" t="inlineStr"/>
     </row>
@@ -44793,7 +44797,7 @@
         <v>398</v>
       </c>
       <c r="P595" t="n">
-        <v>167</v>
+        <v>92</v>
       </c>
       <c r="Q595" t="n">
         <v>398</v>
@@ -46203,7 +46207,7 @@
         <v>3274</v>
       </c>
       <c r="P613" t="n">
-        <v>2532</v>
+        <v>2933</v>
       </c>
       <c r="Q613" t="n">
         <v>3274</v>
@@ -48001,13 +48005,13 @@
         <v>447</v>
       </c>
       <c r="P637" t="n">
-        <v>687</v>
+        <v>942</v>
       </c>
       <c r="Q637" t="n">
-        <v>687</v>
+        <v>942</v>
       </c>
       <c r="R637" t="n">
-        <v>11.45</v>
+        <v>15.7</v>
       </c>
       <c r="S637" t="n">
         <v>8</v>
@@ -48021,7 +48025,7 @@
         <v>964.63</v>
       </c>
       <c r="V637" t="n">
-        <v>-28.78</v>
+        <v>-2.35</v>
       </c>
       <c r="W637" t="inlineStr"/>
     </row>
@@ -48315,7 +48319,7 @@
         <v>7248</v>
       </c>
       <c r="P641" t="n">
-        <v>4823</v>
+        <v>4412</v>
       </c>
       <c r="Q641" t="n">
         <v>9088</v>
@@ -49403,7 +49407,7 @@
         <v>2179</v>
       </c>
       <c r="P655" t="n">
-        <v>2151</v>
+        <v>2780</v>
       </c>
       <c r="Q655" t="n">
         <v>2801</v>
@@ -51010,13 +51014,13 @@
         <v>2439</v>
       </c>
       <c r="P676" t="n">
-        <v>3098</v>
+        <v>3083</v>
       </c>
       <c r="Q676" t="n">
-        <v>3098</v>
+        <v>3083</v>
       </c>
       <c r="R676" t="n">
-        <v>25.82</v>
+        <v>25.69</v>
       </c>
       <c r="S676" t="n">
         <v>8</v>
@@ -51030,7 +51034,7 @@
         <v>4555.14</v>
       </c>
       <c r="V676" t="n">
-        <v>-31.99</v>
+        <v>-32.32</v>
       </c>
       <c r="W676" t="inlineStr"/>
     </row>
@@ -52119,13 +52123,13 @@
         <v>372</v>
       </c>
       <c r="P691" t="n">
-        <v>687</v>
+        <v>932</v>
       </c>
       <c r="Q691" t="n">
-        <v>687</v>
+        <v>932</v>
       </c>
       <c r="R691" t="n">
-        <v>15.98</v>
+        <v>21.67</v>
       </c>
       <c r="S691" t="n">
         <v>8</v>
@@ -52139,7 +52143,7 @@
         <v>1851.79</v>
       </c>
       <c r="V691" t="n">
-        <v>-62.9</v>
+        <v>-49.67</v>
       </c>
       <c r="W691" t="inlineStr"/>
     </row>
@@ -53124,13 +53128,13 @@
         <v>266</v>
       </c>
       <c r="P704" t="n">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="Q704" t="n">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="R704" t="n">
-        <v>6.9</v>
+        <v>7.02</v>
       </c>
       <c r="S704" t="n">
         <v>8</v>
@@ -53144,7 +53148,7 @@
         <v>285.39</v>
       </c>
       <c r="V704" t="n">
-        <v>-3.29</v>
+        <v>-1.54</v>
       </c>
       <c r="W704" t="inlineStr"/>
     </row>
@@ -53357,7 +53361,7 @@
         <v>400</v>
       </c>
       <c r="P707" t="n">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="Q707" t="n">
         <v>410</v>
@@ -53434,7 +53438,7 @@
         <v>3176</v>
       </c>
       <c r="P708" t="n">
-        <v>1030</v>
+        <v>1082</v>
       </c>
       <c r="Q708" t="n">
         <v>3176</v>
@@ -53902,7 +53906,7 @@
         <v>4</v>
       </c>
       <c r="P714" t="n">
-        <v>-56</v>
+        <v>-50</v>
       </c>
       <c r="Q714" t="n">
         <v>4528</v>
@@ -54370,13 +54374,13 @@
         <v>1355</v>
       </c>
       <c r="P720" t="n">
-        <v>1334</v>
+        <v>1627</v>
       </c>
       <c r="Q720" t="n">
-        <v>1486</v>
+        <v>1627</v>
       </c>
       <c r="R720" t="n">
-        <v>14.8</v>
+        <v>16.21</v>
       </c>
       <c r="S720" t="n">
         <v>8</v>
@@ -54390,7 +54394,7 @@
         <v>4501.56</v>
       </c>
       <c r="V720" t="n">
-        <v>-66.98999999999999</v>
+        <v>-63.86</v>
       </c>
       <c r="W720" t="inlineStr"/>
     </row>
@@ -55454,7 +55458,7 @@
         <v>6867</v>
       </c>
       <c r="P734" t="n">
-        <v>6370</v>
+        <v>6562</v>
       </c>
       <c r="Q734" t="n">
         <v>7742</v>
@@ -56155,7 +56159,7 @@
         <v>8830</v>
       </c>
       <c r="P743" t="n">
-        <v>6506</v>
+        <v>5581</v>
       </c>
       <c r="Q743" t="n">
         <v>8830</v>
@@ -56848,7 +56852,7 @@
         <v>5114</v>
       </c>
       <c r="P752" t="n">
-        <v>1917</v>
+        <v>1882</v>
       </c>
       <c r="Q752" t="n">
         <v>5114</v>
@@ -56921,7 +56925,7 @@
         <v>1154</v>
       </c>
       <c r="P753" t="n">
-        <v>910</v>
+        <v>877</v>
       </c>
       <c r="Q753" t="n">
         <v>1431</v>
@@ -57150,13 +57154,13 @@
         <v>1934</v>
       </c>
       <c r="P756" t="n">
-        <v>3412</v>
+        <v>3352</v>
       </c>
       <c r="Q756" t="n">
-        <v>3412</v>
+        <v>3352</v>
       </c>
       <c r="R756" t="n">
-        <v>42.65</v>
+        <v>41.9</v>
       </c>
       <c r="S756" t="n">
         <v>8</v>
@@ -57170,10 +57174,10 @@
         <v>2448.7</v>
       </c>
       <c r="V756" t="n">
-        <v>39.34</v>
+        <v>36.89</v>
       </c>
       <c r="W756" t="n">
-        <v>1.358009671633811</v>
+        <v>1.350752317292871</v>
       </c>
     </row>
     <row r="757">
@@ -62676,13 +62680,13 @@
         <v>7806</v>
       </c>
       <c r="P832" t="n">
-        <v>7480</v>
+        <v>9400</v>
       </c>
       <c r="Q832" t="n">
-        <v>7806</v>
+        <v>9400</v>
       </c>
       <c r="R832" t="n">
-        <v>65.05</v>
+        <v>78.33</v>
       </c>
       <c r="S832" t="n">
         <v>8</v>
@@ -62696,10 +62700,10 @@
         <v>4603.66</v>
       </c>
       <c r="V832" t="n">
-        <v>69.56</v>
+        <v>104.19</v>
       </c>
       <c r="W832" t="n">
-        <v>1.424065497627815</v>
+        <v>1.472828467557885</v>
       </c>
     </row>
     <row r="833">
@@ -62911,13 +62915,13 @@
         <v>1722</v>
       </c>
       <c r="P835" t="n">
-        <v>1891</v>
+        <v>1749</v>
       </c>
       <c r="Q835" t="n">
-        <v>1891</v>
+        <v>1749</v>
       </c>
       <c r="R835" t="n">
-        <v>21.01</v>
+        <v>19.43</v>
       </c>
       <c r="S835" t="n">
         <v>8</v>
@@ -62931,7 +62935,7 @@
         <v>3162.28</v>
       </c>
       <c r="V835" t="n">
-        <v>-40.2</v>
+        <v>-44.69</v>
       </c>
       <c r="W835" t="inlineStr"/>
     </row>
@@ -65627,7 +65631,7 @@
         <v>5274</v>
       </c>
       <c r="P871" t="n">
-        <v>3737</v>
+        <v>3760</v>
       </c>
       <c r="Q871" t="n">
         <v>8343</v>
